--- a/Oil_current.xlsx
+++ b/Oil_current.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29328"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="V:\Information Management\Info Sharing and Tracking\Product Services\Operations\Product Creation\ST3\ST3s_Report_Prep\All_Pages_Content_Update\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B5589DE-3C88-46D9-B3A8-428A11D4D02C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F475B57-7982-4BE7-9A9B-7D860B43BBCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="16440" windowHeight="28320" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-19310" yWindow="1390" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Documentation" sheetId="21" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="130">
   <si>
     <t>Reporting Adjustment</t>
   </si>
@@ -479,7 +479,7 @@
     <t/>
   </si>
   <si>
-    <t xml:space="preserve"> Run Date:  27 October 2025</t>
+    <t xml:space="preserve"> Run Date:  29 December 2025</t>
   </si>
 </sst>
 </file>
@@ -835,7 +835,7 @@
     </xf>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="116">
+  <cellXfs count="111">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1051,44 +1051,31 @@
     <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="6"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" indent="3"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" indent="3"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" indent="6"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="16">
@@ -1188,9 +1175,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>1694180</xdr:colOff>
+      <xdr:colOff>1697990</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>18051</xdr:rowOff>
+      <xdr:rowOff>21861</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1523,17 +1510,17 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:BK84"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
     <col min="2" max="2" width="43" customWidth="1"/>
-    <col min="3" max="3" width="3.88671875" customWidth="1"/>
-    <col min="4" max="15" width="14.5546875" customWidth="1"/>
-    <col min="16" max="16" width="1.5546875" customWidth="1"/>
+    <col min="3" max="3" width="3.85546875" customWidth="1"/>
+    <col min="4" max="15" width="14.5703125" customWidth="1"/>
+    <col min="16" max="16" width="1.5703125" customWidth="1"/>
     <col min="17" max="17" width="17" customWidth="1"/>
-    <col min="18" max="18" width="14.5546875" customWidth="1"/>
-    <col min="21" max="21" width="20.33203125" customWidth="1"/>
-    <col min="22" max="22" width="14.44140625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.5703125" customWidth="1"/>
+    <col min="21" max="21" width="20.28515625" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:63" s="2" customFormat="1" ht="20.25" customHeight="1">
@@ -1646,11 +1633,11 @@
     </row>
     <row r="3" spans="1:63" s="2" customFormat="1" ht="19.5" customHeight="1">
       <c r="G3" s="33"/>
-      <c r="H3" s="104" t="s">
+      <c r="H3" s="108" t="s">
         <v>120</v>
       </c>
-      <c r="I3" s="104"/>
-      <c r="J3" s="104"/>
+      <c r="I3" s="108"/>
+      <c r="J3" s="108"/>
       <c r="K3" s="34"/>
       <c r="M3" s="2" t="s">
         <v>38</v>
@@ -2509,7 +2496,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="56" spans="1:19" ht="15" thickBot="1">
+    <row r="56" spans="1:19" ht="15.75" thickBot="1">
       <c r="B56" s="50"/>
       <c r="C56" s="17"/>
       <c r="D56" s="69"/>
@@ -2526,7 +2513,7 @@
       <c r="O56" s="25"/>
       <c r="Q56" s="25"/>
     </row>
-    <row r="57" spans="1:19" ht="15" thickTop="1">
+    <row r="57" spans="1:19" ht="15.75" thickTop="1">
       <c r="B57" s="59" t="s">
         <v>31</v>
       </c>
@@ -2748,7 +2735,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="77" spans="2:17" ht="15" thickBot="1">
+    <row r="77" spans="2:17" ht="15.75" thickBot="1">
       <c r="B77" s="50"/>
       <c r="C77" s="19"/>
       <c r="D77" s="69"/>
@@ -2765,7 +2752,7 @@
       <c r="O77" s="25"/>
       <c r="Q77" s="25"/>
     </row>
-    <row r="78" spans="2:17" ht="15" thickTop="1">
+    <row r="78" spans="2:17" ht="15.75" thickTop="1">
       <c r="B78" s="59" t="s">
         <v>36</v>
       </c>
@@ -2819,16 +2806,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:V89"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
-    <col min="2" max="2" width="44.6640625" customWidth="1"/>
+    <col min="2" max="2" width="44.7109375" customWidth="1"/>
     <col min="3" max="3" width="4" customWidth="1"/>
-    <col min="4" max="13" width="15.6640625" customWidth="1"/>
-    <col min="14" max="14" width="15.88671875" customWidth="1"/>
-    <col min="15" max="15" width="15.6640625" customWidth="1"/>
-    <col min="16" max="16" width="1.5546875" customWidth="1"/>
-    <col min="17" max="17" width="19.44140625" customWidth="1"/>
+    <col min="4" max="13" width="15.7109375" customWidth="1"/>
+    <col min="14" max="14" width="15.85546875" customWidth="1"/>
+    <col min="15" max="15" width="15.7109375" customWidth="1"/>
+    <col min="16" max="16" width="1.5703125" customWidth="1"/>
+    <col min="17" max="17" width="19.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:22" s="2" customFormat="1" ht="20.25" customHeight="1">
@@ -2846,11 +2833,11 @@
     </row>
     <row r="3" spans="2:22" s="2" customFormat="1" ht="19.5" customHeight="1">
       <c r="G3" s="33"/>
-      <c r="H3" s="104" t="s">
+      <c r="H3" s="108" t="s">
         <v>120</v>
       </c>
-      <c r="I3" s="104"/>
-      <c r="J3" s="104"/>
+      <c r="I3" s="108"/>
+      <c r="J3" s="108"/>
       <c r="K3" s="34"/>
       <c r="Q3"/>
     </row>
@@ -2932,44 +2919,44 @@
       </c>
       <c r="C7"/>
       <c r="D7" s="90">
-        <v>9506619.9000000004</v>
+        <v>9506670.5999999996</v>
       </c>
       <c r="E7" s="16">
-        <v>9473787.8000000007</v>
+        <v>9474020.8000000007</v>
       </c>
       <c r="F7" s="16">
-        <v>8863594.4000000004</v>
+        <v>8863827.3000000007</v>
       </c>
       <c r="G7" s="16">
-        <v>9166840.3000000007</v>
+        <v>9166898.4000000004</v>
       </c>
       <c r="H7" s="16">
-        <v>10019682.5</v>
+        <v>10019874.1</v>
       </c>
       <c r="I7" s="16">
-        <v>9475340</v>
+        <v>9475582.3000000007</v>
       </c>
       <c r="J7" s="16">
-        <v>9440385.8000000007</v>
+        <v>9440603.5999999996</v>
       </c>
       <c r="K7" s="16">
-        <v>9658687.3000000007</v>
+        <v>9659011.3000000007</v>
       </c>
       <c r="L7" s="16">
-        <v>9453096.6999999993</v>
+        <v>9453269.9000000004</v>
       </c>
       <c r="M7" s="16">
-        <v>0</v>
+        <v>9791836</v>
       </c>
       <c r="N7" s="16">
-        <v>0</v>
+        <v>9498595.5</v>
       </c>
       <c r="O7" s="16">
         <v>0</v>
       </c>
       <c r="P7" s="8"/>
       <c r="Q7" s="91">
-        <v>9506619.9000000004</v>
+        <v>9506670.5999999996</v>
       </c>
       <c r="V7" s="16"/>
     </row>
@@ -3033,44 +3020,44 @@
         <v>25</v>
       </c>
       <c r="D11" s="90">
-        <v>1504352</v>
+        <v>1500578.1</v>
       </c>
       <c r="E11" s="16">
-        <v>1373031.9</v>
+        <v>1369310.1</v>
       </c>
       <c r="F11" s="16">
-        <v>1595942.9</v>
+        <v>1586346.7</v>
       </c>
       <c r="G11" s="16">
-        <v>1568974.1</v>
+        <v>1554035</v>
       </c>
       <c r="H11" s="16">
-        <v>1579879.1</v>
+        <v>1561687.6</v>
       </c>
       <c r="I11" s="16">
-        <v>1518130.7</v>
+        <v>1500419.7</v>
       </c>
       <c r="J11" s="16">
-        <v>1592509.6</v>
+        <v>1573026.5</v>
       </c>
       <c r="K11" s="16">
-        <v>1602644.6</v>
+        <v>1583247.8</v>
       </c>
       <c r="L11" s="16">
-        <v>1526191.3</v>
+        <v>1503127</v>
       </c>
       <c r="M11" s="16">
-        <v>0</v>
+        <v>1613400.3</v>
       </c>
       <c r="N11" s="16">
-        <v>0</v>
+        <v>1625997.7</v>
       </c>
       <c r="O11" s="16">
         <v>0</v>
       </c>
       <c r="P11" s="8"/>
       <c r="Q11" s="91">
-        <v>13861656.199999999</v>
+        <v>16971176.5</v>
       </c>
     </row>
     <row r="12" spans="2:22" s="1" customFormat="1">
@@ -3079,44 +3066,44 @@
       </c>
       <c r="C12"/>
       <c r="D12" s="90">
-        <v>374350.5</v>
+        <v>378569.5</v>
       </c>
       <c r="E12" s="16">
-        <v>331222</v>
+        <v>334457.7</v>
       </c>
       <c r="F12" s="16">
-        <v>382820.3</v>
+        <v>388112.1</v>
       </c>
       <c r="G12" s="16">
-        <v>372022</v>
+        <v>377949.5</v>
       </c>
       <c r="H12" s="16">
-        <v>371738.7</v>
+        <v>378470.3</v>
       </c>
       <c r="I12" s="16">
-        <v>341204</v>
+        <v>349360.7</v>
       </c>
       <c r="J12" s="16">
-        <v>349883</v>
+        <v>361290.3</v>
       </c>
       <c r="K12" s="16">
-        <v>346225</v>
+        <v>358283.9</v>
       </c>
       <c r="L12" s="16">
-        <v>334003.90000000002</v>
+        <v>349318.3</v>
       </c>
       <c r="M12" s="16">
-        <v>0</v>
+        <v>355715.6</v>
       </c>
       <c r="N12" s="16">
-        <v>0</v>
+        <v>347065.59999999998</v>
       </c>
       <c r="O12" s="16">
         <v>0</v>
       </c>
       <c r="P12" s="8"/>
       <c r="Q12" s="91">
-        <v>3203469.4</v>
+        <v>3978593.4999999995</v>
       </c>
     </row>
     <row r="13" spans="2:22">
@@ -3124,44 +3111,44 @@
         <v>27</v>
       </c>
       <c r="D13" s="90">
-        <v>177680.7</v>
+        <v>178514.1</v>
       </c>
       <c r="E13" s="16">
-        <v>159687.20000000001</v>
+        <v>160436.5</v>
       </c>
       <c r="F13" s="16">
-        <v>185699.20000000001</v>
+        <v>186608.6</v>
       </c>
       <c r="G13" s="16">
-        <v>173536.9</v>
+        <v>174999.1</v>
       </c>
       <c r="H13" s="16">
-        <v>177153.9</v>
+        <v>180036.2</v>
       </c>
       <c r="I13" s="16">
-        <v>167331.9</v>
+        <v>169476.7</v>
       </c>
       <c r="J13" s="16">
-        <v>172315.1</v>
+        <v>172138.2</v>
       </c>
       <c r="K13" s="16">
-        <v>171103.5</v>
+        <v>171129.3</v>
       </c>
       <c r="L13" s="16">
-        <v>162637.70000000001</v>
+        <v>163010</v>
       </c>
       <c r="M13" s="16">
-        <v>0</v>
+        <v>168484.4</v>
       </c>
       <c r="N13" s="16">
-        <v>0</v>
+        <v>162856.4</v>
       </c>
       <c r="O13" s="16">
         <v>0</v>
       </c>
       <c r="P13" s="8"/>
       <c r="Q13" s="91">
-        <v>1547146.1</v>
+        <v>1887689.4999999998</v>
       </c>
     </row>
     <row r="14" spans="2:22">
@@ -3169,44 +3156,44 @@
         <v>122</v>
       </c>
       <c r="D14" s="96">
-        <v>652795.6</v>
+        <v>652946.69999999995</v>
       </c>
       <c r="E14" s="76">
-        <v>585014</v>
+        <v>586029.5</v>
       </c>
       <c r="F14" s="76">
-        <v>644159.5</v>
+        <v>648942.30000000005</v>
       </c>
       <c r="G14" s="75">
-        <v>618855.5</v>
+        <v>627743</v>
       </c>
       <c r="H14" s="75">
-        <v>627495.4</v>
+        <v>637325.9</v>
       </c>
       <c r="I14" s="75">
-        <v>615875.1</v>
+        <v>624375.9</v>
       </c>
       <c r="J14" s="75">
-        <v>628878.6</v>
+        <v>638371.4</v>
       </c>
       <c r="K14" s="75">
-        <v>626441.4</v>
+        <v>634514.69999999995</v>
       </c>
       <c r="L14" s="75">
-        <v>613825.5</v>
+        <v>620250</v>
       </c>
       <c r="M14" s="75">
-        <v>0</v>
+        <v>630133</v>
       </c>
       <c r="N14" s="75">
-        <v>0</v>
+        <v>620862.5</v>
       </c>
       <c r="O14" s="75">
         <v>0</v>
       </c>
       <c r="P14" s="76"/>
       <c r="Q14" s="96">
-        <v>5613340.6000000006</v>
+        <v>6921494.9000000004</v>
       </c>
     </row>
     <row r="15" spans="2:22" s="1" customFormat="1">
@@ -3214,44 +3201,44 @@
         <v>114</v>
       </c>
       <c r="D15" s="90">
-        <v>2709178.8</v>
+        <v>2710608.4000000004</v>
       </c>
       <c r="E15" s="16">
-        <v>2448955.0999999996</v>
+        <v>2450233.7999999998</v>
       </c>
       <c r="F15" s="16">
-        <v>2808621.9</v>
+        <v>2810009.7</v>
       </c>
       <c r="G15" s="16">
-        <v>2733388.5</v>
+        <v>2734726.6</v>
       </c>
       <c r="H15" s="16">
-        <v>2756267.1</v>
+        <v>2757520</v>
       </c>
       <c r="I15" s="16">
-        <v>2642541.6999999997</v>
+        <v>2643633</v>
       </c>
       <c r="J15" s="16">
-        <v>2743586.3000000003</v>
+        <v>2744826.4</v>
       </c>
       <c r="K15" s="16">
-        <v>2746414.5</v>
+        <v>2747175.7</v>
       </c>
       <c r="L15" s="16">
-        <v>2636658.4000000004</v>
+        <v>2635705.2999999998</v>
       </c>
       <c r="M15" s="16">
-        <v>0</v>
+        <v>2767733.3</v>
       </c>
       <c r="N15" s="16">
-        <v>0</v>
+        <v>2756782.1999999997</v>
       </c>
       <c r="O15" s="16">
         <v>0</v>
       </c>
       <c r="P15" s="8"/>
       <c r="Q15" s="91">
-        <v>24225612.300000001</v>
+        <v>29758954.399999999</v>
       </c>
     </row>
     <row r="16" spans="2:22" s="1" customFormat="1">
@@ -3276,44 +3263,44 @@
         <v>30</v>
       </c>
       <c r="D17" s="90">
-        <v>414554.2</v>
+        <v>413127.3</v>
       </c>
       <c r="E17" s="16">
-        <v>358190.4</v>
+        <v>356911.7</v>
       </c>
       <c r="F17" s="16">
-        <v>394239.8</v>
+        <v>392862.7</v>
       </c>
       <c r="G17" s="16">
-        <v>421093.4</v>
+        <v>419757.4</v>
       </c>
       <c r="H17" s="16">
-        <v>442105.1</v>
+        <v>440859.9</v>
       </c>
       <c r="I17" s="16">
-        <v>386714.1</v>
+        <v>385598.9</v>
       </c>
       <c r="J17" s="16">
-        <v>421275.9</v>
+        <v>419995.9</v>
       </c>
       <c r="K17" s="16">
-        <v>437192.7</v>
+        <v>436399.4</v>
       </c>
       <c r="L17" s="16">
-        <v>426853.5</v>
+        <v>426799.5</v>
       </c>
       <c r="M17" s="16">
-        <v>0</v>
+        <v>444218.9</v>
       </c>
       <c r="N17" s="16">
-        <v>0</v>
+        <v>480521.8</v>
       </c>
       <c r="O17" s="16">
         <v>0</v>
       </c>
       <c r="P17" s="8"/>
       <c r="Q17" s="91">
-        <v>3702219.1000000006</v>
+        <v>4617053.3999999994</v>
       </c>
     </row>
     <row r="18" spans="2:17">
@@ -3377,44 +3364,44 @@
       </c>
       <c r="C21" s="18"/>
       <c r="D21" s="90">
-        <v>9632904.5999999996</v>
+        <v>9633084.1999999993</v>
       </c>
       <c r="E21" s="16">
-        <v>8586573.8000000007</v>
+        <v>8586573.6999999993</v>
       </c>
       <c r="F21" s="16">
-        <v>9674675.1999999993</v>
+        <v>9674228.9000000004</v>
       </c>
       <c r="G21" s="16">
-        <v>9111057.1999999993</v>
+        <v>9111404.8000000007</v>
       </c>
       <c r="H21" s="16">
-        <v>8858743.1999999993</v>
+        <v>8858833.8000000007</v>
       </c>
       <c r="I21" s="16">
-        <v>8756491.1999999993</v>
+        <v>8756491.5</v>
       </c>
       <c r="J21" s="16">
-        <v>9732681.4000000004</v>
+        <v>9732291.5</v>
       </c>
       <c r="K21" s="16">
-        <v>9668690.4000000004</v>
+        <v>9668037.9000000004</v>
       </c>
       <c r="L21" s="16">
-        <v>9193391.6999999993</v>
+        <v>9195188</v>
       </c>
       <c r="M21" s="16">
-        <v>0</v>
+        <v>9721119.0999999996</v>
       </c>
       <c r="N21" s="16">
-        <v>0</v>
+        <v>9611281.1999999993</v>
       </c>
       <c r="O21" s="16">
         <v>0</v>
       </c>
       <c r="P21" s="8"/>
       <c r="Q21" s="91">
-        <v>83215208.700000003</v>
+        <v>102548534.59999999</v>
       </c>
     </row>
     <row r="22" spans="2:17">
@@ -3441,26 +3428,26 @@
         <v>8448607.8000000007</v>
       </c>
       <c r="J22" s="16">
-        <v>9342586.8000000007</v>
+        <v>9336202.6999999993</v>
       </c>
       <c r="K22" s="16">
-        <v>9088365.5</v>
+        <v>9061990.1999999993</v>
       </c>
       <c r="L22" s="16">
-        <v>8879617.8000000007</v>
+        <v>8878592.9000000004</v>
       </c>
       <c r="M22" s="16">
-        <v>0</v>
+        <v>8522998.1999999993</v>
       </c>
       <c r="N22" s="16">
-        <v>0</v>
+        <v>9090317.3000000007</v>
       </c>
       <c r="O22" s="16">
         <v>0</v>
       </c>
       <c r="P22" s="8"/>
       <c r="Q22" s="91">
-        <v>75313237.199999988</v>
+        <v>92892768.400000006</v>
       </c>
     </row>
     <row r="23" spans="2:17">
@@ -3487,26 +3474,26 @@
         <v>-6572086.0999999996</v>
       </c>
       <c r="J23" s="16">
-        <v>-7692217.0999999996</v>
+        <v>-7685788.0999999996</v>
       </c>
       <c r="K23" s="16">
-        <v>-7791409.0999999996</v>
+        <v>-7765147.5999999996</v>
       </c>
       <c r="L23" s="16">
-        <v>-7285570.7999999998</v>
+        <v>-7284179.2000000002</v>
       </c>
       <c r="M23" s="16">
-        <v>0</v>
+        <v>-7767823.9000000004</v>
       </c>
       <c r="N23" s="16">
-        <v>0</v>
+        <v>-8027360.0999999996</v>
       </c>
       <c r="O23" s="16">
         <v>0</v>
       </c>
       <c r="P23" s="8"/>
       <c r="Q23" s="91">
-        <v>-64206282.700000003</v>
+        <v>-79967384.600000009</v>
       </c>
     </row>
     <row r="24" spans="2:17">
@@ -3515,44 +3502,44 @@
       </c>
       <c r="C24" s="17"/>
       <c r="D24" s="90">
-        <v>10490851.699999999</v>
+        <v>10491031.300000001</v>
       </c>
       <c r="E24" s="16">
-        <v>9086275.5000000019</v>
+        <v>9086275.4000000004</v>
       </c>
       <c r="F24" s="16">
-        <v>10717104.899999999</v>
+        <v>10716658.600000001</v>
       </c>
       <c r="G24" s="16">
-        <v>10283893.300000001</v>
+        <v>10284240.900000002</v>
       </c>
       <c r="H24" s="16">
-        <v>9974888.2999999989</v>
+        <v>9974978.9000000004</v>
       </c>
       <c r="I24" s="16">
-        <v>10633012.9</v>
+        <v>10633013.200000001</v>
       </c>
       <c r="J24" s="16">
-        <v>11383051.100000003</v>
+        <v>11382706.1</v>
       </c>
       <c r="K24" s="16">
-        <v>10965646.799999999</v>
+        <v>10964880.500000002</v>
       </c>
       <c r="L24" s="16">
-        <v>10787438.699999999</v>
+        <v>10789601.699999999</v>
       </c>
       <c r="M24" s="16">
-        <v>0</v>
+        <v>10476293.399999997</v>
       </c>
       <c r="N24" s="16">
-        <v>0</v>
+        <v>10674238.4</v>
       </c>
       <c r="O24" s="16">
         <v>0</v>
       </c>
       <c r="P24" s="8"/>
       <c r="Q24" s="91">
-        <v>94322163.199999973</v>
+        <v>115473918.39999999</v>
       </c>
     </row>
     <row r="25" spans="2:17">
@@ -3578,26 +3565,26 @@
         <v>5698414.5</v>
       </c>
       <c r="J25" s="42">
-        <v>6714940.2999999998</v>
+        <v>6714939.2000000002</v>
       </c>
       <c r="K25" s="42">
-        <v>6697996.7000000002</v>
+        <v>6698151.5</v>
       </c>
       <c r="L25" s="42">
-        <v>6241019.2000000002</v>
+        <v>6240638.5999999996</v>
       </c>
       <c r="M25" s="42">
-        <v>0</v>
+        <v>6696334.5999999996</v>
       </c>
       <c r="N25" s="42">
-        <v>0</v>
+        <v>7061615.7999999998</v>
       </c>
       <c r="O25" s="42">
         <v>0</v>
       </c>
       <c r="P25" s="8"/>
       <c r="Q25" s="98">
-        <v>55372309.900000006</v>
+        <v>69130033.400000006</v>
       </c>
     </row>
     <row r="26" spans="2:17">
@@ -3605,44 +3592,44 @@
         <v>46</v>
       </c>
       <c r="D26" s="90">
-        <v>17532418.899999999</v>
+        <v>17532598.5</v>
       </c>
       <c r="E26" s="16">
-        <v>15073567.700000003</v>
+        <v>15073567.600000001</v>
       </c>
       <c r="F26" s="16">
-        <v>17459781</v>
+        <v>17459334.700000003</v>
       </c>
       <c r="G26" s="16">
-        <v>15931717.4</v>
+        <v>15932065.000000002</v>
       </c>
       <c r="H26" s="16">
-        <v>14575467.899999999</v>
+        <v>14575558.5</v>
       </c>
       <c r="I26" s="16">
-        <v>16331427.4</v>
+        <v>16331427.700000001</v>
       </c>
       <c r="J26" s="16">
-        <v>18097991.400000002</v>
+        <v>18097645.300000001</v>
       </c>
       <c r="K26" s="16">
-        <v>17663643.5</v>
+        <v>17663032</v>
       </c>
       <c r="L26" s="16">
-        <v>17028457.899999999</v>
+        <v>17030240.299999997</v>
       </c>
       <c r="M26" s="16">
-        <v>0</v>
+        <v>17172627.999999996</v>
       </c>
       <c r="N26" s="16">
-        <v>0</v>
+        <v>17735854.199999999</v>
       </c>
       <c r="O26" s="16">
         <v>0</v>
       </c>
       <c r="P26" s="8"/>
       <c r="Q26" s="91">
-        <v>149694473.09999996</v>
+        <v>184603951.80000001</v>
       </c>
     </row>
     <row r="27" spans="2:17">
@@ -3668,44 +3655,44 @@
       </c>
       <c r="C28" s="17"/>
       <c r="D28" s="90">
-        <v>20656151.899999999</v>
+        <v>20656334.199999999</v>
       </c>
       <c r="E28" s="16">
-        <v>17880713.200000003</v>
+        <v>17880713.100000001</v>
       </c>
       <c r="F28" s="16">
-        <v>20662642.699999999</v>
+        <v>20662207.100000001</v>
       </c>
       <c r="G28" s="16">
-        <v>19086199.299999997</v>
+        <v>19086549</v>
       </c>
       <c r="H28" s="16">
-        <v>17773840.100000001</v>
+        <v>17773938.399999999</v>
       </c>
       <c r="I28" s="16">
-        <v>19360683.200000003</v>
+        <v>19360659.600000001</v>
       </c>
       <c r="J28" s="16">
-        <v>21262853.600000001</v>
+        <v>21262467.599999998</v>
       </c>
       <c r="K28" s="16">
-        <v>20847250.699999999</v>
+        <v>20846607.099999998</v>
       </c>
       <c r="L28" s="16">
-        <v>20091969.799999997</v>
+        <v>20092745.099999998</v>
       </c>
       <c r="M28" s="16">
-        <v>0</v>
+        <v>20384580.199999996</v>
       </c>
       <c r="N28" s="16">
-        <v>0</v>
+        <v>20973158.199999999</v>
       </c>
       <c r="O28" s="16">
         <v>0</v>
       </c>
       <c r="P28" s="8"/>
       <c r="Q28" s="90">
-        <v>177622304.49999997</v>
+        <v>218979959.60000002</v>
       </c>
     </row>
     <row r="29" spans="2:17">
@@ -3749,7 +3736,7 @@
         <v>49</v>
       </c>
       <c r="D31" s="90">
-        <v>1243178.2</v>
+        <v>1243239.2</v>
       </c>
       <c r="E31" s="16">
         <v>1071663.1000000001</v>
@@ -3767,26 +3754,26 @@
         <v>1127290.7</v>
       </c>
       <c r="J31" s="16">
-        <v>1240310.2</v>
+        <v>1240232</v>
       </c>
       <c r="K31" s="16">
-        <v>1269226.3999999999</v>
+        <v>1269247</v>
       </c>
       <c r="L31" s="16">
-        <v>1267545.6000000001</v>
+        <v>1267540</v>
       </c>
       <c r="M31" s="16">
-        <v>0</v>
+        <v>1317951.1000000001</v>
       </c>
       <c r="N31" s="16">
-        <v>0</v>
+        <v>1312369.3</v>
       </c>
       <c r="O31" s="16">
         <v>0</v>
       </c>
       <c r="P31" s="8"/>
       <c r="Q31" s="91">
-        <v>10889678.399999999</v>
+        <v>13519996.6</v>
       </c>
     </row>
     <row r="32" spans="2:17">
@@ -3821,17 +3808,17 @@
         <v>360140.3</v>
       </c>
       <c r="M32" s="16">
-        <v>0</v>
+        <v>366038.7</v>
       </c>
       <c r="N32" s="16">
-        <v>0</v>
+        <v>395917.7</v>
       </c>
       <c r="O32" s="16">
         <v>0</v>
       </c>
       <c r="P32" s="8"/>
       <c r="Q32" s="90">
-        <v>3335094.9</v>
+        <v>4097051.3000000003</v>
       </c>
     </row>
     <row r="33" spans="2:17">
@@ -3875,7 +3862,7 @@
         <v>9398.4</v>
       </c>
       <c r="J34" s="16">
-        <v>10289.299999999999</v>
+        <v>10341.700000000001</v>
       </c>
       <c r="K34" s="16">
         <v>10489.1</v>
@@ -3884,17 +3871,17 @@
         <v>9211.2000000000007</v>
       </c>
       <c r="M34" s="16">
-        <v>0</v>
+        <v>10256.4</v>
       </c>
       <c r="N34" s="16">
-        <v>0</v>
+        <v>9775.5</v>
       </c>
       <c r="O34" s="16">
         <v>0</v>
       </c>
       <c r="P34" s="8"/>
       <c r="Q34" s="91">
-        <v>93634.6</v>
+        <v>113718.90000000001</v>
       </c>
     </row>
     <row r="35" spans="2:17">
@@ -3930,17 +3917,17 @@
         <v>13283</v>
       </c>
       <c r="M35" s="16">
-        <v>0</v>
+        <v>14729.9</v>
       </c>
       <c r="N35" s="16">
-        <v>0</v>
+        <v>13051.2</v>
       </c>
       <c r="O35" s="16">
         <v>0</v>
       </c>
       <c r="P35" s="8"/>
       <c r="Q35" s="91">
-        <v>86772</v>
+        <v>114553.09999999999</v>
       </c>
     </row>
     <row r="36" spans="2:17">
@@ -3967,26 +3954,26 @@
         <v>346895.6</v>
       </c>
       <c r="J36" s="16">
-        <v>447301</v>
+        <v>447325</v>
       </c>
       <c r="K36" s="16">
-        <v>359056.3</v>
+        <v>359023.8</v>
       </c>
       <c r="L36" s="16">
-        <v>459452.4</v>
+        <v>346730.7</v>
       </c>
       <c r="M36" s="16">
-        <v>0</v>
+        <v>402894.4</v>
       </c>
       <c r="N36" s="16">
-        <v>0</v>
+        <v>495527.1</v>
       </c>
       <c r="O36" s="16">
         <v>0</v>
       </c>
       <c r="P36" s="8"/>
       <c r="Q36" s="91">
-        <v>3940952.6999999997</v>
+        <v>4726644</v>
       </c>
     </row>
     <row r="37" spans="2:17">
@@ -4040,17 +4027,17 @@
         <v>245857.6</v>
       </c>
       <c r="M38" s="16">
-        <v>0</v>
+        <v>268526.09999999998</v>
       </c>
       <c r="N38" s="16">
-        <v>0</v>
+        <v>270289.59999999998</v>
       </c>
       <c r="O38" s="16">
         <v>0</v>
       </c>
       <c r="P38" s="8"/>
       <c r="Q38" s="91">
-        <v>2247084.9</v>
+        <v>2785900.6</v>
       </c>
     </row>
     <row r="39" spans="2:17">
@@ -4086,17 +4073,17 @@
         <v>209.4</v>
       </c>
       <c r="M39" s="16">
-        <v>0</v>
+        <v>361.6</v>
       </c>
       <c r="N39" s="16">
-        <v>0</v>
+        <v>382.8</v>
       </c>
       <c r="O39" s="16">
         <v>0</v>
       </c>
       <c r="P39" s="8"/>
       <c r="Q39" s="91">
-        <v>728.19999999999993</v>
+        <v>1472.6</v>
       </c>
     </row>
     <row r="40" spans="2:17">
@@ -4118,10 +4105,10 @@
       <c r="Q40" s="91"/>
     </row>
     <row r="41" spans="2:17">
-      <c r="B41" s="105" t="s">
+      <c r="B41" s="102" t="s">
         <v>42</v>
       </c>
-      <c r="C41" s="106"/>
+      <c r="C41" s="17"/>
       <c r="D41" s="90"/>
       <c r="E41" s="90"/>
       <c r="F41" s="90"/>
@@ -4138,10 +4125,10 @@
       <c r="Q41" s="91"/>
     </row>
     <row r="42" spans="2:17">
-      <c r="B42" s="107" t="s">
+      <c r="B42" s="103" t="s">
         <v>102</v>
       </c>
-      <c r="C42" s="108"/>
+      <c r="C42" s="18"/>
       <c r="D42" s="78">
         <v>486366.8</v>
       </c>
@@ -4170,10 +4157,10 @@
         <v>261476.4</v>
       </c>
       <c r="M42" s="78">
-        <v>0</v>
+        <v>270584.90000000002</v>
       </c>
       <c r="N42" s="78">
-        <v>0</v>
+        <v>343811.2</v>
       </c>
       <c r="O42" s="78">
         <v>0</v>
@@ -4181,14 +4168,14 @@
       <c r="P42" s="79"/>
       <c r="Q42" s="79">
         <f t="shared" ref="Q42:Q46" si="0">SUM(D42:O42)</f>
-        <v>3938660.5</v>
+        <v>4553056.6000000006</v>
       </c>
     </row>
     <row r="43" spans="2:17">
-      <c r="B43" s="107" t="s">
+      <c r="B43" s="103" t="s">
         <v>103</v>
       </c>
-      <c r="C43" s="108"/>
+      <c r="C43" s="18"/>
       <c r="D43" s="78">
         <f>545525.1+612469.9</f>
         <v>1157995</v>
@@ -4222,14 +4209,16 @@
         <v>1065295.1000000001</v>
       </c>
       <c r="L43" s="78">
-        <f>493931+540104.7</f>
-        <v>1034035.7</v>
+        <f>493931+509475.7</f>
+        <v>1003406.7</v>
       </c>
       <c r="M43" s="78">
-        <v>0</v>
+        <f>530050.6+526738</f>
+        <v>1056788.6000000001</v>
       </c>
       <c r="N43" s="78">
-        <v>0</v>
+        <f>500495.1+423316.5</f>
+        <v>923811.6</v>
       </c>
       <c r="O43" s="78">
         <v>0</v>
@@ -4237,14 +4226,14 @@
       <c r="P43" s="79"/>
       <c r="Q43" s="79">
         <f t="shared" si="0"/>
-        <v>10302550.6</v>
+        <v>12252521.799999999</v>
       </c>
     </row>
     <row r="44" spans="2:17">
-      <c r="B44" s="107" t="s">
+      <c r="B44" s="103" t="s">
         <v>124</v>
       </c>
-      <c r="C44" s="108"/>
+      <c r="C44" s="18"/>
       <c r="D44" s="78">
         <v>911629.3</v>
       </c>
@@ -4273,10 +4262,10 @@
         <v>729109.6</v>
       </c>
       <c r="M44" s="78">
-        <v>0</v>
+        <v>802436.7</v>
       </c>
       <c r="N44" s="78">
-        <v>0</v>
+        <v>913548.9</v>
       </c>
       <c r="O44" s="78">
         <v>0</v>
@@ -4284,14 +4273,14 @@
       <c r="P44" s="79"/>
       <c r="Q44" s="79">
         <f t="shared" si="0"/>
-        <v>7363045.5999999987</v>
+        <v>9079031.1999999993</v>
       </c>
     </row>
     <row r="45" spans="2:17">
-      <c r="B45" s="107" t="s">
+      <c r="B45" s="103" t="s">
         <v>104</v>
       </c>
-      <c r="C45" s="106"/>
+      <c r="C45" s="17"/>
       <c r="D45" s="80">
         <v>295695.40000000002</v>
       </c>
@@ -4320,10 +4309,10 @@
         <v>310743.59999999998</v>
       </c>
       <c r="M45" s="80">
-        <v>0</v>
+        <v>344343.6</v>
       </c>
       <c r="N45" s="80">
-        <v>0</v>
+        <v>294435.20000000001</v>
       </c>
       <c r="O45" s="80">
         <v>0</v>
@@ -4331,16 +4320,16 @@
       <c r="P45" s="80"/>
       <c r="Q45" s="80">
         <f t="shared" si="0"/>
-        <v>2723327.5999999996</v>
+        <v>3362106.4</v>
       </c>
     </row>
     <row r="46" spans="2:17">
-      <c r="B46" s="105" t="s">
+      <c r="B46" s="102" t="s">
         <v>101</v>
       </c>
-      <c r="C46" s="106"/>
+      <c r="C46" s="17"/>
       <c r="D46" s="89">
-        <f t="shared" ref="D46:L46" si="1">SUM(D42:D45)</f>
+        <f t="shared" ref="D46:N46" si="1">SUM(D42:D45)</f>
         <v>2851686.5</v>
       </c>
       <c r="E46" s="89">
@@ -4373,13 +4362,15 @@
       </c>
       <c r="L46" s="89">
         <f t="shared" si="1"/>
-        <v>2335365.2999999998</v>
+        <v>2304736.2999999998</v>
       </c>
       <c r="M46" s="89">
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>2474153.8000000003</v>
       </c>
       <c r="N46" s="89">
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>2475606.9000000004</v>
       </c>
       <c r="O46" s="89">
         <v>0</v>
@@ -4387,12 +4378,12 @@
       <c r="P46" s="79"/>
       <c r="Q46" s="79">
         <f t="shared" si="0"/>
-        <v>24327584.300000001</v>
+        <v>29246716</v>
       </c>
     </row>
     <row r="47" spans="2:17">
-      <c r="B47" s="109"/>
-      <c r="C47" s="106"/>
+      <c r="B47" s="104"/>
+      <c r="C47" s="17"/>
       <c r="D47" s="78"/>
       <c r="E47" s="78"/>
       <c r="F47" s="78"/>
@@ -4409,13 +4400,12 @@
       <c r="Q47" s="79"/>
     </row>
     <row r="48" spans="2:17">
-      <c r="B48" s="109" t="s">
+      <c r="B48" s="104" t="s">
         <v>58</v>
       </c>
-      <c r="C48" s="110"/>
       <c r="D48" s="89">
-        <f t="shared" ref="D48:L48" si="2">D31+D32+D34+D35+D36+D38+D39+D46</f>
-        <v>5351114.4000000004</v>
+        <f t="shared" ref="D48:N48" si="2">D31+D32+D34+D35+D36+D38+D39+D46</f>
+        <v>5351175.4000000004</v>
       </c>
       <c r="E48" s="89">
         <f t="shared" si="2"/>
@@ -4439,21 +4429,23 @@
       </c>
       <c r="J48" s="89">
         <f t="shared" si="2"/>
-        <v>5157616.2000000011</v>
+        <v>5157614.4000000004</v>
       </c>
       <c r="K48" s="89">
         <f t="shared" si="2"/>
-        <v>4907161.0999999996</v>
+        <v>4907149.1999999993</v>
       </c>
       <c r="L48" s="89">
         <f t="shared" si="2"/>
-        <v>4691064.8</v>
+        <v>4547708.5</v>
       </c>
       <c r="M48" s="89">
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>4854912</v>
       </c>
       <c r="N48" s="89">
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>4972920.0999999996</v>
       </c>
       <c r="O48" s="89">
         <v>0</v>
@@ -4461,12 +4453,11 @@
       <c r="P48" s="79"/>
       <c r="Q48" s="79">
         <f>SUM(D48:O48)</f>
-        <v>44921530.000000007</v>
+        <v>54606053.100000001</v>
       </c>
     </row>
     <row r="49" spans="2:17">
-      <c r="B49" s="109"/>
-      <c r="C49" s="110"/>
+      <c r="B49" s="104"/>
       <c r="D49" s="81"/>
       <c r="E49" s="81"/>
       <c r="F49" s="81"/>
@@ -4483,10 +4474,9 @@
       <c r="Q49" s="82"/>
     </row>
     <row r="50" spans="2:17">
-      <c r="B50" s="111" t="s">
+      <c r="B50" s="105" t="s">
         <v>54</v>
       </c>
-      <c r="C50" s="110"/>
       <c r="D50" s="78">
         <v>222824.7</v>
       </c>
@@ -4506,19 +4496,19 @@
         <v>248140.7</v>
       </c>
       <c r="J50" s="78">
-        <v>243337.3</v>
+        <v>243383.2</v>
       </c>
       <c r="K50" s="78">
-        <v>251478.39999999999</v>
+        <v>251528.9</v>
       </c>
       <c r="L50" s="78">
-        <v>231730.9</v>
+        <v>231718.1</v>
       </c>
       <c r="M50" s="78">
-        <v>0</v>
+        <v>224407.2</v>
       </c>
       <c r="N50" s="78">
-        <v>0</v>
+        <v>236663.9</v>
       </c>
       <c r="O50" s="78">
         <v>0</v>
@@ -4526,14 +4516,13 @@
       <c r="P50" s="79"/>
       <c r="Q50" s="79">
         <f t="shared" ref="Q50:Q52" si="3">SUM(D50:O50)</f>
-        <v>1949028.7999999998</v>
+        <v>2410183.5</v>
       </c>
     </row>
     <row r="51" spans="2:17">
-      <c r="B51" s="109" t="s">
+      <c r="B51" s="104" t="s">
         <v>22</v>
       </c>
-      <c r="C51" s="110"/>
       <c r="D51" s="78">
         <v>124236.8</v>
       </c>
@@ -4562,10 +4551,10 @@
         <v>114977.7</v>
       </c>
       <c r="M51" s="78">
-        <v>0</v>
+        <v>108661.7</v>
       </c>
       <c r="N51" s="78">
-        <v>0</v>
+        <v>119531.3</v>
       </c>
       <c r="O51" s="78">
         <v>0</v>
@@ -4573,16 +4562,15 @@
       <c r="P51" s="79"/>
       <c r="Q51" s="79">
         <f t="shared" si="3"/>
-        <v>1033919.6</v>
+        <v>1262112.6000000001</v>
       </c>
     </row>
     <row r="52" spans="2:17">
-      <c r="B52" s="109" t="s">
+      <c r="B52" s="104" t="s">
         <v>17</v>
       </c>
-      <c r="C52" s="110"/>
       <c r="D52" s="78">
-        <v>356833.3</v>
+        <v>356845.9</v>
       </c>
       <c r="E52" s="78">
         <v>315751.2</v>
@@ -4600,19 +4588,19 @@
         <v>320348.40000000002</v>
       </c>
       <c r="J52" s="78">
-        <v>360221.1</v>
+        <v>360205</v>
       </c>
       <c r="K52" s="78">
-        <v>360029.7</v>
+        <v>360034</v>
       </c>
       <c r="L52" s="78">
-        <v>355535.7</v>
+        <v>355918.8</v>
       </c>
       <c r="M52" s="78">
-        <v>0</v>
+        <v>371758.5</v>
       </c>
       <c r="N52" s="78">
-        <v>0</v>
+        <v>375716</v>
       </c>
       <c r="O52" s="78">
         <v>0</v>
@@ -4620,78 +4608,77 @@
       <c r="P52" s="78"/>
       <c r="Q52" s="78">
         <f t="shared" si="3"/>
-        <v>3126052.3000000003</v>
+        <v>3873910.6999999997</v>
       </c>
     </row>
     <row r="53" spans="2:17" ht="14.25" customHeight="1">
-      <c r="B53" s="109"/>
-      <c r="C53" s="103"/>
-      <c r="D53" s="112"/>
-      <c r="E53" s="112"/>
-      <c r="F53" s="112"/>
-      <c r="G53" s="112"/>
-      <c r="H53" s="112"/>
-      <c r="I53" s="112"/>
-      <c r="J53" s="112"/>
-      <c r="K53" s="112"/>
-      <c r="L53" s="112"/>
-      <c r="M53" s="112"/>
-      <c r="N53" s="112"/>
-      <c r="O53" s="112"/>
-      <c r="P53" s="112"/>
-      <c r="Q53" s="113"/>
+      <c r="B53" s="104"/>
+      <c r="C53" s="101"/>
+      <c r="D53" s="109"/>
+      <c r="E53" s="109"/>
+      <c r="F53" s="109"/>
+      <c r="G53" s="109"/>
+      <c r="H53" s="109"/>
+      <c r="I53" s="109"/>
+      <c r="J53" s="109"/>
+      <c r="K53" s="109"/>
+      <c r="L53" s="109"/>
+      <c r="M53" s="109"/>
+      <c r="N53" s="109"/>
+      <c r="O53" s="109"/>
+      <c r="P53" s="109"/>
+      <c r="Q53" s="110"/>
     </row>
     <row r="54" spans="2:17" s="1" customFormat="1" ht="15" customHeight="1">
-      <c r="B54" s="109" t="s">
+      <c r="B54" s="104" t="s">
         <v>43</v>
       </c>
-      <c r="C54" s="114"/>
+      <c r="C54" s="4"/>
       <c r="D54" s="83">
-        <v>9473887.5</v>
+        <v>9474120.5</v>
       </c>
       <c r="E54" s="83">
-        <v>8863594.4000000004</v>
+        <v>8863827.3000000007</v>
       </c>
       <c r="F54" s="83">
-        <v>9169361.4000000004</v>
+        <v>9169419.5</v>
       </c>
       <c r="G54" s="83">
-        <v>10019759.199999999</v>
+        <v>10019950.800000001</v>
       </c>
       <c r="H54" s="83">
-        <v>9475705.3000000007</v>
+        <v>9475947.5999999996</v>
       </c>
       <c r="I54" s="83">
-        <v>9440385.8000000007</v>
+        <v>9440603.5999999996</v>
       </c>
       <c r="J54" s="83">
-        <v>9658787.3000000007</v>
+        <v>9659011.3000000007</v>
       </c>
       <c r="K54" s="83">
-        <v>9453248.9000000004</v>
+        <v>9453379.9000000004</v>
       </c>
       <c r="L54" s="83">
-        <v>9897857.0999999996</v>
+        <v>9791836</v>
       </c>
       <c r="M54" s="83">
-        <v>0</v>
+        <v>9498969.8000000007</v>
       </c>
       <c r="N54" s="83">
-        <v>0</v>
+        <v>9610133.3000000007</v>
       </c>
       <c r="O54" s="83">
         <v>0</v>
       </c>
       <c r="P54" s="83"/>
       <c r="Q54" s="84">
-        <v>9897857.0999999996</v>
+        <v>9610133.3000000007</v>
       </c>
     </row>
     <row r="55" spans="2:17">
-      <c r="B55" s="109" t="s">
+      <c r="B55" s="104" t="s">
         <v>50</v>
       </c>
-      <c r="C55" s="110"/>
       <c r="D55" s="78">
         <v>-242925.5</v>
       </c>
@@ -4711,19 +4698,19 @@
         <v>-312058.5</v>
       </c>
       <c r="J55" s="78">
-        <v>-289314.09999999998</v>
+        <v>-289209.3</v>
       </c>
       <c r="K55" s="78">
-        <v>-314447.40000000002</v>
+        <v>-314463.90000000002</v>
       </c>
       <c r="L55" s="78">
-        <v>-353196.1</v>
+        <v>-353094.9</v>
       </c>
       <c r="M55" s="78">
-        <v>0</v>
+        <v>-347051.8</v>
       </c>
       <c r="N55" s="78">
-        <v>0</v>
+        <v>-365331.5</v>
       </c>
       <c r="O55" s="78">
         <v>0</v>
@@ -4731,12 +4718,12 @@
       <c r="P55" s="79"/>
       <c r="Q55" s="79">
         <f>SUM(D55:O55)</f>
-        <v>-2219341.9</v>
-      </c>
-    </row>
-    <row r="56" spans="2:17" ht="15" thickBot="1">
-      <c r="B56" s="109"/>
-      <c r="C56" s="108"/>
+        <v>-2931535.6999999997</v>
+      </c>
+    </row>
+    <row r="56" spans="2:17" ht="15.75" thickBot="1">
+      <c r="B56" s="104"/>
+      <c r="C56" s="18"/>
       <c r="D56" s="85"/>
       <c r="E56" s="85"/>
       <c r="F56" s="85"/>
@@ -4752,14 +4739,13 @@
       <c r="P56" s="86"/>
       <c r="Q56" s="86"/>
     </row>
-    <row r="57" spans="2:17" ht="15" thickTop="1">
-      <c r="B57" s="115" t="s">
+    <row r="57" spans="2:17" ht="15.75" thickTop="1">
+      <c r="B57" s="59" t="s">
         <v>31</v>
       </c>
-      <c r="C57" s="110"/>
       <c r="D57" s="89">
-        <f t="shared" ref="D57:L57" si="4">D7-D54+(D28+D48)-(D50+D51+D52)+D55</f>
-        <v>25093178.399999995</v>
+        <f t="shared" ref="D57:N57" si="4">D7-D54+(D28+D48)-(D50+D51+D52)+D55</f>
+        <v>25093226.800000004</v>
       </c>
       <c r="E57" s="89">
         <f t="shared" si="4"/>
@@ -4767,37 +4753,39 @@
       </c>
       <c r="F57" s="89">
         <f t="shared" si="4"/>
-        <v>24874332.199999996</v>
+        <v>24874071.399999999</v>
       </c>
       <c r="G57" s="89">
         <f t="shared" si="4"/>
-        <v>22594462.099999998</v>
+        <v>22594678.300000001</v>
       </c>
       <c r="H57" s="89">
         <f t="shared" si="4"/>
-        <v>22331835.400000002</v>
+        <v>22331883</v>
       </c>
       <c r="I57" s="89">
         <f t="shared" si="4"/>
-        <v>23092989.300000004</v>
+        <v>23092990.200000007</v>
       </c>
       <c r="J57" s="89">
         <f t="shared" si="4"/>
-        <v>25194617.900000002</v>
+        <v>25194298.899999995</v>
       </c>
       <c r="K57" s="89">
         <f t="shared" si="4"/>
-        <v>24924165.299999997</v>
+        <v>24923631.499999996</v>
       </c>
       <c r="L57" s="89">
         <f t="shared" si="4"/>
-        <v>23282833.799999993</v>
+        <v>23246178</v>
       </c>
       <c r="M57" s="89">
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>24480479.199999996</v>
       </c>
       <c r="N57" s="89">
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>24737297.799999997</v>
       </c>
       <c r="O57" s="89">
         <v>0</v>
@@ -4805,7 +4793,7 @@
       <c r="P57" s="79"/>
       <c r="Q57" s="79">
         <f>SUM(D57:O57)</f>
-        <v>213820939.69999996</v>
+        <v>263001260.39999998</v>
       </c>
     </row>
     <row r="58" spans="2:17">
@@ -4830,24 +4818,24 @@
         <v>129</v>
       </c>
       <c r="C59" s="4"/>
-      <c r="D59" s="101"/>
-      <c r="E59" s="101"/>
-      <c r="F59" s="101"/>
-      <c r="G59" s="101"/>
-      <c r="H59" s="101"/>
-      <c r="I59" s="101"/>
-      <c r="J59" s="101"/>
-      <c r="K59" s="101"/>
-      <c r="L59" s="101"/>
-      <c r="M59" s="101"/>
-      <c r="N59" s="101"/>
-      <c r="O59" s="101"/>
-      <c r="P59" s="101"/>
-      <c r="Q59" s="102" t="s">
+      <c r="D59" s="106"/>
+      <c r="E59" s="106"/>
+      <c r="F59" s="106"/>
+      <c r="G59" s="106"/>
+      <c r="H59" s="106"/>
+      <c r="I59" s="106"/>
+      <c r="J59" s="106"/>
+      <c r="K59" s="106"/>
+      <c r="L59" s="106"/>
+      <c r="M59" s="106"/>
+      <c r="N59" s="106"/>
+      <c r="O59" s="106"/>
+      <c r="P59" s="106"/>
+      <c r="Q59" s="107" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="60" spans="2:17" ht="15.6">
+    <row r="60" spans="2:17" ht="15.75">
       <c r="B60" s="48"/>
       <c r="D60" s="92" t="s">
         <v>1</v>
@@ -4961,17 +4949,17 @@
         <v>29883.9</v>
       </c>
       <c r="M63" s="90">
-        <v>0</v>
+        <v>39119.1</v>
       </c>
       <c r="N63" s="90">
-        <v>0</v>
+        <v>61762.700000000004</v>
       </c>
       <c r="O63" s="90">
         <v>0</v>
       </c>
       <c r="P63" s="91"/>
       <c r="Q63" s="91">
-        <v>461013.4</v>
+        <v>561895.19999999995</v>
       </c>
     </row>
     <row r="64" spans="2:17">
@@ -4997,26 +4985,26 @@
         <v>2219657.5</v>
       </c>
       <c r="J64" s="90">
-        <v>2567045.2000000002</v>
+        <v>2566376.4</v>
       </c>
       <c r="K64" s="90">
-        <v>2556409</v>
+        <v>2555429.5</v>
       </c>
       <c r="L64" s="90">
         <v>2204194.6</v>
       </c>
       <c r="M64" s="90">
-        <v>0</v>
+        <v>2374998.4</v>
       </c>
       <c r="N64" s="90">
-        <v>0</v>
+        <v>2488340.2000000002</v>
       </c>
       <c r="O64" s="90">
         <v>0</v>
       </c>
       <c r="P64" s="91"/>
       <c r="Q64" s="91">
-        <v>21026046.200000003</v>
+        <v>25887736.5</v>
       </c>
     </row>
     <row r="65" spans="2:17">
@@ -5033,35 +5021,35 @@
         <v>14432.6</v>
       </c>
       <c r="G65" s="90">
-        <v>15261.8</v>
+        <v>15264.8</v>
       </c>
       <c r="H65" s="90">
         <v>11089.6</v>
       </c>
       <c r="I65" s="90">
-        <v>11993</v>
+        <v>11995.6</v>
       </c>
       <c r="J65" s="90">
-        <v>9755.1</v>
+        <v>9807.5</v>
       </c>
       <c r="K65" s="90">
-        <v>12737.5</v>
+        <v>12739</v>
       </c>
       <c r="L65" s="90">
-        <v>12328.8</v>
+        <v>12332.5</v>
       </c>
       <c r="M65" s="90">
-        <v>0</v>
+        <v>17819</v>
       </c>
       <c r="N65" s="90">
-        <v>0</v>
+        <v>15381.7</v>
       </c>
       <c r="O65" s="90">
         <v>0</v>
       </c>
       <c r="P65" s="91"/>
       <c r="Q65" s="91">
-        <v>107400.10000000002</v>
+        <v>140664</v>
       </c>
     </row>
     <row r="66" spans="2:17">
@@ -5087,26 +5075,26 @@
         <v>13665.6</v>
       </c>
       <c r="J66" s="90">
-        <v>15916.7</v>
+        <v>15915.7</v>
       </c>
       <c r="K66" s="90">
-        <v>20032.7</v>
+        <v>20187.5</v>
       </c>
       <c r="L66" s="90">
-        <v>21388</v>
+        <v>21007.4</v>
       </c>
       <c r="M66" s="90">
-        <v>0</v>
+        <v>18338.400000000001</v>
       </c>
       <c r="N66" s="90">
-        <v>0</v>
+        <v>44372.6</v>
       </c>
       <c r="O66" s="90">
         <v>0</v>
       </c>
       <c r="P66" s="91"/>
       <c r="Q66" s="91">
-        <v>156606.40000000002</v>
+        <v>219090.6</v>
       </c>
     </row>
     <row r="67" spans="2:17" s="1" customFormat="1">
@@ -5142,7 +5130,7 @@
         <v>0</v>
       </c>
       <c r="M67" s="90">
-        <v>0</v>
+        <v>162</v>
       </c>
       <c r="N67" s="90">
         <v>0</v>
@@ -5152,7 +5140,7 @@
       </c>
       <c r="P67" s="91"/>
       <c r="Q67" s="93">
-        <v>885.80000000000007</v>
+        <v>1047.8000000000002</v>
       </c>
     </row>
     <row r="68" spans="2:17" s="1" customFormat="1">
@@ -5167,38 +5155,38 @@
         <v>20718</v>
       </c>
       <c r="F68" s="90">
-        <v>-740.2</v>
+        <v>-218.6</v>
       </c>
       <c r="G68" s="90">
-        <v>1166.4000000000001</v>
+        <v>740</v>
       </c>
       <c r="H68" s="90">
-        <v>11802.6</v>
+        <v>11707.4</v>
       </c>
       <c r="I68" s="90">
-        <v>12868.6</v>
+        <v>12872</v>
       </c>
       <c r="J68" s="90">
-        <v>7326.2</v>
+        <v>6761.6</v>
       </c>
       <c r="K68" s="90">
-        <v>-8589</v>
+        <v>-9240.4</v>
       </c>
       <c r="L68" s="90">
-        <v>-12098.5</v>
+        <v>-10297.9</v>
       </c>
       <c r="M68" s="90">
-        <v>0</v>
+        <v>2236.9</v>
       </c>
       <c r="N68" s="90">
-        <v>0</v>
+        <v>-15294.4</v>
       </c>
       <c r="O68" s="90">
         <v>0</v>
       </c>
       <c r="P68" s="91"/>
       <c r="Q68" s="90">
-        <v>21738.699999999997</v>
+        <v>9269.1999999999989</v>
       </c>
     </row>
     <row r="69" spans="2:17">
@@ -5207,7 +5195,7 @@
       </c>
       <c r="C69" s="19"/>
       <c r="D69" s="90">
-        <v>347243.9</v>
+        <v>347304.9</v>
       </c>
       <c r="E69" s="90">
         <v>276205.40000000002</v>
@@ -5231,20 +5219,20 @@
         <v>327118</v>
       </c>
       <c r="L69" s="90">
-        <v>345715.7</v>
+        <v>345747.4</v>
       </c>
       <c r="M69" s="90">
-        <v>0</v>
+        <v>347549.2</v>
       </c>
       <c r="N69" s="90">
-        <v>0</v>
+        <v>352742.3</v>
       </c>
       <c r="O69" s="90">
         <v>0</v>
       </c>
       <c r="P69" s="91"/>
       <c r="Q69" s="91">
-        <v>2682091.8000000003</v>
+        <v>3382476</v>
       </c>
     </row>
     <row r="70" spans="2:17">
@@ -5253,44 +5241,44 @@
       </c>
       <c r="C70" s="19"/>
       <c r="D70" s="90">
-        <v>2951258.8000000003</v>
+        <v>2951319.8000000003</v>
       </c>
       <c r="E70" s="90">
         <v>2689459.4000000004</v>
       </c>
       <c r="F70" s="90">
-        <v>2957103.8999999994</v>
+        <v>2957625.4999999995</v>
       </c>
       <c r="G70" s="90">
-        <v>2503314.9999999995</v>
+        <v>2502891.5999999996</v>
       </c>
       <c r="H70" s="90">
-        <v>2245371.2999999998</v>
+        <v>2245276.0999999996</v>
       </c>
       <c r="I70" s="90">
-        <v>2525546.2000000002</v>
+        <v>2525552.2000000002</v>
       </c>
       <c r="J70" s="90">
-        <v>3023957.6000000006</v>
+        <v>3022775.6</v>
       </c>
       <c r="K70" s="90">
-        <v>2958357.7</v>
+        <v>2956883.1</v>
       </c>
       <c r="L70" s="90">
-        <v>2601412.5</v>
+        <v>2602867.9</v>
       </c>
       <c r="M70" s="90">
-        <v>0</v>
+        <v>2800223</v>
       </c>
       <c r="N70" s="90">
-        <v>0</v>
+        <v>2947305.1000000006</v>
       </c>
       <c r="O70" s="90">
         <v>0</v>
       </c>
       <c r="P70" s="91"/>
       <c r="Q70" s="91">
-        <v>24455782.400000002</v>
+        <v>30202179.300000004</v>
       </c>
     </row>
     <row r="71" spans="2:17">
@@ -5341,20 +5329,20 @@
         <v>21920104.800000001</v>
       </c>
       <c r="L72" s="78">
-        <v>20416525.699999999</v>
+        <v>20411543.699999999</v>
       </c>
       <c r="M72" s="78">
-        <v>0</v>
+        <v>21508636.300000001</v>
       </c>
       <c r="N72" s="78">
-        <v>0</v>
+        <v>21681086.699999999</v>
       </c>
       <c r="O72" s="78">
         <v>0</v>
       </c>
       <c r="P72" s="79"/>
       <c r="Q72" s="79">
-        <v>186856245.59999999</v>
+        <v>230040986.59999999</v>
       </c>
     </row>
     <row r="73" spans="2:17">
@@ -5387,20 +5375,20 @@
         <v>707100.15483870974</v>
       </c>
       <c r="L73" s="78">
-        <v>680550.85666666669</v>
+        <v>680384.78999999992</v>
       </c>
       <c r="M73" s="78">
-        <v>0</v>
+        <v>693826.97741935484</v>
       </c>
       <c r="N73" s="78">
-        <v>0</v>
+        <v>722702.89</v>
       </c>
       <c r="O73" s="78">
         <v>0</v>
       </c>
       <c r="P73" s="79"/>
       <c r="Q73" s="79">
-        <v>684471.68497098482</v>
+        <v>688782.63322650467</v>
       </c>
     </row>
     <row r="74" spans="2:17">
@@ -5425,10 +5413,10 @@
       <c r="B75" s="60" t="s">
         <v>0</v>
       </c>
-      <c r="C75" s="106"/>
+      <c r="C75" s="17"/>
       <c r="D75" s="89">
-        <f t="shared" ref="D75:L75" si="5">D57-(D70+D72)</f>
-        <v>378320.09999999404</v>
+        <f t="shared" ref="D75:N75" si="5">D57-(D70+D72)</f>
+        <v>378307.50000000373</v>
       </c>
       <c r="E75" s="89">
         <f t="shared" si="5"/>
@@ -5436,55 +5424,57 @@
       </c>
       <c r="F75" s="89">
         <f t="shared" si="5"/>
-        <v>339313.89999999851</v>
+        <v>338531.5</v>
       </c>
       <c r="G75" s="89">
         <f t="shared" si="5"/>
-        <v>421417.79999999702</v>
+        <v>422057.40000000224</v>
       </c>
       <c r="H75" s="89">
         <f t="shared" si="5"/>
-        <v>179881</v>
+        <v>180023.79999999702</v>
       </c>
       <c r="I75" s="89">
         <f t="shared" si="5"/>
-        <v>284350.00000000373</v>
+        <v>284344.90000000596</v>
       </c>
       <c r="J75" s="89">
         <f t="shared" si="5"/>
-        <v>443031.69999999925</v>
+        <v>443894.6999999918</v>
       </c>
       <c r="K75" s="89">
         <f t="shared" si="5"/>
-        <v>45702.79999999702</v>
+        <v>46643.59999999404</v>
       </c>
       <c r="L75" s="89">
         <f t="shared" si="5"/>
-        <v>264895.59999999404</v>
+        <v>231766.40000000224</v>
       </c>
       <c r="M75" s="89">
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>171619.89999999478</v>
       </c>
       <c r="N75" s="89">
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>108905.99999999627</v>
       </c>
       <c r="O75" s="89">
         <v>0</v>
       </c>
       <c r="P75" s="79"/>
-      <c r="Q75" s="91">
+      <c r="Q75" s="79">
         <f>SUM(D75:O75)</f>
-        <v>2508911.6999999844</v>
+        <v>2758094.4999999888</v>
       </c>
     </row>
     <row r="76" spans="2:17">
       <c r="B76" s="62" t="s">
         <v>45</v>
       </c>
-      <c r="C76" s="108"/>
+      <c r="C76" s="18"/>
       <c r="D76" s="94">
-        <f t="shared" ref="D76:L76" si="6">IF(D57&gt;0,D75/D57,"")</f>
-        <v>1.5076611418822659E-2</v>
+        <f t="shared" ref="D76:N76" si="6">IF(D57&gt;0,D75/D57,"")</f>
+        <v>1.5076080211414008E-2</v>
       </c>
       <c r="E76" s="94">
         <f t="shared" si="6"/>
@@ -5492,37 +5482,39 @@
       </c>
       <c r="F76" s="94">
         <f t="shared" si="6"/>
-        <v>1.3641126011817056E-2</v>
+        <v>1.3609814595933018E-2</v>
       </c>
       <c r="G76" s="94">
         <f t="shared" si="6"/>
-        <v>1.8651375639519963E-2</v>
+        <v>1.8679504722136371E-2</v>
       </c>
       <c r="H76" s="94">
         <f t="shared" si="6"/>
-        <v>8.0549133905939499E-3</v>
+        <v>8.0612906668012293E-3</v>
       </c>
       <c r="I76" s="94">
         <f t="shared" si="6"/>
-        <v>1.231326080422181E-2</v>
+        <v>1.2313039478101275E-2</v>
       </c>
       <c r="J76" s="94">
         <f t="shared" si="6"/>
-        <v>1.7584378606511797E-2</v>
+        <v>1.761885503390578E-2</v>
       </c>
       <c r="K76" s="94">
         <f t="shared" si="6"/>
-        <v>1.8336742454519439E-3</v>
+        <v>1.8714608262441227E-3</v>
       </c>
       <c r="L76" s="94">
         <f t="shared" si="6"/>
-        <v>1.1377292054543383E-2</v>
-      </c>
-      <c r="M76" s="94" t="s">
-        <v>128</v>
-      </c>
-      <c r="N76" s="94" t="s">
-        <v>128</v>
+        <v>9.9700862653638051E-3</v>
+      </c>
+      <c r="M76" s="94">
+        <f t="shared" si="6"/>
+        <v>7.0104795987814984E-3</v>
+      </c>
+      <c r="N76" s="94">
+        <f t="shared" si="6"/>
+        <v>4.4025018771450567E-3</v>
       </c>
       <c r="O76" s="94" t="s">
         <v>128</v>
@@ -5530,11 +5522,11 @@
       <c r="P76" s="94"/>
       <c r="Q76" s="79">
         <f>AVERAGE(D76:O76)</f>
-        <v>1.1700939360097503E-2</v>
-      </c>
-    </row>
-    <row r="77" spans="2:17" ht="15" thickBot="1">
-      <c r="B77" s="109"/>
+        <v>1.048990321320192E-2</v>
+      </c>
+    </row>
+    <row r="77" spans="2:17" ht="15.75" thickBot="1">
+      <c r="B77" s="104"/>
       <c r="C77" s="26"/>
       <c r="D77" s="87"/>
       <c r="E77" s="87"/>
@@ -5551,14 +5543,13 @@
       <c r="P77" s="79"/>
       <c r="Q77" s="88"/>
     </row>
-    <row r="78" spans="2:17" ht="15" thickTop="1">
-      <c r="B78" s="115" t="s">
+    <row r="78" spans="2:17" ht="15.75" thickTop="1">
+      <c r="B78" s="59" t="s">
         <v>36</v>
       </c>
-      <c r="C78" s="110"/>
       <c r="D78" s="89">
-        <f t="shared" ref="D78:L78" si="7">(D70+D72)+D75</f>
-        <v>25093178.399999995</v>
+        <f t="shared" ref="D78:N78" si="7">(D70+D72)+D75</f>
+        <v>25093226.800000004</v>
       </c>
       <c r="E78" s="89">
         <f t="shared" si="7"/>
@@ -5566,45 +5557,47 @@
       </c>
       <c r="F78" s="89">
         <f t="shared" si="7"/>
-        <v>24874332.199999996</v>
+        <v>24874071.399999999</v>
       </c>
       <c r="G78" s="89">
         <f t="shared" si="7"/>
-        <v>22594462.099999998</v>
+        <v>22594678.300000001</v>
       </c>
       <c r="H78" s="89">
         <f t="shared" si="7"/>
-        <v>22331835.400000002</v>
+        <v>22331883</v>
       </c>
       <c r="I78" s="89">
         <f t="shared" si="7"/>
-        <v>23092989.300000004</v>
+        <v>23092990.200000007</v>
       </c>
       <c r="J78" s="89">
         <f t="shared" si="7"/>
-        <v>25194617.900000002</v>
+        <v>25194298.899999995</v>
       </c>
       <c r="K78" s="89">
         <f t="shared" si="7"/>
-        <v>24924165.299999997</v>
+        <v>24923631.499999996</v>
       </c>
       <c r="L78" s="89">
         <f t="shared" si="7"/>
-        <v>23282833.799999993</v>
+        <v>23246178</v>
       </c>
       <c r="M78" s="89">
-        <v>0</v>
+        <f t="shared" si="7"/>
+        <v>24480479.199999996</v>
       </c>
       <c r="N78" s="89">
-        <v>0</v>
+        <f t="shared" si="7"/>
+        <v>24737297.799999997</v>
       </c>
       <c r="O78" s="89">
         <v>0</v>
       </c>
       <c r="P78" s="79"/>
       <c r="Q78" s="79">
-        <f t="shared" ref="Q78" si="8">SUM(D78:O78)</f>
-        <v>213820939.69999996</v>
+        <f>SUM(D78:O78)</f>
+        <v>263001260.39999998</v>
       </c>
     </row>
     <row r="79" spans="2:17">
@@ -5709,15 +5702,15 @@
       <c r="D86" s="12"/>
       <c r="Q86" s="91"/>
     </row>
-    <row r="87" spans="2:17" ht="15.6">
+    <row r="87" spans="2:17" ht="15.75">
       <c r="B87" s="35"/>
       <c r="D87" s="12"/>
       <c r="Q87" s="91"/>
     </row>
-    <row r="88" spans="2:17" ht="15.6">
+    <row r="88" spans="2:17" ht="15.75">
       <c r="B88" s="35"/>
     </row>
-    <row r="89" spans="2:17" ht="15.6">
+    <row r="89" spans="2:17" ht="15.75">
       <c r="B89" s="35"/>
     </row>
   </sheetData>

--- a/Oil_current.xlsx
+++ b/Oil_current.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="V:\Information Management\Info Sharing and Tracking\Product Services\Operations\Product Creation\ST3\ST3s_Report_Prep\All_Pages_Content_Update\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F475B57-7982-4BE7-9A9B-7D860B43BBCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53361852-8627-4CE6-AC20-813D2C329BA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-19310" yWindow="1390" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="16440" windowHeight="28320" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Documentation" sheetId="21" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="129">
   <si>
     <t>Reporting Adjustment</t>
   </si>
@@ -476,10 +476,7 @@
     <t>2025</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
-    <t xml:space="preserve"> Run Date:  29 December 2025</t>
+    <t xml:space="preserve"> Run Date:  27 January 2026</t>
   </si>
 </sst>
 </file>
@@ -1510,17 +1507,17 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:BK84"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
     <col min="2" max="2" width="43" customWidth="1"/>
-    <col min="3" max="3" width="3.85546875" customWidth="1"/>
-    <col min="4" max="15" width="14.5703125" customWidth="1"/>
-    <col min="16" max="16" width="1.5703125" customWidth="1"/>
+    <col min="3" max="3" width="3.88671875" customWidth="1"/>
+    <col min="4" max="15" width="14.5546875" customWidth="1"/>
+    <col min="16" max="16" width="1.5546875" customWidth="1"/>
     <col min="17" max="17" width="17" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" customWidth="1"/>
-    <col min="21" max="21" width="20.28515625" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.5546875" customWidth="1"/>
+    <col min="21" max="21" width="20.33203125" customWidth="1"/>
+    <col min="22" max="22" width="14.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:63" s="2" customFormat="1" ht="20.25" customHeight="1">
@@ -2496,7 +2493,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="56" spans="1:19" ht="15.75" thickBot="1">
+    <row r="56" spans="1:19" ht="15" thickBot="1">
       <c r="B56" s="50"/>
       <c r="C56" s="17"/>
       <c r="D56" s="69"/>
@@ -2513,7 +2510,7 @@
       <c r="O56" s="25"/>
       <c r="Q56" s="25"/>
     </row>
-    <row r="57" spans="1:19" ht="15.75" thickTop="1">
+    <row r="57" spans="1:19" ht="15" thickTop="1">
       <c r="B57" s="59" t="s">
         <v>31</v>
       </c>
@@ -2735,7 +2732,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="77" spans="2:17" ht="15.75" thickBot="1">
+    <row r="77" spans="2:17" ht="15" thickBot="1">
       <c r="B77" s="50"/>
       <c r="C77" s="19"/>
       <c r="D77" s="69"/>
@@ -2752,7 +2749,7 @@
       <c r="O77" s="25"/>
       <c r="Q77" s="25"/>
     </row>
-    <row r="78" spans="2:17" ht="15.75" thickTop="1">
+    <row r="78" spans="2:17" ht="15" thickTop="1">
       <c r="B78" s="59" t="s">
         <v>36</v>
       </c>
@@ -2806,16 +2803,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:V89"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
-    <col min="2" max="2" width="44.7109375" customWidth="1"/>
+    <col min="2" max="2" width="44.6640625" customWidth="1"/>
     <col min="3" max="3" width="4" customWidth="1"/>
-    <col min="4" max="13" width="15.7109375" customWidth="1"/>
-    <col min="14" max="14" width="15.85546875" customWidth="1"/>
-    <col min="15" max="15" width="15.7109375" customWidth="1"/>
-    <col min="16" max="16" width="1.5703125" customWidth="1"/>
-    <col min="17" max="17" width="19.42578125" customWidth="1"/>
+    <col min="4" max="13" width="15.6640625" customWidth="1"/>
+    <col min="14" max="14" width="15.88671875" customWidth="1"/>
+    <col min="15" max="15" width="15.6640625" customWidth="1"/>
+    <col min="16" max="16" width="1.5546875" customWidth="1"/>
+    <col min="17" max="17" width="19.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:22" s="2" customFormat="1" ht="20.25" customHeight="1">
@@ -2843,7 +2840,7 @@
     </row>
     <row r="4" spans="2:22" ht="22.5" customHeight="1">
       <c r="B4" s="47" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C4" s="22"/>
       <c r="D4" s="1"/>
@@ -2943,16 +2940,16 @@
         <v>9659011.3000000007</v>
       </c>
       <c r="L7" s="16">
-        <v>9453269.9000000004</v>
+        <v>9453273.0999999996</v>
       </c>
       <c r="M7" s="16">
-        <v>9791836</v>
+        <v>9791845.5</v>
       </c>
       <c r="N7" s="16">
-        <v>9498595.5</v>
+        <v>9498732.8000000007</v>
       </c>
       <c r="O7" s="16">
-        <v>0</v>
+        <v>9610374.5</v>
       </c>
       <c r="P7" s="8"/>
       <c r="Q7" s="91">
@@ -3023,41 +3020,41 @@
         <v>1500578.1</v>
       </c>
       <c r="E11" s="16">
-        <v>1369310.1</v>
+        <v>1369675.6</v>
       </c>
       <c r="F11" s="16">
-        <v>1586346.7</v>
+        <v>1586784.1</v>
       </c>
       <c r="G11" s="16">
-        <v>1554035</v>
+        <v>1553184.7</v>
       </c>
       <c r="H11" s="16">
-        <v>1561687.6</v>
+        <v>1560708.5</v>
       </c>
       <c r="I11" s="16">
-        <v>1500419.7</v>
+        <v>1499376</v>
       </c>
       <c r="J11" s="16">
-        <v>1573026.5</v>
+        <v>1569168.3</v>
       </c>
       <c r="K11" s="16">
-        <v>1583247.8</v>
+        <v>1576344.3</v>
       </c>
       <c r="L11" s="16">
-        <v>1503127</v>
+        <v>1494898.5</v>
       </c>
       <c r="M11" s="16">
-        <v>1613400.3</v>
+        <v>1602745.2</v>
       </c>
       <c r="N11" s="16">
-        <v>1625997.7</v>
+        <v>1625857.9</v>
       </c>
       <c r="O11" s="16">
-        <v>0</v>
+        <v>1635881.4</v>
       </c>
       <c r="P11" s="8"/>
       <c r="Q11" s="91">
-        <v>16971176.5</v>
+        <v>18575202.599999998</v>
       </c>
     </row>
     <row r="12" spans="2:22" s="1" customFormat="1">
@@ -3075,35 +3072,35 @@
         <v>388112.1</v>
       </c>
       <c r="G12" s="16">
-        <v>377949.5</v>
+        <v>379080.8</v>
       </c>
       <c r="H12" s="16">
-        <v>378470.3</v>
+        <v>379743.2</v>
       </c>
       <c r="I12" s="16">
-        <v>349360.7</v>
+        <v>350621.8</v>
       </c>
       <c r="J12" s="16">
-        <v>361290.3</v>
+        <v>362398.9</v>
       </c>
       <c r="K12" s="16">
-        <v>358283.9</v>
+        <v>359084.2</v>
       </c>
       <c r="L12" s="16">
-        <v>349318.3</v>
+        <v>349643.3</v>
       </c>
       <c r="M12" s="16">
-        <v>355715.6</v>
+        <v>357522.1</v>
       </c>
       <c r="N12" s="16">
-        <v>347065.59999999998</v>
+        <v>340435.1</v>
       </c>
       <c r="O12" s="16">
-        <v>0</v>
+        <v>328051.40000000002</v>
       </c>
       <c r="P12" s="8"/>
       <c r="Q12" s="91">
-        <v>3978593.4999999995</v>
+        <v>4307720.0999999996</v>
       </c>
     </row>
     <row r="13" spans="2:22">
@@ -3111,44 +3108,44 @@
         <v>27</v>
       </c>
       <c r="D13" s="90">
-        <v>178514.1</v>
+        <v>178444.4</v>
       </c>
       <c r="E13" s="16">
-        <v>160436.5</v>
+        <v>159299.5</v>
       </c>
       <c r="F13" s="16">
-        <v>186608.6</v>
+        <v>184812.5</v>
       </c>
       <c r="G13" s="16">
-        <v>174999.1</v>
+        <v>173392.2</v>
       </c>
       <c r="H13" s="16">
-        <v>180036.2</v>
+        <v>178129.2</v>
       </c>
       <c r="I13" s="16">
-        <v>169476.7</v>
+        <v>167733.9</v>
       </c>
       <c r="J13" s="16">
-        <v>172138.2</v>
+        <v>172540.5</v>
       </c>
       <c r="K13" s="16">
-        <v>171129.3</v>
+        <v>172815.3</v>
       </c>
       <c r="L13" s="16">
-        <v>163010</v>
+        <v>163800.6</v>
       </c>
       <c r="M13" s="16">
-        <v>168484.4</v>
+        <v>170156</v>
       </c>
       <c r="N13" s="16">
-        <v>162856.4</v>
+        <v>164220.1</v>
       </c>
       <c r="O13" s="16">
-        <v>0</v>
+        <v>166056.20000000001</v>
       </c>
       <c r="P13" s="8"/>
       <c r="Q13" s="91">
-        <v>1887689.4999999998</v>
+        <v>2051400.4000000004</v>
       </c>
     </row>
     <row r="14" spans="2:22">
@@ -3156,44 +3153,44 @@
         <v>122</v>
       </c>
       <c r="D14" s="96">
-        <v>652946.69999999995</v>
+        <v>653016.4</v>
       </c>
       <c r="E14" s="76">
-        <v>586029.5</v>
+        <v>587166.5</v>
       </c>
       <c r="F14" s="76">
-        <v>648942.30000000005</v>
+        <v>650738.4</v>
       </c>
       <c r="G14" s="75">
-        <v>627743</v>
+        <v>629349.9</v>
       </c>
       <c r="H14" s="75">
-        <v>637325.9</v>
+        <v>639232.9</v>
       </c>
       <c r="I14" s="75">
-        <v>624375.9</v>
+        <v>626145</v>
       </c>
       <c r="J14" s="75">
-        <v>638371.4</v>
+        <v>640963</v>
       </c>
       <c r="K14" s="75">
-        <v>634514.69999999995</v>
+        <v>639167.30000000005</v>
       </c>
       <c r="L14" s="75">
-        <v>620250</v>
+        <v>627583.9</v>
       </c>
       <c r="M14" s="75">
-        <v>630133</v>
+        <v>637304.80000000005</v>
       </c>
       <c r="N14" s="75">
-        <v>620862.5</v>
+        <v>626405.9</v>
       </c>
       <c r="O14" s="75">
-        <v>0</v>
+        <v>628495</v>
       </c>
       <c r="P14" s="76"/>
       <c r="Q14" s="96">
-        <v>6921494.9000000004</v>
+        <v>7585569</v>
       </c>
     </row>
     <row r="15" spans="2:22" s="1" customFormat="1">
@@ -3201,44 +3198,44 @@
         <v>114</v>
       </c>
       <c r="D15" s="90">
-        <v>2710608.4000000004</v>
+        <v>2710608.4</v>
       </c>
       <c r="E15" s="16">
-        <v>2450233.7999999998</v>
+        <v>2450599.2999999998</v>
       </c>
       <c r="F15" s="16">
-        <v>2810009.7</v>
+        <v>2810447.1</v>
       </c>
       <c r="G15" s="16">
-        <v>2734726.6</v>
+        <v>2735007.6</v>
       </c>
       <c r="H15" s="16">
-        <v>2757520</v>
+        <v>2757813.8</v>
       </c>
       <c r="I15" s="16">
-        <v>2643633</v>
+        <v>2643876.7000000002</v>
       </c>
       <c r="J15" s="16">
-        <v>2744826.4</v>
+        <v>2745070.7</v>
       </c>
       <c r="K15" s="16">
-        <v>2747175.7</v>
+        <v>2747411.0999999996</v>
       </c>
       <c r="L15" s="16">
-        <v>2635705.2999999998</v>
+        <v>2635926.3000000003</v>
       </c>
       <c r="M15" s="16">
-        <v>2767733.3</v>
+        <v>2767728.0999999996</v>
       </c>
       <c r="N15" s="16">
-        <v>2756782.1999999997</v>
+        <v>2756919</v>
       </c>
       <c r="O15" s="16">
-        <v>0</v>
+        <v>2758484</v>
       </c>
       <c r="P15" s="8"/>
       <c r="Q15" s="91">
-        <v>29758954.399999999</v>
+        <v>32519892.099999994</v>
       </c>
     </row>
     <row r="16" spans="2:22" s="1" customFormat="1">
@@ -3275,7 +3272,7 @@
         <v>419757.4</v>
       </c>
       <c r="H17" s="16">
-        <v>440859.9</v>
+        <v>440827.4</v>
       </c>
       <c r="I17" s="16">
         <v>385598.9</v>
@@ -3290,17 +3287,17 @@
         <v>426799.5</v>
       </c>
       <c r="M17" s="16">
-        <v>444218.9</v>
+        <v>444022.8</v>
       </c>
       <c r="N17" s="16">
-        <v>480521.8</v>
+        <v>480571.3</v>
       </c>
       <c r="O17" s="16">
-        <v>0</v>
+        <v>488005.3</v>
       </c>
       <c r="P17" s="8"/>
       <c r="Q17" s="91">
-        <v>4617053.3999999994</v>
+        <v>5104879.5999999996</v>
       </c>
     </row>
     <row r="18" spans="2:17">
@@ -3367,41 +3364,41 @@
         <v>9633084.1999999993</v>
       </c>
       <c r="E21" s="16">
-        <v>8586573.6999999993</v>
+        <v>8586208.1999999993</v>
       </c>
       <c r="F21" s="16">
-        <v>9674228.9000000004</v>
+        <v>9673791.5</v>
       </c>
       <c r="G21" s="16">
-        <v>9111404.8000000007</v>
+        <v>9111123.8000000007</v>
       </c>
       <c r="H21" s="16">
-        <v>8858833.8000000007</v>
+        <v>8858540</v>
       </c>
       <c r="I21" s="16">
-        <v>8756491.5</v>
+        <v>8756247.8000000007</v>
       </c>
       <c r="J21" s="16">
-        <v>9732291.5</v>
+        <v>9732047.1999999993</v>
       </c>
       <c r="K21" s="16">
-        <v>9668037.9000000004</v>
+        <v>9667805.6999999993</v>
       </c>
       <c r="L21" s="16">
-        <v>9195188</v>
+        <v>9194973.3000000007</v>
       </c>
       <c r="M21" s="16">
-        <v>9721119.0999999996</v>
+        <v>9720914.0999999996</v>
       </c>
       <c r="N21" s="16">
-        <v>9611281.1999999993</v>
+        <v>9611151.0999999996</v>
       </c>
       <c r="O21" s="16">
-        <v>0</v>
+        <v>9824155.8000000007</v>
       </c>
       <c r="P21" s="8"/>
       <c r="Q21" s="91">
-        <v>102548534.59999999</v>
+        <v>112370042.69999999</v>
       </c>
     </row>
     <row r="22" spans="2:17">
@@ -3443,11 +3440,11 @@
         <v>9090317.3000000007</v>
       </c>
       <c r="O22" s="16">
-        <v>0</v>
+        <v>9660103.4000000004</v>
       </c>
       <c r="P22" s="8"/>
       <c r="Q22" s="91">
-        <v>92892768.400000006</v>
+        <v>102552871.80000001</v>
       </c>
     </row>
     <row r="23" spans="2:17">
@@ -3489,11 +3486,11 @@
         <v>-8027360.0999999996</v>
       </c>
       <c r="O23" s="16">
-        <v>0</v>
+        <v>-7890512.2000000002</v>
       </c>
       <c r="P23" s="8"/>
       <c r="Q23" s="91">
-        <v>-79967384.600000009</v>
+        <v>-87857896.800000012</v>
       </c>
     </row>
     <row r="24" spans="2:17">
@@ -3505,41 +3502,41 @@
         <v>10491031.300000001</v>
       </c>
       <c r="E24" s="16">
-        <v>9086275.4000000004</v>
+        <v>9085909.9000000004</v>
       </c>
       <c r="F24" s="16">
-        <v>10716658.600000001</v>
+        <v>10716221.199999999</v>
       </c>
       <c r="G24" s="16">
-        <v>10284240.900000002</v>
+        <v>10283959.900000002</v>
       </c>
       <c r="H24" s="16">
-        <v>9974978.9000000004</v>
+        <v>9974685.0999999996</v>
       </c>
       <c r="I24" s="16">
-        <v>10633013.200000001</v>
+        <v>10632769.500000002</v>
       </c>
       <c r="J24" s="16">
-        <v>11382706.1</v>
+        <v>11382461.799999999</v>
       </c>
       <c r="K24" s="16">
-        <v>10964880.500000002</v>
+        <v>10964648.299999999</v>
       </c>
       <c r="L24" s="16">
-        <v>10789601.699999999</v>
+        <v>10789387.000000004</v>
       </c>
       <c r="M24" s="16">
-        <v>10476293.399999997</v>
+        <v>10476088.399999997</v>
       </c>
       <c r="N24" s="16">
-        <v>10674238.4</v>
+        <v>10674108.299999999</v>
       </c>
       <c r="O24" s="16">
-        <v>0</v>
+        <v>11593747.000000004</v>
       </c>
       <c r="P24" s="8"/>
       <c r="Q24" s="91">
-        <v>115473918.39999999</v>
+        <v>127065017.69999999</v>
       </c>
     </row>
     <row r="25" spans="2:17">
@@ -3577,14 +3574,14 @@
         <v>6696334.5999999996</v>
       </c>
       <c r="N25" s="42">
-        <v>7061615.7999999998</v>
+        <v>7052006.7999999998</v>
       </c>
       <c r="O25" s="42">
-        <v>0</v>
+        <v>6867080.5</v>
       </c>
       <c r="P25" s="8"/>
       <c r="Q25" s="98">
-        <v>69130033.400000006</v>
+        <v>75987504.900000006</v>
       </c>
     </row>
     <row r="26" spans="2:17">
@@ -3595,41 +3592,41 @@
         <v>17532598.5</v>
       </c>
       <c r="E26" s="16">
-        <v>15073567.600000001</v>
+        <v>15073202.100000001</v>
       </c>
       <c r="F26" s="16">
-        <v>17459334.700000003</v>
+        <v>17458897.299999997</v>
       </c>
       <c r="G26" s="16">
-        <v>15932065.000000002</v>
+        <v>15931784.000000002</v>
       </c>
       <c r="H26" s="16">
-        <v>14575558.5</v>
+        <v>14575264.699999999</v>
       </c>
       <c r="I26" s="16">
-        <v>16331427.700000001</v>
+        <v>16331184.000000002</v>
       </c>
       <c r="J26" s="16">
-        <v>18097645.300000001</v>
+        <v>18097401</v>
       </c>
       <c r="K26" s="16">
-        <v>17663032</v>
+        <v>17662799.799999997</v>
       </c>
       <c r="L26" s="16">
-        <v>17030240.299999997</v>
+        <v>17030025.600000001</v>
       </c>
       <c r="M26" s="16">
-        <v>17172627.999999996</v>
+        <v>17172422.999999996</v>
       </c>
       <c r="N26" s="16">
-        <v>17735854.199999999</v>
+        <v>17726115.099999998</v>
       </c>
       <c r="O26" s="16">
-        <v>0</v>
+        <v>18460827.500000004</v>
       </c>
       <c r="P26" s="8"/>
       <c r="Q26" s="91">
-        <v>184603951.80000001</v>
+        <v>203052522.59999999</v>
       </c>
     </row>
     <row r="27" spans="2:17">
@@ -3661,13 +3658,13 @@
         <v>17880713.100000001</v>
       </c>
       <c r="F28" s="16">
-        <v>20662207.100000001</v>
+        <v>20662207.099999998</v>
       </c>
       <c r="G28" s="16">
         <v>19086549</v>
       </c>
       <c r="H28" s="16">
-        <v>17773938.399999999</v>
+        <v>17773905.899999999</v>
       </c>
       <c r="I28" s="16">
         <v>19360659.600000001</v>
@@ -3676,23 +3673,23 @@
         <v>21262467.599999998</v>
       </c>
       <c r="K28" s="16">
-        <v>20846607.099999998</v>
+        <v>20846610.299999997</v>
       </c>
       <c r="L28" s="16">
-        <v>20092745.099999998</v>
+        <v>20092751.400000002</v>
       </c>
       <c r="M28" s="16">
-        <v>20384580.199999996</v>
+        <v>20384173.899999995</v>
       </c>
       <c r="N28" s="16">
-        <v>20973158.199999999</v>
+        <v>20963605.399999999</v>
       </c>
       <c r="O28" s="16">
-        <v>0</v>
+        <v>21707316.800000004</v>
       </c>
       <c r="P28" s="8"/>
       <c r="Q28" s="90">
-        <v>218979959.60000002</v>
+        <v>240677294.29999998</v>
       </c>
     </row>
     <row r="29" spans="2:17">
@@ -3763,17 +3760,17 @@
         <v>1267540</v>
       </c>
       <c r="M31" s="16">
-        <v>1317951.1000000001</v>
+        <v>1318333.8</v>
       </c>
       <c r="N31" s="16">
-        <v>1312369.3</v>
+        <v>1312479.8</v>
       </c>
       <c r="O31" s="16">
-        <v>0</v>
+        <v>1372600.3</v>
       </c>
       <c r="P31" s="8"/>
       <c r="Q31" s="91">
-        <v>13519996.6</v>
+        <v>14893090.100000001</v>
       </c>
     </row>
     <row r="32" spans="2:17">
@@ -3814,11 +3811,11 @@
         <v>395917.7</v>
       </c>
       <c r="O32" s="16">
-        <v>0</v>
+        <v>399921.1</v>
       </c>
       <c r="P32" s="8"/>
       <c r="Q32" s="90">
-        <v>4097051.3000000003</v>
+        <v>4496972.4000000004</v>
       </c>
     </row>
     <row r="33" spans="2:17">
@@ -3877,11 +3874,11 @@
         <v>9775.5</v>
       </c>
       <c r="O34" s="16">
-        <v>0</v>
+        <v>9542.4</v>
       </c>
       <c r="P34" s="8"/>
       <c r="Q34" s="91">
-        <v>113718.90000000001</v>
+        <v>123261.3</v>
       </c>
     </row>
     <row r="35" spans="2:17">
@@ -3923,11 +3920,11 @@
         <v>13051.2</v>
       </c>
       <c r="O35" s="16">
-        <v>0</v>
+        <v>10010.799999999999</v>
       </c>
       <c r="P35" s="8"/>
       <c r="Q35" s="91">
-        <v>114553.09999999999</v>
+        <v>124563.9</v>
       </c>
     </row>
     <row r="36" spans="2:17">
@@ -3948,13 +3945,13 @@
         <v>424637.2</v>
       </c>
       <c r="H36" s="16">
-        <v>298511.09999999998</v>
+        <v>298543.59999999998</v>
       </c>
       <c r="I36" s="16">
-        <v>346895.6</v>
+        <v>346895.7</v>
       </c>
       <c r="J36" s="16">
-        <v>447325</v>
+        <v>447325.3</v>
       </c>
       <c r="K36" s="16">
         <v>359023.8</v>
@@ -3966,14 +3963,14 @@
         <v>402894.4</v>
       </c>
       <c r="N36" s="16">
-        <v>495527.1</v>
+        <v>496125.7</v>
       </c>
       <c r="O36" s="16">
-        <v>0</v>
+        <v>570493.69999999995</v>
       </c>
       <c r="P36" s="8"/>
       <c r="Q36" s="91">
-        <v>4726644</v>
+        <v>5297769.2</v>
       </c>
     </row>
     <row r="37" spans="2:17">
@@ -4030,14 +4027,14 @@
         <v>268526.09999999998</v>
       </c>
       <c r="N38" s="16">
-        <v>270289.59999999998</v>
+        <v>270348.59999999998</v>
       </c>
       <c r="O38" s="16">
-        <v>0</v>
+        <v>277399.8</v>
       </c>
       <c r="P38" s="8"/>
       <c r="Q38" s="91">
-        <v>2785900.6</v>
+        <v>3063359.4</v>
       </c>
     </row>
     <row r="39" spans="2:17">
@@ -4079,11 +4076,11 @@
         <v>382.8</v>
       </c>
       <c r="O39" s="16">
-        <v>0</v>
+        <v>592.70000000000005</v>
       </c>
       <c r="P39" s="8"/>
       <c r="Q39" s="91">
-        <v>1472.6</v>
+        <v>2065.3000000000002</v>
       </c>
     </row>
     <row r="40" spans="2:17">
@@ -4163,12 +4160,12 @@
         <v>343811.2</v>
       </c>
       <c r="O42" s="78">
-        <v>0</v>
+        <v>368503.5</v>
       </c>
       <c r="P42" s="79"/>
       <c r="Q42" s="79">
         <f t="shared" ref="Q42:Q46" si="0">SUM(D42:O42)</f>
-        <v>4553056.6000000006</v>
+        <v>4921560.1000000006</v>
       </c>
     </row>
     <row r="43" spans="2:17">
@@ -4221,12 +4218,13 @@
         <v>923811.6</v>
       </c>
       <c r="O43" s="78">
-        <v>0</v>
+        <f>579248.2+467338.6</f>
+        <v>1046586.7999999999</v>
       </c>
       <c r="P43" s="79"/>
       <c r="Q43" s="79">
         <f t="shared" si="0"/>
-        <v>12252521.799999999</v>
+        <v>13299108.6</v>
       </c>
     </row>
     <row r="44" spans="2:17">
@@ -4268,12 +4266,12 @@
         <v>913548.9</v>
       </c>
       <c r="O44" s="78">
-        <v>0</v>
+        <v>872867</v>
       </c>
       <c r="P44" s="79"/>
       <c r="Q44" s="79">
         <f t="shared" si="0"/>
-        <v>9079031.1999999993</v>
+        <v>9951898.1999999993</v>
       </c>
     </row>
     <row r="45" spans="2:17">
@@ -4315,12 +4313,12 @@
         <v>294435.20000000001</v>
       </c>
       <c r="O45" s="80">
-        <v>0</v>
+        <v>273732.8</v>
       </c>
       <c r="P45" s="80"/>
       <c r="Q45" s="80">
         <f t="shared" si="0"/>
-        <v>3362106.4</v>
+        <v>3635839.1999999997</v>
       </c>
     </row>
     <row r="46" spans="2:17">
@@ -4329,7 +4327,7 @@
       </c>
       <c r="C46" s="17"/>
       <c r="D46" s="89">
-        <f t="shared" ref="D46:N46" si="1">SUM(D42:D45)</f>
+        <f t="shared" ref="D46:O46" si="1">SUM(D42:D45)</f>
         <v>2851686.5</v>
       </c>
       <c r="E46" s="89">
@@ -4373,12 +4371,13 @@
         <v>2475606.9000000004</v>
       </c>
       <c r="O46" s="89">
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>2561690.0999999996</v>
       </c>
       <c r="P46" s="79"/>
       <c r="Q46" s="79">
         <f t="shared" si="0"/>
-        <v>29246716</v>
+        <v>31808406.100000001</v>
       </c>
     </row>
     <row r="47" spans="2:17">
@@ -4404,7 +4403,7 @@
         <v>58</v>
       </c>
       <c r="D48" s="89">
-        <f t="shared" ref="D48:N48" si="2">D31+D32+D34+D35+D36+D38+D39+D46</f>
+        <f t="shared" ref="D48:O48" si="2">D31+D32+D34+D35+D36+D38+D39+D46</f>
         <v>5351175.4000000004</v>
       </c>
       <c r="E48" s="89">
@@ -4421,15 +4420,15 @@
       </c>
       <c r="H48" s="89">
         <f t="shared" si="2"/>
-        <v>4980598.2000000011</v>
+        <v>4980630.7000000011</v>
       </c>
       <c r="I48" s="89">
         <f t="shared" si="2"/>
-        <v>4687966.1000000006</v>
+        <v>4687966.2</v>
       </c>
       <c r="J48" s="89">
         <f t="shared" si="2"/>
-        <v>5157614.4000000004</v>
+        <v>5157614.7</v>
       </c>
       <c r="K48" s="89">
         <f t="shared" si="2"/>
@@ -4441,19 +4440,20 @@
       </c>
       <c r="M48" s="89">
         <f t="shared" si="2"/>
-        <v>4854912</v>
+        <v>4855294.7</v>
       </c>
       <c r="N48" s="89">
         <f t="shared" si="2"/>
-        <v>4972920.0999999996</v>
+        <v>4973688.2</v>
       </c>
       <c r="O48" s="89">
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>5202250.8999999994</v>
       </c>
       <c r="P48" s="79"/>
       <c r="Q48" s="79">
         <f>SUM(D48:O48)</f>
-        <v>54606053.100000001</v>
+        <v>59809487.70000001</v>
       </c>
     </row>
     <row r="49" spans="2:17">
@@ -4511,12 +4511,12 @@
         <v>236663.9</v>
       </c>
       <c r="O50" s="78">
-        <v>0</v>
+        <v>244180</v>
       </c>
       <c r="P50" s="79"/>
       <c r="Q50" s="79">
         <f t="shared" ref="Q50:Q52" si="3">SUM(D50:O50)</f>
-        <v>2410183.5</v>
+        <v>2654363.5</v>
       </c>
     </row>
     <row r="51" spans="2:17">
@@ -4557,12 +4557,12 @@
         <v>119531.3</v>
       </c>
       <c r="O51" s="78">
-        <v>0</v>
+        <v>121137.9</v>
       </c>
       <c r="P51" s="79"/>
       <c r="Q51" s="79">
         <f t="shared" si="3"/>
-        <v>1262112.6000000001</v>
+        <v>1383250.5</v>
       </c>
     </row>
     <row r="52" spans="2:17">
@@ -4597,18 +4597,18 @@
         <v>355918.8</v>
       </c>
       <c r="M52" s="78">
-        <v>371758.5</v>
+        <v>371786.1</v>
       </c>
       <c r="N52" s="78">
-        <v>375716</v>
+        <v>375602.8</v>
       </c>
       <c r="O52" s="78">
-        <v>0</v>
+        <v>394583</v>
       </c>
       <c r="P52" s="78"/>
       <c r="Q52" s="78">
         <f t="shared" si="3"/>
-        <v>3873910.6999999997</v>
+        <v>4268408.0999999996</v>
       </c>
     </row>
     <row r="53" spans="2:17" ht="14.25" customHeight="1">
@@ -4656,23 +4656,23 @@
         <v>9659011.3000000007</v>
       </c>
       <c r="K54" s="83">
-        <v>9453379.9000000004</v>
+        <v>9453383.0999999996</v>
       </c>
       <c r="L54" s="83">
-        <v>9791836</v>
+        <v>9791845.5</v>
       </c>
       <c r="M54" s="83">
-        <v>9498969.8000000007</v>
+        <v>9499007.0999999996</v>
       </c>
       <c r="N54" s="83">
-        <v>9610133.3000000007</v>
+        <v>9610488.9000000004</v>
       </c>
       <c r="O54" s="83">
-        <v>0</v>
+        <v>9791667.5999999996</v>
       </c>
       <c r="P54" s="83"/>
       <c r="Q54" s="84">
-        <v>9610133.3000000007</v>
+        <v>9791667.5999999996</v>
       </c>
     </row>
     <row r="55" spans="2:17">
@@ -4710,18 +4710,18 @@
         <v>-347051.8</v>
       </c>
       <c r="N55" s="78">
-        <v>-365331.5</v>
+        <v>-355355.2</v>
       </c>
       <c r="O55" s="78">
-        <v>0</v>
+        <v>-88387.5</v>
       </c>
       <c r="P55" s="79"/>
       <c r="Q55" s="79">
-        <f>SUM(D55:O55)</f>
-        <v>-2931535.6999999997</v>
-      </c>
-    </row>
-    <row r="56" spans="2:17" ht="15.75" thickBot="1">
+        <f t="shared" ref="Q55" si="4">SUM(D55:O55)</f>
+        <v>-3009946.9</v>
+      </c>
+    </row>
+    <row r="56" spans="2:17" ht="15" thickBot="1">
       <c r="B56" s="104"/>
       <c r="C56" s="18"/>
       <c r="D56" s="85"/>
@@ -4739,61 +4739,62 @@
       <c r="P56" s="86"/>
       <c r="Q56" s="86"/>
     </row>
-    <row r="57" spans="2:17" ht="15.75" thickTop="1">
+    <row r="57" spans="2:17" ht="15" thickTop="1">
       <c r="B57" s="59" t="s">
         <v>31</v>
       </c>
       <c r="D57" s="89">
-        <f t="shared" ref="D57:N57" si="4">D7-D54+(D28+D48)-(D50+D51+D52)+D55</f>
+        <f t="shared" ref="D57:O57" si="5">D7-D54+(D28+D48)-(D50+D51+D52)+D55</f>
         <v>25093226.800000004</v>
       </c>
       <c r="E57" s="89">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>22432525.300000001</v>
       </c>
       <c r="F57" s="89">
-        <f t="shared" si="4"/>
-        <v>24874071.399999999</v>
+        <f t="shared" si="5"/>
+        <v>24874071.399999995</v>
       </c>
       <c r="G57" s="89">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>22594678.300000001</v>
       </c>
       <c r="H57" s="89">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>22331883</v>
       </c>
       <c r="I57" s="89">
-        <f t="shared" si="4"/>
-        <v>23092990.200000007</v>
+        <f t="shared" si="5"/>
+        <v>23092990.300000001</v>
       </c>
       <c r="J57" s="89">
-        <f t="shared" si="4"/>
-        <v>25194298.899999995</v>
+        <f t="shared" si="5"/>
+        <v>25194299.199999992</v>
       </c>
       <c r="K57" s="89">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>24923631.499999996</v>
       </c>
       <c r="L57" s="89">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>23246178</v>
       </c>
       <c r="M57" s="89">
-        <f t="shared" si="4"/>
-        <v>24480479.199999996</v>
+        <f t="shared" si="5"/>
+        <v>24480400.199999992</v>
       </c>
       <c r="N57" s="89">
-        <f t="shared" si="4"/>
-        <v>24737297.799999997</v>
+        <f t="shared" si="5"/>
+        <v>24738384.300000001</v>
       </c>
       <c r="O57" s="89">
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>25879986.200000003</v>
       </c>
       <c r="P57" s="79"/>
       <c r="Q57" s="79">
-        <f>SUM(D57:O57)</f>
-        <v>263001260.39999998</v>
+        <f t="shared" ref="Q57" si="6">SUM(D57:O57)</f>
+        <v>288882254.5</v>
       </c>
     </row>
     <row r="58" spans="2:17">
@@ -4815,7 +4816,7 @@
     </row>
     <row r="59" spans="2:17" s="1" customFormat="1" ht="18" customHeight="1">
       <c r="B59" s="47" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C59" s="4"/>
       <c r="D59" s="106"/>
@@ -4835,7 +4836,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="60" spans="2:17" ht="15.75">
+    <row r="60" spans="2:17" ht="15.6">
       <c r="B60" s="48"/>
       <c r="D60" s="92" t="s">
         <v>1</v>
@@ -4955,11 +4956,11 @@
         <v>61762.700000000004</v>
       </c>
       <c r="O63" s="90">
-        <v>0</v>
+        <v>99370.3</v>
       </c>
       <c r="P63" s="91"/>
       <c r="Q63" s="91">
-        <v>561895.19999999995</v>
+        <v>661265.5</v>
       </c>
     </row>
     <row r="64" spans="2:17">
@@ -5000,11 +5001,11 @@
         <v>2488340.2000000002</v>
       </c>
       <c r="O64" s="90">
-        <v>0</v>
+        <v>2571850.6</v>
       </c>
       <c r="P64" s="91"/>
       <c r="Q64" s="91">
-        <v>25887736.5</v>
+        <v>28459587.100000001</v>
       </c>
     </row>
     <row r="65" spans="2:17">
@@ -5027,10 +5028,10 @@
         <v>11089.6</v>
       </c>
       <c r="I65" s="90">
-        <v>11995.6</v>
+        <v>11995.7</v>
       </c>
       <c r="J65" s="90">
-        <v>9807.5</v>
+        <v>9807.7999999999993</v>
       </c>
       <c r="K65" s="90">
         <v>12739</v>
@@ -5045,11 +5046,11 @@
         <v>15381.7</v>
       </c>
       <c r="O65" s="90">
-        <v>0</v>
+        <v>9760.5</v>
       </c>
       <c r="P65" s="91"/>
       <c r="Q65" s="91">
-        <v>140664</v>
+        <v>150424.90000000002</v>
       </c>
     </row>
     <row r="66" spans="2:17">
@@ -5090,11 +5091,11 @@
         <v>44372.6</v>
       </c>
       <c r="O66" s="90">
-        <v>0</v>
+        <v>10947</v>
       </c>
       <c r="P66" s="91"/>
       <c r="Q66" s="91">
-        <v>219090.6</v>
+        <v>230037.6</v>
       </c>
     </row>
     <row r="67" spans="2:17" s="1" customFormat="1">
@@ -5179,14 +5180,14 @@
         <v>2236.9</v>
       </c>
       <c r="N68" s="90">
-        <v>-15294.4</v>
+        <v>-15341</v>
       </c>
       <c r="O68" s="90">
-        <v>0</v>
+        <v>-8655.1</v>
       </c>
       <c r="P68" s="91"/>
       <c r="Q68" s="90">
-        <v>9269.1999999999989</v>
+        <v>567.49999999999818</v>
       </c>
     </row>
     <row r="69" spans="2:17">
@@ -5225,14 +5226,14 @@
         <v>347549.2</v>
       </c>
       <c r="N69" s="90">
-        <v>352742.3</v>
+        <v>352737.8</v>
       </c>
       <c r="O69" s="90">
-        <v>0</v>
+        <v>341697.8</v>
       </c>
       <c r="P69" s="91"/>
       <c r="Q69" s="91">
-        <v>3382476</v>
+        <v>3724169.3</v>
       </c>
     </row>
     <row r="70" spans="2:17">
@@ -5256,10 +5257,10 @@
         <v>2245276.0999999996</v>
       </c>
       <c r="I70" s="90">
-        <v>2525552.2000000002</v>
+        <v>2525552.3000000003</v>
       </c>
       <c r="J70" s="90">
-        <v>3022775.6</v>
+        <v>3022775.9</v>
       </c>
       <c r="K70" s="90">
         <v>2956883.1</v>
@@ -5271,14 +5272,14 @@
         <v>2800223</v>
       </c>
       <c r="N70" s="90">
-        <v>2947305.1000000006</v>
+        <v>2947254.0000000005</v>
       </c>
       <c r="O70" s="90">
-        <v>0</v>
+        <v>3024971.0999999996</v>
       </c>
       <c r="P70" s="91"/>
       <c r="Q70" s="91">
-        <v>30202179.300000004</v>
+        <v>33227099.700000003</v>
       </c>
     </row>
     <row r="71" spans="2:17">
@@ -5338,11 +5339,11 @@
         <v>21681086.699999999</v>
       </c>
       <c r="O72" s="78">
-        <v>0</v>
+        <v>22442772.100000001</v>
       </c>
       <c r="P72" s="79"/>
       <c r="Q72" s="79">
-        <v>230040986.59999999</v>
+        <v>252483758.69999999</v>
       </c>
     </row>
     <row r="73" spans="2:17">
@@ -5384,11 +5385,11 @@
         <v>722702.89</v>
       </c>
       <c r="O73" s="78">
-        <v>0</v>
+        <v>723960.3903225807</v>
       </c>
       <c r="P73" s="79"/>
       <c r="Q73" s="79">
-        <v>688782.63322650467</v>
+        <v>691714.11298451107</v>
       </c>
     </row>
     <row r="74" spans="2:17">
@@ -5415,56 +5416,57 @@
       </c>
       <c r="C75" s="17"/>
       <c r="D75" s="89">
-        <f t="shared" ref="D75:N75" si="5">D57-(D70+D72)</f>
+        <f t="shared" ref="D75:O75" si="7">D57-(D70+D72)</f>
         <v>378307.50000000373</v>
       </c>
       <c r="E75" s="89">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>151998.80000000075</v>
       </c>
       <c r="F75" s="89">
-        <f t="shared" si="5"/>
-        <v>338531.5</v>
+        <f t="shared" si="7"/>
+        <v>338531.49999999627</v>
       </c>
       <c r="G75" s="89">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>422057.40000000224</v>
       </c>
       <c r="H75" s="89">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>180023.79999999702</v>
       </c>
       <c r="I75" s="89">
-        <f t="shared" si="5"/>
-        <v>284344.90000000596</v>
+        <f t="shared" si="7"/>
+        <v>284344.89999999851</v>
       </c>
       <c r="J75" s="89">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>443894.6999999918</v>
       </c>
       <c r="K75" s="89">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>46643.59999999404</v>
       </c>
       <c r="L75" s="89">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>231766.40000000224</v>
       </c>
       <c r="M75" s="89">
-        <f t="shared" si="5"/>
-        <v>171619.89999999478</v>
+        <f t="shared" si="7"/>
+        <v>171540.89999999106</v>
       </c>
       <c r="N75" s="89">
-        <f t="shared" si="5"/>
-        <v>108905.99999999627</v>
+        <f t="shared" si="7"/>
+        <v>110043.60000000149</v>
       </c>
       <c r="O75" s="89">
-        <v>0</v>
+        <f t="shared" si="7"/>
+        <v>412243</v>
       </c>
       <c r="P75" s="79"/>
       <c r="Q75" s="79">
         <f>SUM(D75:O75)</f>
-        <v>2758094.4999999888</v>
+        <v>3171396.0999999791</v>
       </c>
     </row>
     <row r="76" spans="2:17">
@@ -5473,59 +5475,60 @@
       </c>
       <c r="C76" s="18"/>
       <c r="D76" s="94">
-        <f t="shared" ref="D76:N76" si="6">IF(D57&gt;0,D75/D57,"")</f>
+        <f t="shared" ref="D76:O76" si="8">IF(D57&gt;0,D75/D57,"")</f>
         <v>1.5076080211414008E-2</v>
       </c>
       <c r="E76" s="94">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>6.7758220693949576E-3</v>
       </c>
       <c r="F76" s="94">
-        <f t="shared" si="6"/>
-        <v>1.3609814595933018E-2</v>
+        <f t="shared" si="8"/>
+        <v>1.360981459593287E-2</v>
       </c>
       <c r="G76" s="94">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>1.8679504722136371E-2</v>
       </c>
       <c r="H76" s="94">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>8.0612906668012293E-3</v>
       </c>
       <c r="I76" s="94">
-        <f t="shared" si="6"/>
-        <v>1.2313039478101275E-2</v>
+        <f t="shared" si="8"/>
+        <v>1.2313039424781576E-2</v>
       </c>
       <c r="J76" s="94">
-        <f t="shared" si="6"/>
-        <v>1.761885503390578E-2</v>
+        <f t="shared" si="8"/>
+        <v>1.7618854824110047E-2</v>
       </c>
       <c r="K76" s="94">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>1.8714608262441227E-3</v>
       </c>
       <c r="L76" s="94">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>9.9700862653638051E-3</v>
       </c>
       <c r="M76" s="94">
-        <f t="shared" si="6"/>
-        <v>7.0104795987814984E-3</v>
+        <f t="shared" si="8"/>
+        <v>7.0072751506730317E-3</v>
       </c>
       <c r="N76" s="94">
-        <f t="shared" si="6"/>
-        <v>4.4025018771450567E-3</v>
-      </c>
-      <c r="O76" s="94" t="s">
-        <v>128</v>
+        <f t="shared" si="8"/>
+        <v>4.4482937392156807E-3</v>
+      </c>
+      <c r="O76" s="94">
+        <f t="shared" si="8"/>
+        <v>1.5929027040980415E-2</v>
       </c>
       <c r="P76" s="94"/>
       <c r="Q76" s="79">
         <f>AVERAGE(D76:O76)</f>
-        <v>1.048990321320192E-2</v>
-      </c>
-    </row>
-    <row r="77" spans="2:17" ht="15.75" thickBot="1">
+        <v>1.0946712461420677E-2</v>
+      </c>
+    </row>
+    <row r="77" spans="2:17" ht="15" thickBot="1">
       <c r="B77" s="104"/>
       <c r="C77" s="26"/>
       <c r="D77" s="87"/>
@@ -5543,61 +5546,62 @@
       <c r="P77" s="79"/>
       <c r="Q77" s="88"/>
     </row>
-    <row r="78" spans="2:17" ht="15.75" thickTop="1">
+    <row r="78" spans="2:17" ht="15" thickTop="1">
       <c r="B78" s="59" t="s">
         <v>36</v>
       </c>
       <c r="D78" s="89">
-        <f t="shared" ref="D78:N78" si="7">(D70+D72)+D75</f>
+        <f t="shared" ref="D78:O78" si="9">(D70+D72)+D75</f>
         <v>25093226.800000004</v>
       </c>
       <c r="E78" s="89">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>22432525.300000001</v>
       </c>
       <c r="F78" s="89">
-        <f t="shared" si="7"/>
-        <v>24874071.399999999</v>
+        <f t="shared" si="9"/>
+        <v>24874071.399999995</v>
       </c>
       <c r="G78" s="89">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>22594678.300000001</v>
       </c>
       <c r="H78" s="89">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>22331883</v>
       </c>
       <c r="I78" s="89">
-        <f t="shared" si="7"/>
-        <v>23092990.200000007</v>
+        <f t="shared" si="9"/>
+        <v>23092990.300000001</v>
       </c>
       <c r="J78" s="89">
-        <f t="shared" si="7"/>
-        <v>25194298.899999995</v>
+        <f t="shared" si="9"/>
+        <v>25194299.199999992</v>
       </c>
       <c r="K78" s="89">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>24923631.499999996</v>
       </c>
       <c r="L78" s="89">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>23246178</v>
       </c>
       <c r="M78" s="89">
-        <f t="shared" si="7"/>
-        <v>24480479.199999996</v>
+        <f t="shared" si="9"/>
+        <v>24480400.199999992</v>
       </c>
       <c r="N78" s="89">
-        <f t="shared" si="7"/>
-        <v>24737297.799999997</v>
+        <f t="shared" si="9"/>
+        <v>24738384.300000001</v>
       </c>
       <c r="O78" s="89">
-        <v>0</v>
+        <f t="shared" si="9"/>
+        <v>25879986.200000003</v>
       </c>
       <c r="P78" s="79"/>
       <c r="Q78" s="79">
         <f>SUM(D78:O78)</f>
-        <v>263001260.39999998</v>
+        <v>288882254.5</v>
       </c>
     </row>
     <row r="79" spans="2:17">
@@ -5702,15 +5706,15 @@
       <c r="D86" s="12"/>
       <c r="Q86" s="91"/>
     </row>
-    <row r="87" spans="2:17" ht="15.75">
+    <row r="87" spans="2:17" ht="15.6">
       <c r="B87" s="35"/>
       <c r="D87" s="12"/>
       <c r="Q87" s="91"/>
     </row>
-    <row r="88" spans="2:17" ht="15.75">
+    <row r="88" spans="2:17" ht="15.6">
       <c r="B88" s="35"/>
     </row>
-    <row r="89" spans="2:17" ht="15.75">
+    <row r="89" spans="2:17" ht="15.6">
       <c r="B89" s="35"/>
     </row>
   </sheetData>

--- a/Oil_current.xlsx
+++ b/Oil_current.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29530"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="V:\Information Management\Info Sharing and Tracking\Product Services\Operations\Product Creation\ST3\ST3s_Report_Prep\All_Pages_Content_Update\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53361852-8627-4CE6-AC20-813D2C329BA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2737612-7BCE-41D6-9D5B-E9D4610A08E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="16440" windowHeight="28320" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Documentation" sheetId="21" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="130">
   <si>
     <t>Reporting Adjustment</t>
   </si>
@@ -473,10 +473,13 @@
     <t>Nonupgraded</t>
   </si>
   <si>
-    <t>2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Run Date:  27 January 2026</t>
+    <t xml:space="preserve"> Run Date:  27 February 2026</t>
+  </si>
+  <si>
+    <t>2026</t>
+  </si>
+  <si>
+    <t/>
   </si>
 </sst>
 </file>
@@ -832,7 +835,7 @@
     </xf>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="111">
+  <cellXfs count="112">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1064,16 +1067,17 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="16">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -1507,17 +1511,17 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:BK84"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
     <col min="2" max="2" width="43" customWidth="1"/>
-    <col min="3" max="3" width="3.88671875" customWidth="1"/>
-    <col min="4" max="15" width="14.5546875" customWidth="1"/>
-    <col min="16" max="16" width="1.5546875" customWidth="1"/>
+    <col min="3" max="3" width="3.85546875" customWidth="1"/>
+    <col min="4" max="15" width="14.5703125" customWidth="1"/>
+    <col min="16" max="16" width="1.5703125" customWidth="1"/>
     <col min="17" max="17" width="17" customWidth="1"/>
-    <col min="18" max="18" width="14.5546875" customWidth="1"/>
-    <col min="21" max="21" width="20.33203125" customWidth="1"/>
-    <col min="22" max="22" width="14.44140625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.5703125" customWidth="1"/>
+    <col min="21" max="21" width="20.28515625" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:63" s="2" customFormat="1" ht="20.25" customHeight="1">
@@ -2493,7 +2497,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="56" spans="1:19" ht="15" thickBot="1">
+    <row r="56" spans="1:19" ht="15.75" thickBot="1">
       <c r="B56" s="50"/>
       <c r="C56" s="17"/>
       <c r="D56" s="69"/>
@@ -2510,7 +2514,7 @@
       <c r="O56" s="25"/>
       <c r="Q56" s="25"/>
     </row>
-    <row r="57" spans="1:19" ht="15" thickTop="1">
+    <row r="57" spans="1:19" ht="15.75" thickTop="1">
       <c r="B57" s="59" t="s">
         <v>31</v>
       </c>
@@ -2732,7 +2736,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="77" spans="2:17" ht="15" thickBot="1">
+    <row r="77" spans="2:17" ht="15.75" thickBot="1">
       <c r="B77" s="50"/>
       <c r="C77" s="19"/>
       <c r="D77" s="69"/>
@@ -2749,7 +2753,7 @@
       <c r="O77" s="25"/>
       <c r="Q77" s="25"/>
     </row>
-    <row r="78" spans="2:17" ht="15" thickTop="1">
+    <row r="78" spans="2:17" ht="15.75" thickTop="1">
       <c r="B78" s="59" t="s">
         <v>36</v>
       </c>
@@ -2803,16 +2807,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:V89"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
-    <col min="2" max="2" width="44.6640625" customWidth="1"/>
+    <col min="2" max="2" width="44.7109375" customWidth="1"/>
     <col min="3" max="3" width="4" customWidth="1"/>
-    <col min="4" max="13" width="15.6640625" customWidth="1"/>
-    <col min="14" max="14" width="15.88671875" customWidth="1"/>
-    <col min="15" max="15" width="15.6640625" customWidth="1"/>
-    <col min="16" max="16" width="1.5546875" customWidth="1"/>
-    <col min="17" max="17" width="19.44140625" customWidth="1"/>
+    <col min="4" max="13" width="15.7109375" customWidth="1"/>
+    <col min="14" max="14" width="15.85546875" customWidth="1"/>
+    <col min="15" max="15" width="15.7109375" customWidth="1"/>
+    <col min="16" max="16" width="1.5703125" customWidth="1"/>
+    <col min="17" max="17" width="19.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:22" s="2" customFormat="1" ht="20.25" customHeight="1">
@@ -2840,7 +2844,7 @@
     </row>
     <row r="4" spans="2:22" ht="22.5" customHeight="1">
       <c r="B4" s="47" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C4" s="22"/>
       <c r="D4" s="1"/>
@@ -2901,7 +2905,7 @@
       </c>
       <c r="P5" s="3"/>
       <c r="Q5" s="29" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="6" spans="2:22" s="1" customFormat="1">
@@ -2916,44 +2920,44 @@
       </c>
       <c r="C7"/>
       <c r="D7" s="90">
-        <v>9506670.5999999996</v>
+        <v>9791712</v>
       </c>
       <c r="E7" s="16">
-        <v>9474020.8000000007</v>
+        <v>0</v>
       </c>
       <c r="F7" s="16">
-        <v>8863827.3000000007</v>
+        <v>0</v>
       </c>
       <c r="G7" s="16">
-        <v>9166898.4000000004</v>
+        <v>0</v>
       </c>
       <c r="H7" s="16">
-        <v>10019874.1</v>
+        <v>0</v>
       </c>
       <c r="I7" s="16">
-        <v>9475582.3000000007</v>
+        <v>0</v>
       </c>
       <c r="J7" s="16">
-        <v>9440603.5999999996</v>
+        <v>0</v>
       </c>
       <c r="K7" s="16">
-        <v>9659011.3000000007</v>
+        <v>0</v>
       </c>
       <c r="L7" s="16">
-        <v>9453273.0999999996</v>
+        <v>0</v>
       </c>
       <c r="M7" s="16">
-        <v>9791845.5</v>
+        <v>0</v>
       </c>
       <c r="N7" s="16">
-        <v>9498732.8000000007</v>
+        <v>0</v>
       </c>
       <c r="O7" s="16">
-        <v>9610374.5</v>
+        <v>0</v>
       </c>
       <c r="P7" s="8"/>
       <c r="Q7" s="91">
-        <v>9506670.5999999996</v>
+        <v>9791712</v>
       </c>
       <c r="V7" s="16"/>
     </row>
@@ -3017,44 +3021,44 @@
         <v>25</v>
       </c>
       <c r="D11" s="90">
-        <v>1500578.1</v>
+        <v>1628795.8</v>
       </c>
       <c r="E11" s="16">
-        <v>1369675.6</v>
+        <v>0</v>
       </c>
       <c r="F11" s="16">
-        <v>1586784.1</v>
+        <v>0</v>
       </c>
       <c r="G11" s="16">
-        <v>1553184.7</v>
+        <v>0</v>
       </c>
       <c r="H11" s="16">
-        <v>1560708.5</v>
+        <v>0</v>
       </c>
       <c r="I11" s="16">
-        <v>1499376</v>
+        <v>0</v>
       </c>
       <c r="J11" s="16">
-        <v>1569168.3</v>
+        <v>0</v>
       </c>
       <c r="K11" s="16">
-        <v>1576344.3</v>
+        <v>0</v>
       </c>
       <c r="L11" s="16">
-        <v>1494898.5</v>
+        <v>0</v>
       </c>
       <c r="M11" s="16">
-        <v>1602745.2</v>
+        <v>0</v>
       </c>
       <c r="N11" s="16">
-        <v>1625857.9</v>
+        <v>0</v>
       </c>
       <c r="O11" s="16">
-        <v>1635881.4</v>
+        <v>0</v>
       </c>
       <c r="P11" s="8"/>
       <c r="Q11" s="91">
-        <v>18575202.599999998</v>
+        <v>1628795.8</v>
       </c>
     </row>
     <row r="12" spans="2:22" s="1" customFormat="1">
@@ -3063,44 +3067,44 @@
       </c>
       <c r="C12"/>
       <c r="D12" s="90">
-        <v>378569.5</v>
+        <v>339234</v>
       </c>
       <c r="E12" s="16">
-        <v>334457.7</v>
+        <v>0</v>
       </c>
       <c r="F12" s="16">
-        <v>388112.1</v>
+        <v>0</v>
       </c>
       <c r="G12" s="16">
-        <v>379080.8</v>
+        <v>0</v>
       </c>
       <c r="H12" s="16">
-        <v>379743.2</v>
+        <v>0</v>
       </c>
       <c r="I12" s="16">
-        <v>350621.8</v>
+        <v>0</v>
       </c>
       <c r="J12" s="16">
-        <v>362398.9</v>
+        <v>0</v>
       </c>
       <c r="K12" s="16">
-        <v>359084.2</v>
+        <v>0</v>
       </c>
       <c r="L12" s="16">
-        <v>349643.3</v>
+        <v>0</v>
       </c>
       <c r="M12" s="16">
-        <v>357522.1</v>
+        <v>0</v>
       </c>
       <c r="N12" s="16">
-        <v>340435.1</v>
+        <v>0</v>
       </c>
       <c r="O12" s="16">
-        <v>328051.40000000002</v>
+        <v>0</v>
       </c>
       <c r="P12" s="8"/>
       <c r="Q12" s="91">
-        <v>4307720.0999999996</v>
+        <v>339234</v>
       </c>
     </row>
     <row r="13" spans="2:22">
@@ -3108,44 +3112,44 @@
         <v>27</v>
       </c>
       <c r="D13" s="90">
-        <v>178444.4</v>
+        <v>167246.1</v>
       </c>
       <c r="E13" s="16">
-        <v>159299.5</v>
+        <v>0</v>
       </c>
       <c r="F13" s="16">
-        <v>184812.5</v>
+        <v>0</v>
       </c>
       <c r="G13" s="16">
-        <v>173392.2</v>
+        <v>0</v>
       </c>
       <c r="H13" s="16">
-        <v>178129.2</v>
+        <v>0</v>
       </c>
       <c r="I13" s="16">
-        <v>167733.9</v>
+        <v>0</v>
       </c>
       <c r="J13" s="16">
-        <v>172540.5</v>
+        <v>0</v>
       </c>
       <c r="K13" s="16">
-        <v>172815.3</v>
+        <v>0</v>
       </c>
       <c r="L13" s="16">
-        <v>163800.6</v>
+        <v>0</v>
       </c>
       <c r="M13" s="16">
-        <v>170156</v>
+        <v>0</v>
       </c>
       <c r="N13" s="16">
-        <v>164220.1</v>
+        <v>0</v>
       </c>
       <c r="O13" s="16">
-        <v>166056.20000000001</v>
+        <v>0</v>
       </c>
       <c r="P13" s="8"/>
       <c r="Q13" s="91">
-        <v>2051400.4000000004</v>
+        <v>167246.1</v>
       </c>
     </row>
     <row r="14" spans="2:22">
@@ -3153,44 +3157,44 @@
         <v>122</v>
       </c>
       <c r="D14" s="96">
-        <v>653016.4</v>
+        <v>639936.30000000005</v>
       </c>
       <c r="E14" s="76">
-        <v>587166.5</v>
+        <v>0</v>
       </c>
       <c r="F14" s="76">
-        <v>650738.4</v>
+        <v>0</v>
       </c>
       <c r="G14" s="75">
-        <v>629349.9</v>
+        <v>0</v>
       </c>
       <c r="H14" s="75">
-        <v>639232.9</v>
+        <v>0</v>
       </c>
       <c r="I14" s="75">
-        <v>626145</v>
+        <v>0</v>
       </c>
       <c r="J14" s="75">
-        <v>640963</v>
+        <v>0</v>
       </c>
       <c r="K14" s="75">
-        <v>639167.30000000005</v>
+        <v>0</v>
       </c>
       <c r="L14" s="75">
-        <v>627583.9</v>
+        <v>0</v>
       </c>
       <c r="M14" s="75">
-        <v>637304.80000000005</v>
+        <v>0</v>
       </c>
       <c r="N14" s="75">
-        <v>626405.9</v>
+        <v>0</v>
       </c>
       <c r="O14" s="75">
-        <v>628495</v>
+        <v>0</v>
       </c>
       <c r="P14" s="76"/>
       <c r="Q14" s="96">
-        <v>7585569</v>
+        <v>639936.30000000005</v>
       </c>
     </row>
     <row r="15" spans="2:22" s="1" customFormat="1">
@@ -3198,44 +3202,44 @@
         <v>114</v>
       </c>
       <c r="D15" s="90">
-        <v>2710608.4</v>
+        <v>2775212.2</v>
       </c>
       <c r="E15" s="16">
-        <v>2450599.2999999998</v>
+        <v>0</v>
       </c>
       <c r="F15" s="16">
-        <v>2810447.1</v>
+        <v>0</v>
       </c>
       <c r="G15" s="16">
-        <v>2735007.6</v>
+        <v>0</v>
       </c>
       <c r="H15" s="16">
-        <v>2757813.8</v>
+        <v>0</v>
       </c>
       <c r="I15" s="16">
-        <v>2643876.7000000002</v>
+        <v>0</v>
       </c>
       <c r="J15" s="16">
-        <v>2745070.7</v>
+        <v>0</v>
       </c>
       <c r="K15" s="16">
-        <v>2747411.0999999996</v>
+        <v>0</v>
       </c>
       <c r="L15" s="16">
-        <v>2635926.3000000003</v>
+        <v>0</v>
       </c>
       <c r="M15" s="16">
-        <v>2767728.0999999996</v>
+        <v>0</v>
       </c>
       <c r="N15" s="16">
-        <v>2756919</v>
+        <v>0</v>
       </c>
       <c r="O15" s="16">
-        <v>2758484</v>
+        <v>0</v>
       </c>
       <c r="P15" s="8"/>
       <c r="Q15" s="91">
-        <v>32519892.099999994</v>
+        <v>2775212.2</v>
       </c>
     </row>
     <row r="16" spans="2:22" s="1" customFormat="1">
@@ -3260,44 +3264,44 @@
         <v>30</v>
       </c>
       <c r="D17" s="90">
-        <v>413127.3</v>
+        <v>465488.7</v>
       </c>
       <c r="E17" s="16">
-        <v>356911.7</v>
+        <v>0</v>
       </c>
       <c r="F17" s="16">
-        <v>392862.7</v>
+        <v>0</v>
       </c>
       <c r="G17" s="16">
-        <v>419757.4</v>
+        <v>0</v>
       </c>
       <c r="H17" s="16">
-        <v>440827.4</v>
+        <v>0</v>
       </c>
       <c r="I17" s="16">
-        <v>385598.9</v>
+        <v>0</v>
       </c>
       <c r="J17" s="16">
-        <v>419995.9</v>
+        <v>0</v>
       </c>
       <c r="K17" s="16">
-        <v>436399.4</v>
+        <v>0</v>
       </c>
       <c r="L17" s="16">
-        <v>426799.5</v>
+        <v>0</v>
       </c>
       <c r="M17" s="16">
-        <v>444022.8</v>
+        <v>0</v>
       </c>
       <c r="N17" s="16">
-        <v>480571.3</v>
+        <v>0</v>
       </c>
       <c r="O17" s="16">
-        <v>488005.3</v>
+        <v>0</v>
       </c>
       <c r="P17" s="8"/>
       <c r="Q17" s="91">
-        <v>5104879.5999999996</v>
+        <v>465488.7</v>
       </c>
     </row>
     <row r="18" spans="2:17">
@@ -3361,44 +3365,44 @@
       </c>
       <c r="C21" s="18"/>
       <c r="D21" s="90">
-        <v>9633084.1999999993</v>
+        <v>9908622.6999999993</v>
       </c>
       <c r="E21" s="16">
-        <v>8586208.1999999993</v>
+        <v>0</v>
       </c>
       <c r="F21" s="16">
-        <v>9673791.5</v>
+        <v>0</v>
       </c>
       <c r="G21" s="16">
-        <v>9111123.8000000007</v>
+        <v>0</v>
       </c>
       <c r="H21" s="16">
-        <v>8858540</v>
+        <v>0</v>
       </c>
       <c r="I21" s="16">
-        <v>8756247.8000000007</v>
+        <v>0</v>
       </c>
       <c r="J21" s="16">
-        <v>9732047.1999999993</v>
+        <v>0</v>
       </c>
       <c r="K21" s="16">
-        <v>9667805.6999999993</v>
+        <v>0</v>
       </c>
       <c r="L21" s="16">
-        <v>9194973.3000000007</v>
+        <v>0</v>
       </c>
       <c r="M21" s="16">
-        <v>9720914.0999999996</v>
+        <v>0</v>
       </c>
       <c r="N21" s="16">
-        <v>9611151.0999999996</v>
+        <v>0</v>
       </c>
       <c r="O21" s="16">
-        <v>9824155.8000000007</v>
+        <v>0</v>
       </c>
       <c r="P21" s="8"/>
       <c r="Q21" s="91">
-        <v>112370042.69999999</v>
+        <v>9908622.6999999993</v>
       </c>
     </row>
     <row r="22" spans="2:17">
@@ -3407,44 +3411,44 @@
       </c>
       <c r="C22" s="18"/>
       <c r="D22" s="90">
-        <v>8942975.4000000004</v>
+        <v>8723461.9000000004</v>
       </c>
       <c r="E22" s="16">
-        <v>7374643.2999999998</v>
+        <v>0</v>
       </c>
       <c r="F22" s="16">
-        <v>8814790.6999999993</v>
+        <v>0</v>
       </c>
       <c r="G22" s="16">
-        <v>7802331.9000000004</v>
+        <v>0</v>
       </c>
       <c r="H22" s="16">
-        <v>6619318</v>
+        <v>0</v>
       </c>
       <c r="I22" s="16">
-        <v>8448607.8000000007</v>
+        <v>0</v>
       </c>
       <c r="J22" s="16">
-        <v>9336202.6999999993</v>
+        <v>0</v>
       </c>
       <c r="K22" s="16">
-        <v>9061990.1999999993</v>
+        <v>0</v>
       </c>
       <c r="L22" s="16">
-        <v>8878592.9000000004</v>
+        <v>0</v>
       </c>
       <c r="M22" s="16">
-        <v>8522998.1999999993</v>
+        <v>0</v>
       </c>
       <c r="N22" s="16">
-        <v>9090317.3000000007</v>
+        <v>0</v>
       </c>
       <c r="O22" s="16">
-        <v>9660103.4000000004</v>
+        <v>0</v>
       </c>
       <c r="P22" s="8"/>
       <c r="Q22" s="91">
-        <v>102552871.80000001</v>
+        <v>8723461.9000000004</v>
       </c>
     </row>
     <row r="23" spans="2:17">
@@ -3453,44 +3457,44 @@
       </c>
       <c r="C23" s="17"/>
       <c r="D23" s="90">
-        <v>-8085028.2999999998</v>
+        <v>-7655105</v>
       </c>
       <c r="E23" s="16">
-        <v>-6874941.5999999996</v>
+        <v>0</v>
       </c>
       <c r="F23" s="16">
-        <v>-7772361</v>
+        <v>0</v>
       </c>
       <c r="G23" s="16">
-        <v>-6629495.7999999998</v>
+        <v>0</v>
       </c>
       <c r="H23" s="16">
-        <v>-5503172.9000000004</v>
+        <v>0</v>
       </c>
       <c r="I23" s="16">
-        <v>-6572086.0999999996</v>
+        <v>0</v>
       </c>
       <c r="J23" s="16">
-        <v>-7685788.0999999996</v>
+        <v>0</v>
       </c>
       <c r="K23" s="16">
-        <v>-7765147.5999999996</v>
+        <v>0</v>
       </c>
       <c r="L23" s="16">
-        <v>-7284179.2000000002</v>
+        <v>0</v>
       </c>
       <c r="M23" s="16">
-        <v>-7767823.9000000004</v>
+        <v>0</v>
       </c>
       <c r="N23" s="16">
-        <v>-8027360.0999999996</v>
+        <v>0</v>
       </c>
       <c r="O23" s="16">
-        <v>-7890512.2000000002</v>
+        <v>0</v>
       </c>
       <c r="P23" s="8"/>
       <c r="Q23" s="91">
-        <v>-87857896.800000012</v>
+        <v>-7655105</v>
       </c>
     </row>
     <row r="24" spans="2:17">
@@ -3499,44 +3503,44 @@
       </c>
       <c r="C24" s="17"/>
       <c r="D24" s="90">
-        <v>10491031.300000001</v>
+        <v>10976979.600000001</v>
       </c>
       <c r="E24" s="16">
-        <v>9085909.9000000004</v>
+        <v>0</v>
       </c>
       <c r="F24" s="16">
-        <v>10716221.199999999</v>
+        <v>0</v>
       </c>
       <c r="G24" s="16">
-        <v>10283959.900000002</v>
+        <v>0</v>
       </c>
       <c r="H24" s="16">
-        <v>9974685.0999999996</v>
+        <v>0</v>
       </c>
       <c r="I24" s="16">
-        <v>10632769.500000002</v>
+        <v>0</v>
       </c>
       <c r="J24" s="16">
-        <v>11382461.799999999</v>
+        <v>0</v>
       </c>
       <c r="K24" s="16">
-        <v>10964648.299999999</v>
+        <v>0</v>
       </c>
       <c r="L24" s="16">
-        <v>10789387.000000004</v>
+        <v>0</v>
       </c>
       <c r="M24" s="16">
-        <v>10476088.399999997</v>
+        <v>0</v>
       </c>
       <c r="N24" s="16">
-        <v>10674108.299999999</v>
+        <v>0</v>
       </c>
       <c r="O24" s="16">
-        <v>11593747.000000004</v>
+        <v>0</v>
       </c>
       <c r="P24" s="8"/>
       <c r="Q24" s="91">
-        <v>127065017.69999999</v>
+        <v>10976979.600000001</v>
       </c>
     </row>
     <row r="25" spans="2:17">
@@ -3544,44 +3548,44 @@
         <v>28</v>
       </c>
       <c r="D25" s="95">
-        <v>7041567.2000000002</v>
+        <v>6541474</v>
       </c>
       <c r="E25" s="42">
-        <v>5987292.2000000002</v>
+        <v>0</v>
       </c>
       <c r="F25" s="42">
-        <v>6742676.0999999996</v>
+        <v>0</v>
       </c>
       <c r="G25" s="42">
-        <v>5647824.0999999996</v>
+        <v>0</v>
       </c>
       <c r="H25" s="42">
-        <v>4600579.5999999996</v>
+        <v>0</v>
       </c>
       <c r="I25" s="42">
-        <v>5698414.5</v>
+        <v>0</v>
       </c>
       <c r="J25" s="42">
-        <v>6714939.2000000002</v>
+        <v>0</v>
       </c>
       <c r="K25" s="42">
-        <v>6698151.5</v>
+        <v>0</v>
       </c>
       <c r="L25" s="42">
-        <v>6240638.5999999996</v>
+        <v>0</v>
       </c>
       <c r="M25" s="42">
-        <v>6696334.5999999996</v>
+        <v>0</v>
       </c>
       <c r="N25" s="42">
-        <v>7052006.7999999998</v>
+        <v>0</v>
       </c>
       <c r="O25" s="42">
-        <v>6867080.5</v>
+        <v>0</v>
       </c>
       <c r="P25" s="8"/>
       <c r="Q25" s="98">
-        <v>75987504.900000006</v>
+        <v>6541474</v>
       </c>
     </row>
     <row r="26" spans="2:17">
@@ -3589,44 +3593,44 @@
         <v>46</v>
       </c>
       <c r="D26" s="90">
-        <v>17532598.5</v>
+        <v>17518453.600000001</v>
       </c>
       <c r="E26" s="16">
-        <v>15073202.100000001</v>
+        <v>0</v>
       </c>
       <c r="F26" s="16">
-        <v>17458897.299999997</v>
+        <v>0</v>
       </c>
       <c r="G26" s="16">
-        <v>15931784.000000002</v>
+        <v>0</v>
       </c>
       <c r="H26" s="16">
-        <v>14575264.699999999</v>
+        <v>0</v>
       </c>
       <c r="I26" s="16">
-        <v>16331184.000000002</v>
+        <v>0</v>
       </c>
       <c r="J26" s="16">
-        <v>18097401</v>
+        <v>0</v>
       </c>
       <c r="K26" s="16">
-        <v>17662799.799999997</v>
+        <v>0</v>
       </c>
       <c r="L26" s="16">
-        <v>17030025.600000001</v>
+        <v>0</v>
       </c>
       <c r="M26" s="16">
-        <v>17172422.999999996</v>
+        <v>0</v>
       </c>
       <c r="N26" s="16">
-        <v>17726115.099999998</v>
+        <v>0</v>
       </c>
       <c r="O26" s="16">
-        <v>18460827.500000004</v>
+        <v>0</v>
       </c>
       <c r="P26" s="8"/>
       <c r="Q26" s="91">
-        <v>203052522.59999999</v>
+        <v>17518453.600000001</v>
       </c>
     </row>
     <row r="27" spans="2:17">
@@ -3652,44 +3656,44 @@
       </c>
       <c r="C28" s="17"/>
       <c r="D28" s="90">
-        <v>20656334.199999999</v>
+        <v>20759154.5</v>
       </c>
       <c r="E28" s="16">
-        <v>17880713.100000001</v>
+        <v>0</v>
       </c>
       <c r="F28" s="16">
-        <v>20662207.099999998</v>
+        <v>0</v>
       </c>
       <c r="G28" s="16">
-        <v>19086549</v>
+        <v>0</v>
       </c>
       <c r="H28" s="16">
-        <v>17773905.899999999</v>
+        <v>0</v>
       </c>
       <c r="I28" s="16">
-        <v>19360659.600000001</v>
+        <v>0</v>
       </c>
       <c r="J28" s="16">
-        <v>21262467.599999998</v>
+        <v>0</v>
       </c>
       <c r="K28" s="16">
-        <v>20846610.299999997</v>
+        <v>0</v>
       </c>
       <c r="L28" s="16">
-        <v>20092751.400000002</v>
+        <v>0</v>
       </c>
       <c r="M28" s="16">
-        <v>20384173.899999995</v>
+        <v>0</v>
       </c>
       <c r="N28" s="16">
-        <v>20963605.399999999</v>
+        <v>0</v>
       </c>
       <c r="O28" s="16">
-        <v>21707316.800000004</v>
+        <v>0</v>
       </c>
       <c r="P28" s="8"/>
       <c r="Q28" s="90">
-        <v>240677294.29999998</v>
+        <v>20759154.5</v>
       </c>
     </row>
     <row r="29" spans="2:17">
@@ -3733,44 +3737,44 @@
         <v>49</v>
       </c>
       <c r="D31" s="90">
-        <v>1243239.2</v>
+        <v>1388226.7</v>
       </c>
       <c r="E31" s="16">
-        <v>1071663.1000000001</v>
+        <v>0</v>
       </c>
       <c r="F31" s="16">
-        <v>1273290.8999999999</v>
+        <v>0</v>
       </c>
       <c r="G31" s="16">
-        <v>1190294.5</v>
+        <v>0</v>
       </c>
       <c r="H31" s="16">
-        <v>1206878.8</v>
+        <v>0</v>
       </c>
       <c r="I31" s="16">
-        <v>1127290.7</v>
+        <v>0</v>
       </c>
       <c r="J31" s="16">
-        <v>1240232</v>
+        <v>0</v>
       </c>
       <c r="K31" s="16">
-        <v>1269247</v>
+        <v>0</v>
       </c>
       <c r="L31" s="16">
-        <v>1267540</v>
+        <v>0</v>
       </c>
       <c r="M31" s="16">
-        <v>1318333.8</v>
+        <v>0</v>
       </c>
       <c r="N31" s="16">
-        <v>1312479.8</v>
+        <v>0</v>
       </c>
       <c r="O31" s="16">
-        <v>1372600.3</v>
+        <v>0</v>
       </c>
       <c r="P31" s="8"/>
       <c r="Q31" s="91">
-        <v>14893090.100000001</v>
+        <v>1388226.7</v>
       </c>
     </row>
     <row r="32" spans="2:17">
@@ -3778,44 +3782,44 @@
         <v>48</v>
       </c>
       <c r="D32" s="90">
-        <v>392640.5</v>
+        <v>404376.2</v>
       </c>
       <c r="E32" s="16">
-        <v>341167.9</v>
+        <v>0</v>
       </c>
       <c r="F32" s="16">
-        <v>384891.6</v>
+        <v>0</v>
       </c>
       <c r="G32" s="16">
-        <v>373030.6</v>
+        <v>0</v>
       </c>
       <c r="H32" s="16">
-        <v>363016.5</v>
+        <v>0</v>
       </c>
       <c r="I32" s="16">
-        <v>325942.40000000002</v>
+        <v>0</v>
       </c>
       <c r="J32" s="16">
-        <v>395262.9</v>
+        <v>0</v>
       </c>
       <c r="K32" s="16">
-        <v>399002.2</v>
+        <v>0</v>
       </c>
       <c r="L32" s="16">
-        <v>360140.3</v>
+        <v>0</v>
       </c>
       <c r="M32" s="16">
-        <v>366038.7</v>
+        <v>0</v>
       </c>
       <c r="N32" s="16">
-        <v>395917.7</v>
+        <v>0</v>
       </c>
       <c r="O32" s="16">
-        <v>399921.1</v>
+        <v>0</v>
       </c>
       <c r="P32" s="8"/>
       <c r="Q32" s="90">
-        <v>4496972.4000000004</v>
+        <v>404376.2</v>
       </c>
     </row>
     <row r="33" spans="2:17">
@@ -3841,44 +3845,44 @@
       </c>
       <c r="C34" s="17"/>
       <c r="D34" s="90">
-        <v>11063.1</v>
+        <v>10103.799999999999</v>
       </c>
       <c r="E34" s="16">
-        <v>9839.6</v>
+        <v>0</v>
       </c>
       <c r="F34" s="16">
-        <v>10997.5</v>
+        <v>0</v>
       </c>
       <c r="G34" s="16">
-        <v>11388.1</v>
+        <v>0</v>
       </c>
       <c r="H34" s="16">
-        <v>10958.3</v>
+        <v>0</v>
       </c>
       <c r="I34" s="16">
-        <v>9398.4</v>
+        <v>0</v>
       </c>
       <c r="J34" s="16">
-        <v>10341.700000000001</v>
+        <v>0</v>
       </c>
       <c r="K34" s="16">
-        <v>10489.1</v>
+        <v>0</v>
       </c>
       <c r="L34" s="16">
-        <v>9211.2000000000007</v>
+        <v>0</v>
       </c>
       <c r="M34" s="16">
-        <v>10256.4</v>
+        <v>0</v>
       </c>
       <c r="N34" s="16">
-        <v>9775.5</v>
+        <v>0</v>
       </c>
       <c r="O34" s="16">
-        <v>9542.4</v>
+        <v>0</v>
       </c>
       <c r="P34" s="8"/>
       <c r="Q34" s="91">
-        <v>123261.3</v>
+        <v>10103.799999999999</v>
       </c>
     </row>
     <row r="35" spans="2:17">
@@ -3887,44 +3891,44 @@
       </c>
       <c r="C35" s="18"/>
       <c r="D35" s="90">
-        <v>7685.1</v>
+        <v>11035</v>
       </c>
       <c r="E35" s="16">
-        <v>6828.7</v>
+        <v>0</v>
       </c>
       <c r="F35" s="16">
-        <v>11412.3</v>
+        <v>0</v>
       </c>
       <c r="G35" s="16">
-        <v>10763.4</v>
+        <v>0</v>
       </c>
       <c r="H35" s="16">
-        <v>7623.8</v>
+        <v>0</v>
       </c>
       <c r="I35" s="16">
-        <v>10400.1</v>
+        <v>0</v>
       </c>
       <c r="J35" s="16">
-        <v>8522.5</v>
+        <v>0</v>
       </c>
       <c r="K35" s="16">
-        <v>10253.1</v>
+        <v>0</v>
       </c>
       <c r="L35" s="16">
-        <v>13283</v>
+        <v>0</v>
       </c>
       <c r="M35" s="16">
-        <v>14729.9</v>
+        <v>0</v>
       </c>
       <c r="N35" s="16">
-        <v>13051.2</v>
+        <v>0</v>
       </c>
       <c r="O35" s="16">
-        <v>10010.799999999999</v>
+        <v>0</v>
       </c>
       <c r="P35" s="8"/>
       <c r="Q35" s="91">
-        <v>124563.9</v>
+        <v>11035</v>
       </c>
     </row>
     <row r="36" spans="2:17">
@@ -3933,44 +3937,44 @@
       </c>
       <c r="C36" s="17"/>
       <c r="D36" s="90">
-        <v>564268.30000000005</v>
+        <v>487218.8</v>
       </c>
       <c r="E36" s="16">
-        <v>466259.8</v>
+        <v>0</v>
       </c>
       <c r="F36" s="16">
-        <v>574571</v>
+        <v>0</v>
       </c>
       <c r="G36" s="16">
-        <v>424637.2</v>
+        <v>0</v>
       </c>
       <c r="H36" s="16">
-        <v>298543.59999999998</v>
+        <v>0</v>
       </c>
       <c r="I36" s="16">
-        <v>346895.7</v>
+        <v>0</v>
       </c>
       <c r="J36" s="16">
-        <v>447325.3</v>
+        <v>0</v>
       </c>
       <c r="K36" s="16">
-        <v>359023.8</v>
+        <v>0</v>
       </c>
       <c r="L36" s="16">
-        <v>346730.7</v>
+        <v>0</v>
       </c>
       <c r="M36" s="16">
-        <v>402894.4</v>
+        <v>0</v>
       </c>
       <c r="N36" s="16">
-        <v>496125.7</v>
+        <v>0</v>
       </c>
       <c r="O36" s="16">
-        <v>570493.69999999995</v>
+        <v>0</v>
       </c>
       <c r="P36" s="8"/>
       <c r="Q36" s="91">
-        <v>5297769.2</v>
+        <v>487218.8</v>
       </c>
     </row>
     <row r="37" spans="2:17">
@@ -3997,44 +4001,44 @@
       </c>
       <c r="C38" s="17"/>
       <c r="D38" s="90">
-        <v>280568.8</v>
+        <v>289216.7</v>
       </c>
       <c r="E38" s="16">
-        <v>244717.5</v>
+        <v>0</v>
       </c>
       <c r="F38" s="16">
-        <v>291235.7</v>
+        <v>0</v>
       </c>
       <c r="G38" s="16">
-        <v>270068.3</v>
+        <v>0</v>
       </c>
       <c r="H38" s="16">
-        <v>214731.2</v>
+        <v>0</v>
       </c>
       <c r="I38" s="16">
-        <v>213097.8</v>
+        <v>0</v>
       </c>
       <c r="J38" s="16">
-        <v>240844.7</v>
+        <v>0</v>
       </c>
       <c r="K38" s="16">
-        <v>245963.3</v>
+        <v>0</v>
       </c>
       <c r="L38" s="16">
-        <v>245857.6</v>
+        <v>0</v>
       </c>
       <c r="M38" s="16">
-        <v>268526.09999999998</v>
+        <v>0</v>
       </c>
       <c r="N38" s="16">
-        <v>270348.59999999998</v>
+        <v>0</v>
       </c>
       <c r="O38" s="16">
-        <v>277399.8</v>
+        <v>0</v>
       </c>
       <c r="P38" s="8"/>
       <c r="Q38" s="91">
-        <v>3063359.4</v>
+        <v>289216.7</v>
       </c>
     </row>
     <row r="39" spans="2:17">
@@ -4043,44 +4047,44 @@
       </c>
       <c r="C39" s="17"/>
       <c r="D39" s="90">
-        <v>23.9</v>
+        <v>325.7</v>
       </c>
       <c r="E39" s="16">
-        <v>72.8</v>
+        <v>0</v>
       </c>
       <c r="F39" s="16">
-        <v>51.9</v>
+        <v>0</v>
       </c>
       <c r="G39" s="16">
-        <v>107.5</v>
+        <v>0</v>
       </c>
       <c r="H39" s="16">
-        <v>82.2</v>
+        <v>0</v>
       </c>
       <c r="I39" s="16">
-        <v>26.5</v>
+        <v>0</v>
       </c>
       <c r="J39" s="16">
-        <v>46.2</v>
+        <v>0</v>
       </c>
       <c r="K39" s="16">
-        <v>107.8</v>
+        <v>0</v>
       </c>
       <c r="L39" s="16">
-        <v>209.4</v>
+        <v>0</v>
       </c>
       <c r="M39" s="16">
-        <v>361.6</v>
+        <v>0</v>
       </c>
       <c r="N39" s="16">
-        <v>382.8</v>
+        <v>0</v>
       </c>
       <c r="O39" s="16">
-        <v>592.70000000000005</v>
+        <v>0</v>
       </c>
       <c r="P39" s="8"/>
       <c r="Q39" s="91">
-        <v>2065.3000000000002</v>
+        <v>325.7</v>
       </c>
     </row>
     <row r="40" spans="2:17">
@@ -4127,45 +4131,45 @@
       </c>
       <c r="C42" s="18"/>
       <c r="D42" s="78">
-        <v>486366.8</v>
+        <v>540930.4</v>
       </c>
       <c r="E42" s="78">
-        <v>404814.4</v>
+        <v>0</v>
       </c>
       <c r="F42" s="78">
-        <v>424953.5</v>
+        <v>0</v>
       </c>
       <c r="G42" s="78">
-        <v>486286.3</v>
+        <v>0</v>
       </c>
       <c r="H42" s="78">
-        <v>527931.4</v>
+        <v>0</v>
       </c>
       <c r="I42" s="78">
-        <v>459063.2</v>
+        <v>0</v>
       </c>
       <c r="J42" s="78">
-        <v>434041.8</v>
+        <v>0</v>
       </c>
       <c r="K42" s="78">
-        <v>453726.7</v>
+        <v>0</v>
       </c>
       <c r="L42" s="78">
-        <v>261476.4</v>
+        <v>0</v>
       </c>
       <c r="M42" s="78">
-        <v>270584.90000000002</v>
+        <v>0</v>
       </c>
       <c r="N42" s="78">
-        <v>343811.2</v>
+        <v>0</v>
       </c>
       <c r="O42" s="78">
-        <v>368503.5</v>
+        <v>0</v>
       </c>
       <c r="P42" s="79"/>
       <c r="Q42" s="79">
-        <f t="shared" ref="Q42:Q46" si="0">SUM(D42:O42)</f>
-        <v>4921560.1000000006</v>
+        <f t="shared" ref="Q42:Q57" si="0">D42</f>
+        <v>540930.4</v>
       </c>
     </row>
     <row r="43" spans="2:17">
@@ -4174,57 +4178,46 @@
       </c>
       <c r="C43" s="18"/>
       <c r="D43" s="78">
-        <f>545525.1+612469.9</f>
-        <v>1157995</v>
+        <f>545525.1+761707.6</f>
+        <v>1307232.7</v>
       </c>
       <c r="E43" s="78">
-        <f>550137+548662.1</f>
-        <v>1098799.1000000001</v>
+        <v>0</v>
       </c>
       <c r="F43" s="78">
-        <f>566495.6+582720</f>
-        <v>1149215.6000000001</v>
+        <v>0</v>
       </c>
       <c r="G43" s="78">
-        <f>545193.8+630875.2</f>
-        <v>1176069</v>
+        <v>0</v>
       </c>
       <c r="H43" s="78">
-        <f>573030.5+687839.2</f>
-        <v>1260869.7</v>
+        <v>0</v>
       </c>
       <c r="I43" s="78">
-        <f>500782.5+608790.2</f>
-        <v>1109572.7</v>
+        <v>0</v>
       </c>
       <c r="J43" s="78">
-        <f>521888+728810.7</f>
-        <v>1250698.7</v>
+        <v>0</v>
       </c>
       <c r="K43" s="78">
-        <f>508726.8+556568.3</f>
-        <v>1065295.1000000001</v>
+        <v>0</v>
       </c>
       <c r="L43" s="78">
-        <f>493931+509475.7</f>
-        <v>1003406.7</v>
+        <v>0</v>
       </c>
       <c r="M43" s="78">
-        <f>530050.6+526738</f>
-        <v>1056788.6000000001</v>
+        <v>0</v>
       </c>
       <c r="N43" s="78">
-        <f>500495.1+423316.5</f>
-        <v>923811.6</v>
+        <v>0</v>
       </c>
       <c r="O43" s="78">
-        <f>579248.2+467338.6</f>
-        <v>1046586.7999999999</v>
+        <v>0</v>
       </c>
       <c r="P43" s="79"/>
       <c r="Q43" s="79">
         <f t="shared" si="0"/>
-        <v>13299108.6</v>
+        <v>1307232.7</v>
       </c>
     </row>
     <row r="44" spans="2:17">
@@ -4233,45 +4226,45 @@
       </c>
       <c r="C44" s="18"/>
       <c r="D44" s="78">
-        <v>911629.3</v>
+        <v>817025.9</v>
       </c>
       <c r="E44" s="78">
-        <v>799705.2</v>
+        <v>0</v>
       </c>
       <c r="F44" s="78">
-        <v>910397.8</v>
+        <v>0</v>
       </c>
       <c r="G44" s="78">
-        <v>891385.3</v>
+        <v>0</v>
       </c>
       <c r="H44" s="78">
-        <v>769001</v>
+        <v>0</v>
       </c>
       <c r="I44" s="78">
-        <v>732303.1</v>
+        <v>0</v>
       </c>
       <c r="J44" s="78">
-        <v>784413</v>
+        <v>0</v>
       </c>
       <c r="K44" s="78">
-        <v>835101.3</v>
+        <v>0</v>
       </c>
       <c r="L44" s="78">
-        <v>729109.6</v>
+        <v>0</v>
       </c>
       <c r="M44" s="78">
-        <v>802436.7</v>
+        <v>0</v>
       </c>
       <c r="N44" s="78">
-        <v>913548.9</v>
+        <v>0</v>
       </c>
       <c r="O44" s="78">
-        <v>872867</v>
+        <v>0</v>
       </c>
       <c r="P44" s="79"/>
       <c r="Q44" s="79">
         <f t="shared" si="0"/>
-        <v>9951898.1999999993</v>
+        <v>817025.9</v>
       </c>
     </row>
     <row r="45" spans="2:17">
@@ -4280,45 +4273,45 @@
       </c>
       <c r="C45" s="17"/>
       <c r="D45" s="80">
-        <v>295695.40000000002</v>
+        <v>304164.7</v>
       </c>
       <c r="E45" s="80">
-        <v>244069</v>
+        <v>0</v>
       </c>
       <c r="F45" s="80">
-        <v>335457.90000000002</v>
+        <v>0</v>
       </c>
       <c r="G45" s="80">
-        <v>257566.2</v>
+        <v>0</v>
       </c>
       <c r="H45" s="80">
-        <v>320994.2</v>
+        <v>0</v>
       </c>
       <c r="I45" s="80">
-        <v>353975.6</v>
+        <v>0</v>
       </c>
       <c r="J45" s="80">
-        <v>345885.9</v>
+        <v>0</v>
       </c>
       <c r="K45" s="80">
-        <v>258939.8</v>
+        <v>0</v>
       </c>
       <c r="L45" s="80">
-        <v>310743.59999999998</v>
+        <v>0</v>
       </c>
       <c r="M45" s="80">
-        <v>344343.6</v>
+        <v>0</v>
       </c>
       <c r="N45" s="80">
-        <v>294435.20000000001</v>
+        <v>0</v>
       </c>
       <c r="O45" s="80">
-        <v>273732.8</v>
+        <v>0</v>
       </c>
       <c r="P45" s="80"/>
       <c r="Q45" s="80">
         <f t="shared" si="0"/>
-        <v>3635839.1999999997</v>
+        <v>304164.7</v>
       </c>
     </row>
     <row r="46" spans="2:17">
@@ -4327,57 +4320,46 @@
       </c>
       <c r="C46" s="17"/>
       <c r="D46" s="89">
-        <f t="shared" ref="D46:O46" si="1">SUM(D42:D45)</f>
-        <v>2851686.5</v>
+        <f t="shared" ref="D46" si="1">SUM(D42:D45)</f>
+        <v>2969353.7</v>
       </c>
       <c r="E46" s="89">
-        <f t="shared" si="1"/>
-        <v>2547387.7000000002</v>
+        <v>0</v>
       </c>
       <c r="F46" s="89">
-        <f t="shared" si="1"/>
-        <v>2820024.8000000003</v>
+        <v>0</v>
       </c>
       <c r="G46" s="89">
-        <f t="shared" si="1"/>
-        <v>2811306.8000000003</v>
+        <v>0</v>
       </c>
       <c r="H46" s="89">
-        <f t="shared" si="1"/>
-        <v>2878796.3000000003</v>
+        <v>0</v>
       </c>
       <c r="I46" s="89">
-        <f t="shared" si="1"/>
-        <v>2654914.6</v>
+        <v>0</v>
       </c>
       <c r="J46" s="89">
-        <f t="shared" si="1"/>
-        <v>2815039.4</v>
+        <v>0</v>
       </c>
       <c r="K46" s="89">
-        <f t="shared" si="1"/>
-        <v>2613062.9</v>
+        <v>0</v>
       </c>
       <c r="L46" s="89">
-        <f t="shared" si="1"/>
-        <v>2304736.2999999998</v>
+        <v>0</v>
       </c>
       <c r="M46" s="89">
-        <f t="shared" si="1"/>
-        <v>2474153.8000000003</v>
+        <v>0</v>
       </c>
       <c r="N46" s="89">
-        <f t="shared" si="1"/>
-        <v>2475606.9000000004</v>
+        <v>0</v>
       </c>
       <c r="O46" s="89">
-        <f t="shared" si="1"/>
-        <v>2561690.0999999996</v>
+        <v>0</v>
       </c>
       <c r="P46" s="79"/>
       <c r="Q46" s="79">
         <f t="shared" si="0"/>
-        <v>31808406.100000001</v>
+        <v>2969353.7</v>
       </c>
     </row>
     <row r="47" spans="2:17">
@@ -4403,57 +4385,46 @@
         <v>58</v>
       </c>
       <c r="D48" s="89">
-        <f t="shared" ref="D48:O48" si="2">D31+D32+D34+D35+D36+D38+D39+D46</f>
-        <v>5351175.4000000004</v>
+        <f t="shared" ref="D48" si="2">D31+D32+D34+D35+D36+D38+D39+D46</f>
+        <v>5559856.6000000006</v>
       </c>
       <c r="E48" s="89">
-        <f t="shared" si="2"/>
-        <v>4687937.0999999996</v>
+        <v>0</v>
       </c>
       <c r="F48" s="89">
-        <f t="shared" si="2"/>
-        <v>5366475.7</v>
+        <v>0</v>
       </c>
       <c r="G48" s="89">
-        <f t="shared" si="2"/>
-        <v>5091596.4000000004</v>
+        <v>0</v>
       </c>
       <c r="H48" s="89">
-        <f t="shared" si="2"/>
-        <v>4980630.7000000011</v>
+        <v>0</v>
       </c>
       <c r="I48" s="89">
-        <f t="shared" si="2"/>
-        <v>4687966.2</v>
+        <v>0</v>
       </c>
       <c r="J48" s="89">
-        <f t="shared" si="2"/>
-        <v>5157614.7</v>
+        <v>0</v>
       </c>
       <c r="K48" s="89">
-        <f t="shared" si="2"/>
-        <v>4907149.1999999993</v>
+        <v>0</v>
       </c>
       <c r="L48" s="89">
-        <f t="shared" si="2"/>
-        <v>4547708.5</v>
+        <v>0</v>
       </c>
       <c r="M48" s="89">
-        <f t="shared" si="2"/>
-        <v>4855294.7</v>
+        <v>0</v>
       </c>
       <c r="N48" s="89">
-        <f t="shared" si="2"/>
-        <v>4973688.2</v>
+        <v>0</v>
       </c>
       <c r="O48" s="89">
-        <f t="shared" si="2"/>
-        <v>5202250.8999999994</v>
+        <v>0</v>
       </c>
       <c r="P48" s="79"/>
       <c r="Q48" s="79">
-        <f>SUM(D48:O48)</f>
-        <v>59809487.70000001</v>
+        <f t="shared" si="0"/>
+        <v>5559856.6000000006</v>
       </c>
     </row>
     <row r="49" spans="2:17">
@@ -4478,45 +4449,45 @@
         <v>54</v>
       </c>
       <c r="D50" s="78">
-        <v>222824.7</v>
+        <v>209662.3</v>
       </c>
       <c r="E50" s="78">
-        <v>174768.1</v>
+        <v>0</v>
       </c>
       <c r="F50" s="78">
-        <v>215046.8</v>
+        <v>0</v>
       </c>
       <c r="G50" s="78">
-        <v>189681.1</v>
+        <v>0</v>
       </c>
       <c r="H50" s="78">
-        <v>172020.8</v>
+        <v>0</v>
       </c>
       <c r="I50" s="78">
-        <v>248140.7</v>
+        <v>0</v>
       </c>
       <c r="J50" s="78">
-        <v>243383.2</v>
+        <v>0</v>
       </c>
       <c r="K50" s="78">
-        <v>251528.9</v>
+        <v>0</v>
       </c>
       <c r="L50" s="78">
-        <v>231718.1</v>
+        <v>0</v>
       </c>
       <c r="M50" s="78">
-        <v>224407.2</v>
+        <v>0</v>
       </c>
       <c r="N50" s="78">
-        <v>236663.9</v>
+        <v>0</v>
       </c>
       <c r="O50" s="78">
-        <v>244180</v>
+        <v>0</v>
       </c>
       <c r="P50" s="79"/>
       <c r="Q50" s="79">
-        <f t="shared" ref="Q50:Q52" si="3">SUM(D50:O50)</f>
-        <v>2654363.5</v>
+        <f t="shared" si="0"/>
+        <v>209662.3</v>
       </c>
     </row>
     <row r="51" spans="2:17">
@@ -4524,45 +4495,45 @@
         <v>22</v>
       </c>
       <c r="D51" s="78">
-        <v>124236.8</v>
+        <v>117473.8</v>
       </c>
       <c r="E51" s="78">
-        <v>116058.3</v>
+        <v>0</v>
       </c>
       <c r="F51" s="78">
-        <v>121794.8</v>
+        <v>0</v>
       </c>
       <c r="G51" s="78">
-        <v>106269.2</v>
+        <v>0</v>
       </c>
       <c r="H51" s="78">
-        <v>116208.9</v>
+        <v>0</v>
       </c>
       <c r="I51" s="78">
-        <v>110066.6</v>
+        <v>0</v>
       </c>
       <c r="J51" s="78">
-        <v>114577.9</v>
+        <v>0</v>
       </c>
       <c r="K51" s="78">
-        <v>109729.4</v>
+        <v>0</v>
       </c>
       <c r="L51" s="78">
-        <v>114977.7</v>
+        <v>0</v>
       </c>
       <c r="M51" s="78">
-        <v>108661.7</v>
+        <v>0</v>
       </c>
       <c r="N51" s="78">
-        <v>119531.3</v>
+        <v>0</v>
       </c>
       <c r="O51" s="78">
-        <v>121137.9</v>
+        <v>0</v>
       </c>
       <c r="P51" s="79"/>
       <c r="Q51" s="79">
-        <f t="shared" si="3"/>
-        <v>1383250.5</v>
+        <f t="shared" si="0"/>
+        <v>117473.8</v>
       </c>
     </row>
     <row r="52" spans="2:17">
@@ -4570,64 +4541,64 @@
         <v>17</v>
       </c>
       <c r="D52" s="78">
-        <v>356845.9</v>
+        <v>395846.40000000002</v>
       </c>
       <c r="E52" s="78">
-        <v>315751.2</v>
+        <v>0</v>
       </c>
       <c r="F52" s="78">
-        <v>370289</v>
+        <v>0</v>
       </c>
       <c r="G52" s="78">
-        <v>346980.5</v>
+        <v>0</v>
       </c>
       <c r="H52" s="78">
-        <v>340063.4</v>
+        <v>0</v>
       </c>
       <c r="I52" s="78">
-        <v>320348.40000000002</v>
+        <v>0</v>
       </c>
       <c r="J52" s="78">
-        <v>360205</v>
+        <v>0</v>
       </c>
       <c r="K52" s="78">
-        <v>360034</v>
+        <v>0</v>
       </c>
       <c r="L52" s="78">
-        <v>355918.8</v>
+        <v>0</v>
       </c>
       <c r="M52" s="78">
-        <v>371786.1</v>
+        <v>0</v>
       </c>
       <c r="N52" s="78">
-        <v>375602.8</v>
+        <v>0</v>
       </c>
       <c r="O52" s="78">
-        <v>394583</v>
+        <v>0</v>
       </c>
       <c r="P52" s="78"/>
       <c r="Q52" s="78">
-        <f t="shared" si="3"/>
-        <v>4268408.0999999996</v>
+        <f t="shared" si="0"/>
+        <v>395846.40000000002</v>
       </c>
     </row>
     <row r="53" spans="2:17" ht="14.25" customHeight="1">
       <c r="B53" s="104"/>
       <c r="C53" s="101"/>
-      <c r="D53" s="109"/>
-      <c r="E53" s="109"/>
-      <c r="F53" s="109"/>
-      <c r="G53" s="109"/>
-      <c r="H53" s="109"/>
-      <c r="I53" s="109"/>
-      <c r="J53" s="109"/>
-      <c r="K53" s="109"/>
-      <c r="L53" s="109"/>
-      <c r="M53" s="109"/>
-      <c r="N53" s="109"/>
-      <c r="O53" s="109"/>
-      <c r="P53" s="109"/>
-      <c r="Q53" s="110"/>
+      <c r="D53" s="111"/>
+      <c r="E53" s="107"/>
+      <c r="F53" s="107"/>
+      <c r="G53" s="107"/>
+      <c r="H53" s="107"/>
+      <c r="I53" s="107"/>
+      <c r="J53" s="107"/>
+      <c r="K53" s="107"/>
+      <c r="L53" s="107"/>
+      <c r="M53" s="107"/>
+      <c r="N53" s="107"/>
+      <c r="O53" s="107"/>
+      <c r="P53" s="107"/>
+      <c r="Q53" s="109"/>
     </row>
     <row r="54" spans="2:17" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="B54" s="104" t="s">
@@ -4635,44 +4606,45 @@
       </c>
       <c r="C54" s="4"/>
       <c r="D54" s="83">
-        <v>9474120.5</v>
+        <v>10073236.6</v>
       </c>
       <c r="E54" s="83">
-        <v>8863827.3000000007</v>
+        <v>0</v>
       </c>
       <c r="F54" s="83">
-        <v>9169419.5</v>
+        <v>0</v>
       </c>
       <c r="G54" s="83">
-        <v>10019950.800000001</v>
+        <v>0</v>
       </c>
       <c r="H54" s="83">
-        <v>9475947.5999999996</v>
+        <v>0</v>
       </c>
       <c r="I54" s="83">
-        <v>9440603.5999999996</v>
+        <v>0</v>
       </c>
       <c r="J54" s="83">
-        <v>9659011.3000000007</v>
+        <v>0</v>
       </c>
       <c r="K54" s="83">
-        <v>9453383.0999999996</v>
+        <v>0</v>
       </c>
       <c r="L54" s="83">
-        <v>9791845.5</v>
+        <v>0</v>
       </c>
       <c r="M54" s="83">
-        <v>9499007.0999999996</v>
+        <v>0</v>
       </c>
       <c r="N54" s="83">
-        <v>9610488.9000000004</v>
+        <v>0</v>
       </c>
       <c r="O54" s="83">
-        <v>9791667.5999999996</v>
+        <v>0</v>
       </c>
       <c r="P54" s="83"/>
       <c r="Q54" s="84">
-        <v>9791667.5999999996</v>
+        <f t="shared" si="0"/>
+        <v>10073236.6</v>
       </c>
     </row>
     <row r="55" spans="2:17">
@@ -4680,48 +4652,48 @@
         <v>50</v>
       </c>
       <c r="D55" s="78">
-        <v>-242925.5</v>
+        <v>-281448.59999999998</v>
       </c>
       <c r="E55" s="78">
-        <v>-139740.79999999999</v>
+        <v>0</v>
       </c>
       <c r="F55" s="78">
-        <v>-141888.6</v>
+        <v>0</v>
       </c>
       <c r="G55" s="78">
-        <v>-87483.9</v>
+        <v>0</v>
       </c>
       <c r="H55" s="78">
-        <v>-338287</v>
+        <v>0</v>
       </c>
       <c r="I55" s="78">
-        <v>-312058.5</v>
+        <v>0</v>
       </c>
       <c r="J55" s="78">
-        <v>-289209.3</v>
+        <v>0</v>
       </c>
       <c r="K55" s="78">
-        <v>-314463.90000000002</v>
+        <v>0</v>
       </c>
       <c r="L55" s="78">
-        <v>-353094.9</v>
+        <v>0</v>
       </c>
       <c r="M55" s="78">
-        <v>-347051.8</v>
+        <v>0</v>
       </c>
       <c r="N55" s="78">
-        <v>-355355.2</v>
+        <v>0</v>
       </c>
       <c r="O55" s="78">
-        <v>-88387.5</v>
+        <v>0</v>
       </c>
       <c r="P55" s="79"/>
       <c r="Q55" s="79">
-        <f t="shared" ref="Q55" si="4">SUM(D55:O55)</f>
-        <v>-3009946.9</v>
-      </c>
-    </row>
-    <row r="56" spans="2:17" ht="15" thickBot="1">
+        <f t="shared" si="0"/>
+        <v>-281448.59999999998</v>
+      </c>
+    </row>
+    <row r="56" spans="2:17" ht="15.75" thickBot="1">
       <c r="B56" s="104"/>
       <c r="C56" s="18"/>
       <c r="D56" s="85"/>
@@ -4739,62 +4711,51 @@
       <c r="P56" s="86"/>
       <c r="Q56" s="86"/>
     </row>
-    <row r="57" spans="2:17" ht="15" thickTop="1">
+    <row r="57" spans="2:17" ht="15.75" thickTop="1">
       <c r="B57" s="59" t="s">
         <v>31</v>
       </c>
       <c r="D57" s="89">
-        <f t="shared" ref="D57:O57" si="5">D7-D54+(D28+D48)-(D50+D51+D52)+D55</f>
-        <v>25093226.800000004</v>
+        <f t="shared" ref="D57" si="3">D7-D54+(D28+D48)-(D50+D51+D52)+D55</f>
+        <v>25033055.399999999</v>
       </c>
       <c r="E57" s="89">
-        <f t="shared" si="5"/>
-        <v>22432525.300000001</v>
+        <v>0</v>
       </c>
       <c r="F57" s="89">
-        <f t="shared" si="5"/>
-        <v>24874071.399999995</v>
+        <v>0</v>
       </c>
       <c r="G57" s="89">
-        <f t="shared" si="5"/>
-        <v>22594678.300000001</v>
+        <v>0</v>
       </c>
       <c r="H57" s="89">
-        <f t="shared" si="5"/>
-        <v>22331883</v>
+        <v>0</v>
       </c>
       <c r="I57" s="89">
-        <f t="shared" si="5"/>
-        <v>23092990.300000001</v>
+        <v>0</v>
       </c>
       <c r="J57" s="89">
-        <f t="shared" si="5"/>
-        <v>25194299.199999992</v>
+        <v>0</v>
       </c>
       <c r="K57" s="89">
-        <f t="shared" si="5"/>
-        <v>24923631.499999996</v>
+        <v>0</v>
       </c>
       <c r="L57" s="89">
-        <f t="shared" si="5"/>
-        <v>23246178</v>
+        <v>0</v>
       </c>
       <c r="M57" s="89">
-        <f t="shared" si="5"/>
-        <v>24480400.199999992</v>
+        <v>0</v>
       </c>
       <c r="N57" s="89">
-        <f t="shared" si="5"/>
-        <v>24738384.300000001</v>
+        <v>0</v>
       </c>
       <c r="O57" s="89">
-        <f t="shared" si="5"/>
-        <v>25879986.200000003</v>
+        <v>0</v>
       </c>
       <c r="P57" s="79"/>
       <c r="Q57" s="79">
-        <f t="shared" ref="Q57" si="6">SUM(D57:O57)</f>
-        <v>288882254.5</v>
+        <f t="shared" si="0"/>
+        <v>25033055.399999999</v>
       </c>
     </row>
     <row r="58" spans="2:17">
@@ -4816,7 +4777,7 @@
     </row>
     <row r="59" spans="2:17" s="1" customFormat="1" ht="18" customHeight="1">
       <c r="B59" s="47" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C59" s="4"/>
       <c r="D59" s="106"/>
@@ -4832,11 +4793,11 @@
       <c r="N59" s="106"/>
       <c r="O59" s="106"/>
       <c r="P59" s="106"/>
-      <c r="Q59" s="107" t="s">
+      <c r="Q59" s="110" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="60" spans="2:17" ht="15.6">
+    <row r="60" spans="2:17" ht="15.75">
       <c r="B60" s="48"/>
       <c r="D60" s="92" t="s">
         <v>1</v>
@@ -4876,7 +4837,7 @@
       </c>
       <c r="P60" s="100"/>
       <c r="Q60" s="99" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="61" spans="2:17" s="1" customFormat="1">
@@ -4923,44 +4884,45 @@
         <v>125</v>
       </c>
       <c r="D63" s="90">
-        <v>68129.5</v>
+        <v>98126.2</v>
       </c>
       <c r="E63" s="90">
-        <v>31851.1</v>
+        <v>0</v>
       </c>
       <c r="F63" s="90">
-        <v>69757.399999999994</v>
+        <v>0</v>
       </c>
       <c r="G63" s="90">
-        <v>38272</v>
+        <v>0</v>
       </c>
       <c r="H63" s="90">
-        <v>39155.9</v>
+        <v>0</v>
       </c>
       <c r="I63" s="90">
-        <v>60933.7</v>
+        <v>0</v>
       </c>
       <c r="J63" s="90">
-        <v>72597</v>
+        <v>0</v>
       </c>
       <c r="K63" s="90">
-        <v>50432.9</v>
+        <v>0</v>
       </c>
       <c r="L63" s="90">
-        <v>29883.9</v>
+        <v>0</v>
       </c>
       <c r="M63" s="90">
-        <v>39119.1</v>
+        <v>0</v>
       </c>
       <c r="N63" s="90">
-        <v>61762.700000000004</v>
+        <v>0</v>
       </c>
       <c r="O63" s="90">
-        <v>99370.3</v>
+        <v>0</v>
       </c>
       <c r="P63" s="91"/>
       <c r="Q63" s="91">
-        <v>661265.5</v>
+        <f>D63</f>
+        <v>98126.2</v>
       </c>
     </row>
     <row r="64" spans="2:17">
@@ -4968,44 +4930,45 @@
         <v>32</v>
       </c>
       <c r="D64" s="90">
-        <v>2519528.2000000002</v>
+        <v>2486272.5</v>
       </c>
       <c r="E64" s="90">
-        <v>2335461.5</v>
+        <v>0</v>
       </c>
       <c r="F64" s="90">
-        <v>2517299.4</v>
+        <v>0</v>
       </c>
       <c r="G64" s="90">
-        <v>2118283.4</v>
+        <v>0</v>
       </c>
       <c r="H64" s="90">
-        <v>1988167.4</v>
+        <v>0</v>
       </c>
       <c r="I64" s="90">
-        <v>2219657.5</v>
+        <v>0</v>
       </c>
       <c r="J64" s="90">
-        <v>2566376.4</v>
+        <v>0</v>
       </c>
       <c r="K64" s="90">
-        <v>2555429.5</v>
+        <v>0</v>
       </c>
       <c r="L64" s="90">
-        <v>2204194.6</v>
+        <v>0</v>
       </c>
       <c r="M64" s="90">
-        <v>2374998.4</v>
+        <v>0</v>
       </c>
       <c r="N64" s="90">
-        <v>2488340.2000000002</v>
+        <v>0</v>
       </c>
       <c r="O64" s="90">
-        <v>2571850.6</v>
+        <v>0</v>
       </c>
       <c r="P64" s="91"/>
       <c r="Q64" s="91">
-        <v>28459587.100000001</v>
+        <f t="shared" ref="Q64:Q70" si="4">D64</f>
+        <v>2486272.5</v>
       </c>
     </row>
     <row r="65" spans="2:17">
@@ -5013,44 +4976,45 @@
         <v>53</v>
       </c>
       <c r="D65" s="90">
-        <v>11309</v>
+        <v>11296.8</v>
       </c>
       <c r="E65" s="90">
-        <v>8492.7000000000007</v>
+        <v>0</v>
       </c>
       <c r="F65" s="90">
-        <v>14432.6</v>
+        <v>0</v>
       </c>
       <c r="G65" s="90">
-        <v>15264.8</v>
+        <v>0</v>
       </c>
       <c r="H65" s="90">
-        <v>11089.6</v>
+        <v>0</v>
       </c>
       <c r="I65" s="90">
-        <v>11995.7</v>
+        <v>0</v>
       </c>
       <c r="J65" s="90">
-        <v>9807.7999999999993</v>
+        <v>0</v>
       </c>
       <c r="K65" s="90">
-        <v>12739</v>
+        <v>0</v>
       </c>
       <c r="L65" s="90">
-        <v>12332.5</v>
+        <v>0</v>
       </c>
       <c r="M65" s="90">
-        <v>17819</v>
+        <v>0</v>
       </c>
       <c r="N65" s="90">
-        <v>15381.7</v>
+        <v>0</v>
       </c>
       <c r="O65" s="90">
-        <v>9760.5</v>
+        <v>0</v>
       </c>
       <c r="P65" s="91"/>
       <c r="Q65" s="91">
-        <v>150424.90000000002</v>
+        <f t="shared" si="4"/>
+        <v>11296.8</v>
       </c>
     </row>
     <row r="66" spans="2:17">
@@ -5058,44 +5022,45 @@
         <v>39</v>
       </c>
       <c r="D66" s="90">
-        <v>15763.6</v>
+        <v>23532.6</v>
       </c>
       <c r="E66" s="90">
-        <v>16730.7</v>
+        <v>0</v>
       </c>
       <c r="F66" s="90">
-        <v>15053.5</v>
+        <v>0</v>
       </c>
       <c r="G66" s="90">
-        <v>18091.8</v>
+        <v>0</v>
       </c>
       <c r="H66" s="90">
-        <v>19963.8</v>
+        <v>0</v>
       </c>
       <c r="I66" s="90">
-        <v>13665.6</v>
+        <v>0</v>
       </c>
       <c r="J66" s="90">
-        <v>15915.7</v>
+        <v>0</v>
       </c>
       <c r="K66" s="90">
-        <v>20187.5</v>
+        <v>0</v>
       </c>
       <c r="L66" s="90">
-        <v>21007.4</v>
+        <v>0</v>
       </c>
       <c r="M66" s="90">
-        <v>18338.400000000001</v>
+        <v>0</v>
       </c>
       <c r="N66" s="90">
-        <v>44372.6</v>
+        <v>0</v>
       </c>
       <c r="O66" s="90">
-        <v>10947</v>
+        <v>0</v>
       </c>
       <c r="P66" s="91"/>
       <c r="Q66" s="91">
-        <v>230037.6</v>
+        <f t="shared" si="4"/>
+        <v>23532.6</v>
       </c>
     </row>
     <row r="67" spans="2:17" s="1" customFormat="1">
@@ -5104,34 +5069,34 @@
       </c>
       <c r="C67" s="24"/>
       <c r="D67" s="90">
-        <v>0</v>
+        <v>404.9</v>
       </c>
       <c r="E67" s="90">
         <v>0</v>
       </c>
       <c r="F67" s="90">
-        <v>107.3</v>
+        <v>0</v>
       </c>
       <c r="G67" s="90">
-        <v>223</v>
+        <v>0</v>
       </c>
       <c r="H67" s="90">
         <v>0</v>
       </c>
       <c r="I67" s="90">
-        <v>338.9</v>
+        <v>0</v>
       </c>
       <c r="J67" s="90">
         <v>0</v>
       </c>
       <c r="K67" s="90">
-        <v>216.6</v>
+        <v>0</v>
       </c>
       <c r="L67" s="90">
         <v>0</v>
       </c>
       <c r="M67" s="90">
-        <v>162</v>
+        <v>0</v>
       </c>
       <c r="N67" s="90">
         <v>0</v>
@@ -5141,7 +5106,8 @@
       </c>
       <c r="P67" s="91"/>
       <c r="Q67" s="93">
-        <v>1047.8000000000002</v>
+        <f t="shared" si="4"/>
+        <v>404.9</v>
       </c>
     </row>
     <row r="68" spans="2:17" s="1" customFormat="1">
@@ -5150,44 +5116,45 @@
       </c>
       <c r="C68" s="24"/>
       <c r="D68" s="90">
-        <v>-10715.4</v>
+        <v>-22912.799999999999</v>
       </c>
       <c r="E68" s="90">
-        <v>20718</v>
+        <v>0</v>
       </c>
       <c r="F68" s="90">
-        <v>-218.6</v>
+        <v>0</v>
       </c>
       <c r="G68" s="90">
-        <v>740</v>
+        <v>0</v>
       </c>
       <c r="H68" s="90">
-        <v>11707.4</v>
+        <v>0</v>
       </c>
       <c r="I68" s="90">
-        <v>12872</v>
+        <v>0</v>
       </c>
       <c r="J68" s="90">
-        <v>6761.6</v>
+        <v>0</v>
       </c>
       <c r="K68" s="90">
-        <v>-9240.4</v>
+        <v>0</v>
       </c>
       <c r="L68" s="90">
-        <v>-10297.9</v>
+        <v>0</v>
       </c>
       <c r="M68" s="90">
-        <v>2236.9</v>
+        <v>0</v>
       </c>
       <c r="N68" s="90">
-        <v>-15341</v>
+        <v>0</v>
       </c>
       <c r="O68" s="90">
-        <v>-8655.1</v>
+        <v>0</v>
       </c>
       <c r="P68" s="91"/>
       <c r="Q68" s="90">
-        <v>567.49999999999818</v>
+        <f t="shared" si="4"/>
+        <v>-22912.799999999999</v>
       </c>
     </row>
     <row r="69" spans="2:17">
@@ -5196,44 +5163,45 @@
       </c>
       <c r="C69" s="19"/>
       <c r="D69" s="90">
-        <v>347304.9</v>
+        <v>346210.7</v>
       </c>
       <c r="E69" s="90">
-        <v>276205.40000000002</v>
+        <v>0</v>
       </c>
       <c r="F69" s="90">
-        <v>341193.9</v>
+        <v>0</v>
       </c>
       <c r="G69" s="90">
-        <v>312016.59999999998</v>
+        <v>0</v>
       </c>
       <c r="H69" s="90">
-        <v>175192</v>
+        <v>0</v>
       </c>
       <c r="I69" s="90">
-        <v>206088.9</v>
+        <v>0</v>
       </c>
       <c r="J69" s="90">
-        <v>351317.4</v>
+        <v>0</v>
       </c>
       <c r="K69" s="90">
-        <v>327118</v>
+        <v>0</v>
       </c>
       <c r="L69" s="90">
-        <v>345747.4</v>
+        <v>0</v>
       </c>
       <c r="M69" s="90">
-        <v>347549.2</v>
+        <v>0</v>
       </c>
       <c r="N69" s="90">
-        <v>352737.8</v>
+        <v>0</v>
       </c>
       <c r="O69" s="90">
-        <v>341697.8</v>
+        <v>0</v>
       </c>
       <c r="P69" s="91"/>
       <c r="Q69" s="91">
-        <v>3724169.3</v>
+        <f t="shared" si="4"/>
+        <v>346210.7</v>
       </c>
     </row>
     <row r="70" spans="2:17">
@@ -5242,44 +5210,45 @@
       </c>
       <c r="C70" s="19"/>
       <c r="D70" s="90">
-        <v>2951319.8000000003</v>
+        <v>2942930.9000000004</v>
       </c>
       <c r="E70" s="90">
-        <v>2689459.4000000004</v>
+        <v>0</v>
       </c>
       <c r="F70" s="90">
-        <v>2957625.4999999995</v>
+        <v>0</v>
       </c>
       <c r="G70" s="90">
-        <v>2502891.5999999996</v>
+        <v>0</v>
       </c>
       <c r="H70" s="90">
-        <v>2245276.0999999996</v>
+        <v>0</v>
       </c>
       <c r="I70" s="90">
-        <v>2525552.3000000003</v>
+        <v>0</v>
       </c>
       <c r="J70" s="90">
-        <v>3022775.9</v>
+        <v>0</v>
       </c>
       <c r="K70" s="90">
-        <v>2956883.1</v>
+        <v>0</v>
       </c>
       <c r="L70" s="90">
-        <v>2602867.9</v>
+        <v>0</v>
       </c>
       <c r="M70" s="90">
-        <v>2800223</v>
+        <v>0</v>
       </c>
       <c r="N70" s="90">
-        <v>2947254.0000000005</v>
+        <v>0</v>
       </c>
       <c r="O70" s="90">
-        <v>3024971.0999999996</v>
+        <v>0</v>
       </c>
       <c r="P70" s="91"/>
       <c r="Q70" s="91">
-        <v>33227099.700000003</v>
+        <f t="shared" si="4"/>
+        <v>2942930.9000000004</v>
       </c>
     </row>
     <row r="71" spans="2:17">
@@ -5306,44 +5275,45 @@
       </c>
       <c r="C72" s="19"/>
       <c r="D72" s="78">
-        <v>21763599.5</v>
+        <v>21651871.5</v>
       </c>
       <c r="E72" s="78">
-        <v>19591067.100000001</v>
+        <v>0</v>
       </c>
       <c r="F72" s="78">
-        <v>21577914.399999999</v>
+        <v>0</v>
       </c>
       <c r="G72" s="78">
-        <v>19669729.300000001</v>
+        <v>0</v>
       </c>
       <c r="H72" s="78">
-        <v>19906583.100000001</v>
+        <v>0</v>
       </c>
       <c r="I72" s="78">
-        <v>20283093.100000001</v>
+        <v>0</v>
       </c>
       <c r="J72" s="78">
-        <v>21727628.600000001</v>
+        <v>0</v>
       </c>
       <c r="K72" s="78">
-        <v>21920104.800000001</v>
+        <v>0</v>
       </c>
       <c r="L72" s="78">
-        <v>20411543.699999999</v>
+        <v>0</v>
       </c>
       <c r="M72" s="78">
-        <v>21508636.300000001</v>
+        <v>0</v>
       </c>
       <c r="N72" s="78">
-        <v>21681086.699999999</v>
+        <v>0</v>
       </c>
       <c r="O72" s="78">
-        <v>22442772.100000001</v>
+        <v>0</v>
       </c>
       <c r="P72" s="79"/>
       <c r="Q72" s="79">
-        <v>252483758.69999999</v>
+        <f>D72</f>
+        <v>21651871.5</v>
       </c>
     </row>
     <row r="73" spans="2:17">
@@ -5352,44 +5322,45 @@
       </c>
       <c r="C73" s="19"/>
       <c r="D73" s="78">
-        <v>702051.59677419357</v>
+        <v>698447.46774193551</v>
       </c>
       <c r="E73" s="78">
-        <v>699680.96785714291</v>
+        <v>0</v>
       </c>
       <c r="F73" s="78">
-        <v>696061.7548387096</v>
+        <v>0</v>
       </c>
       <c r="G73" s="78">
-        <v>655657.64333333331</v>
+        <v>0</v>
       </c>
       <c r="H73" s="78">
-        <v>642147.84193548397</v>
+        <v>0</v>
       </c>
       <c r="I73" s="78">
-        <v>676103.10333333339</v>
+        <v>0</v>
       </c>
       <c r="J73" s="78">
-        <v>700891.2451612904</v>
+        <v>0</v>
       </c>
       <c r="K73" s="78">
-        <v>707100.15483870974</v>
+        <v>0</v>
       </c>
       <c r="L73" s="78">
-        <v>680384.78999999992</v>
+        <v>0</v>
       </c>
       <c r="M73" s="78">
-        <v>693826.97741935484</v>
+        <v>0</v>
       </c>
       <c r="N73" s="78">
-        <v>722702.89</v>
+        <v>0</v>
       </c>
       <c r="O73" s="78">
-        <v>723960.3903225807</v>
+        <v>0</v>
       </c>
       <c r="P73" s="79"/>
       <c r="Q73" s="79">
-        <v>691714.11298451107</v>
+        <f>D73</f>
+        <v>698447.46774193551</v>
       </c>
     </row>
     <row r="74" spans="2:17">
@@ -5416,57 +5387,45 @@
       </c>
       <c r="C75" s="17"/>
       <c r="D75" s="89">
-        <f t="shared" ref="D75:O75" si="7">D57-(D70+D72)</f>
-        <v>378307.50000000373</v>
+        <v>-279126.89999999106</v>
       </c>
       <c r="E75" s="89">
-        <f t="shared" si="7"/>
-        <v>151998.80000000075</v>
+        <v>0</v>
       </c>
       <c r="F75" s="89">
-        <f t="shared" si="7"/>
-        <v>338531.49999999627</v>
+        <v>0</v>
       </c>
       <c r="G75" s="89">
-        <f t="shared" si="7"/>
-        <v>422057.40000000224</v>
+        <v>0</v>
       </c>
       <c r="H75" s="89">
-        <f t="shared" si="7"/>
-        <v>180023.79999999702</v>
+        <v>0</v>
       </c>
       <c r="I75" s="89">
-        <f t="shared" si="7"/>
-        <v>284344.89999999851</v>
+        <v>0</v>
       </c>
       <c r="J75" s="89">
-        <f t="shared" si="7"/>
-        <v>443894.6999999918</v>
+        <v>0</v>
       </c>
       <c r="K75" s="89">
-        <f t="shared" si="7"/>
-        <v>46643.59999999404</v>
+        <v>0</v>
       </c>
       <c r="L75" s="89">
-        <f t="shared" si="7"/>
-        <v>231766.40000000224</v>
+        <v>0</v>
       </c>
       <c r="M75" s="89">
-        <f t="shared" si="7"/>
-        <v>171540.89999999106</v>
+        <v>0</v>
       </c>
       <c r="N75" s="89">
-        <f t="shared" si="7"/>
-        <v>110043.60000000149</v>
+        <v>0</v>
       </c>
       <c r="O75" s="89">
-        <f t="shared" si="7"/>
-        <v>412243</v>
+        <v>0</v>
       </c>
       <c r="P75" s="79"/>
       <c r="Q75" s="79">
-        <f>SUM(D75:O75)</f>
-        <v>3171396.0999999791</v>
+        <f>D75</f>
+        <v>-279126.89999999106</v>
       </c>
     </row>
     <row r="76" spans="2:17">
@@ -5475,60 +5434,48 @@
       </c>
       <c r="C76" s="18"/>
       <c r="D76" s="94">
-        <f t="shared" ref="D76:O76" si="8">IF(D57&gt;0,D75/D57,"")</f>
-        <v>1.5076080211414008E-2</v>
-      </c>
-      <c r="E76" s="94">
-        <f t="shared" si="8"/>
-        <v>6.7758220693949576E-3</v>
-      </c>
-      <c r="F76" s="94">
-        <f t="shared" si="8"/>
-        <v>1.360981459593287E-2</v>
-      </c>
-      <c r="G76" s="94">
-        <f t="shared" si="8"/>
-        <v>1.8679504722136371E-2</v>
-      </c>
-      <c r="H76" s="94">
-        <f t="shared" si="8"/>
-        <v>8.0612906668012293E-3</v>
-      </c>
-      <c r="I76" s="94">
-        <f t="shared" si="8"/>
-        <v>1.2313039424781576E-2</v>
-      </c>
-      <c r="J76" s="94">
-        <f t="shared" si="8"/>
-        <v>1.7618854824110047E-2</v>
-      </c>
-      <c r="K76" s="94">
-        <f t="shared" si="8"/>
-        <v>1.8714608262441227E-3</v>
-      </c>
-      <c r="L76" s="94">
-        <f t="shared" si="8"/>
-        <v>9.9700862653638051E-3</v>
-      </c>
-      <c r="M76" s="94">
-        <f t="shared" si="8"/>
-        <v>7.0072751506730317E-3</v>
-      </c>
-      <c r="N76" s="94">
-        <f t="shared" si="8"/>
-        <v>4.4482937392156807E-3</v>
-      </c>
-      <c r="O76" s="94">
-        <f t="shared" si="8"/>
-        <v>1.5929027040980415E-2</v>
+        <v>-1.1479298611300804E-2</v>
+      </c>
+      <c r="E76" s="94" t="s">
+        <v>129</v>
+      </c>
+      <c r="F76" s="94" t="s">
+        <v>129</v>
+      </c>
+      <c r="G76" s="94" t="s">
+        <v>129</v>
+      </c>
+      <c r="H76" s="94" t="s">
+        <v>129</v>
+      </c>
+      <c r="I76" s="94" t="s">
+        <v>129</v>
+      </c>
+      <c r="J76" s="94" t="s">
+        <v>129</v>
+      </c>
+      <c r="K76" s="94" t="s">
+        <v>129</v>
+      </c>
+      <c r="L76" s="94" t="s">
+        <v>129</v>
+      </c>
+      <c r="M76" s="94" t="s">
+        <v>129</v>
+      </c>
+      <c r="N76" s="94" t="s">
+        <v>129</v>
+      </c>
+      <c r="O76" s="94" t="s">
+        <v>129</v>
       </c>
       <c r="P76" s="94"/>
       <c r="Q76" s="79">
-        <f>AVERAGE(D76:O76)</f>
-        <v>1.0946712461420677E-2</v>
-      </c>
-    </row>
-    <row r="77" spans="2:17" ht="15" thickBot="1">
+        <f>D76</f>
+        <v>-1.1479298611300804E-2</v>
+      </c>
+    </row>
+    <row r="77" spans="2:17" ht="15.75" thickBot="1">
       <c r="B77" s="104"/>
       <c r="C77" s="26"/>
       <c r="D77" s="87"/>
@@ -5546,62 +5493,50 @@
       <c r="P77" s="79"/>
       <c r="Q77" s="88"/>
     </row>
-    <row r="78" spans="2:17" ht="15" thickTop="1">
+    <row r="78" spans="2:17" ht="15.75" thickTop="1">
       <c r="B78" s="59" t="s">
         <v>36</v>
       </c>
       <c r="D78" s="89">
-        <f t="shared" ref="D78:O78" si="9">(D70+D72)+D75</f>
-        <v>25093226.800000004</v>
+        <v>24315675.500000007</v>
       </c>
       <c r="E78" s="89">
-        <f t="shared" si="9"/>
-        <v>22432525.300000001</v>
+        <v>0</v>
       </c>
       <c r="F78" s="89">
-        <f t="shared" si="9"/>
-        <v>24874071.399999995</v>
+        <v>0</v>
       </c>
       <c r="G78" s="89">
-        <f t="shared" si="9"/>
-        <v>22594678.300000001</v>
+        <v>0</v>
       </c>
       <c r="H78" s="89">
-        <f t="shared" si="9"/>
-        <v>22331883</v>
+        <v>0</v>
       </c>
       <c r="I78" s="89">
-        <f t="shared" si="9"/>
-        <v>23092990.300000001</v>
+        <v>0</v>
       </c>
       <c r="J78" s="89">
-        <f t="shared" si="9"/>
-        <v>25194299.199999992</v>
+        <v>0</v>
       </c>
       <c r="K78" s="89">
-        <f t="shared" si="9"/>
-        <v>24923631.499999996</v>
+        <v>0</v>
       </c>
       <c r="L78" s="89">
-        <f t="shared" si="9"/>
-        <v>23246178</v>
+        <v>0</v>
       </c>
       <c r="M78" s="89">
-        <f t="shared" si="9"/>
-        <v>24480400.199999992</v>
+        <v>0</v>
       </c>
       <c r="N78" s="89">
-        <f t="shared" si="9"/>
-        <v>24738384.300000001</v>
+        <v>0</v>
       </c>
       <c r="O78" s="89">
-        <f t="shared" si="9"/>
-        <v>25879986.200000003</v>
+        <v>0</v>
       </c>
       <c r="P78" s="79"/>
-      <c r="Q78" s="79">
-        <f>SUM(D78:O78)</f>
-        <v>288882254.5</v>
+      <c r="Q78" s="82">
+        <f>D78</f>
+        <v>24315675.500000007</v>
       </c>
     </row>
     <row r="79" spans="2:17">
@@ -5706,15 +5641,15 @@
       <c r="D86" s="12"/>
       <c r="Q86" s="91"/>
     </row>
-    <row r="87" spans="2:17" ht="15.6">
+    <row r="87" spans="2:17" ht="15.75">
       <c r="B87" s="35"/>
       <c r="D87" s="12"/>
       <c r="Q87" s="91"/>
     </row>
-    <row r="88" spans="2:17" ht="15.6">
+    <row r="88" spans="2:17" ht="15.75">
       <c r="B88" s="35"/>
     </row>
-    <row r="89" spans="2:17" ht="15.6">
+    <row r="89" spans="2:17" ht="15.75">
       <c r="B89" s="35"/>
     </row>
   </sheetData>

--- a/Oil_current.xlsx
+++ b/Oil_current.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="V:\Information Management\Info Sharing and Tracking\Product Services\Operations\Product Creation\ST3\ST3s_Report_Prep\All_Pages_Content_Update\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2737612-7BCE-41D6-9D5B-E9D4610A08E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94398B9E-ECF1-45AE-B4B7-1DDEB0DC2416}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="130">
   <si>
     <t>Reporting Adjustment</t>
   </si>
@@ -473,13 +473,13 @@
     <t>Nonupgraded</t>
   </si>
   <si>
-    <t xml:space="preserve"> Run Date:  27 February 2026</t>
-  </si>
-  <si>
     <t>2026</t>
   </si>
   <si>
     <t/>
+  </si>
+  <si>
+    <t xml:space="preserve"> Run Date:  27 April 2026</t>
   </si>
 </sst>
 </file>
@@ -487,12 +487,12 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="6">
-    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="164" formatCode="#,##0.0"/>
-    <numFmt numFmtId="165" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="166" formatCode="0.00_)"/>
-    <numFmt numFmtId="167" formatCode="0____"/>
-    <numFmt numFmtId="168" formatCode="0.0"/>
+    <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="#,##0.0"/>
+    <numFmt numFmtId="166" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="167" formatCode="0.00_)"/>
+    <numFmt numFmtId="168" formatCode="0____"/>
+    <numFmt numFmtId="169" formatCode="0.0"/>
   </numFmts>
   <fonts count="31">
     <font>
@@ -712,7 +712,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -802,17 +802,28 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="double">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
     <xf numFmtId="4" fontId="11" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="0">
+    <xf numFmtId="167" fontId="12" fillId="0" borderId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="40" fontId="13" fillId="0" borderId="0">
@@ -823,7 +834,7 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0">
       <alignment textRotation="90"/>
     </xf>
-    <xf numFmtId="167" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="168" fontId="16" fillId="0" borderId="0"/>
     <xf numFmtId="39" fontId="17" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
@@ -835,7 +846,7 @@
     </xf>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="112">
+  <cellXfs count="113">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -848,23 +859,23 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -876,13 +887,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" indent="6"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -892,7 +903,7 @@
       <alignment horizontal="left" indent="3"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" indent="3"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -912,15 +923,15 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -929,13 +940,13 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="25" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="25" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="27" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="27" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -966,13 +977,13 @@
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="29" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="29" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="29" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="29" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="3"/>
     </xf>
-    <xf numFmtId="164" fontId="29" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="29" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" indent="6"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -981,8 +992,8 @@
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="24" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="24" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="24" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="24" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="24" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -995,63 +1006,63 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="6"/>
     </xf>
-    <xf numFmtId="165" fontId="29" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="29" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="29" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="29" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="29" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="29" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="29" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="29" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="29" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="29" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="29" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="29" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="29" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="29" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="29" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="29" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="29" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="29" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="29" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="29" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="29" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="29" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="2" fillId="0" borderId="0" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="2" fillId="0" borderId="0" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="2" fillId="0" borderId="0" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1067,17 +1078,22 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="16">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -1634,11 +1650,11 @@
     </row>
     <row r="3" spans="1:63" s="2" customFormat="1" ht="19.5" customHeight="1">
       <c r="G3" s="33"/>
-      <c r="H3" s="108" t="s">
+      <c r="H3" s="111" t="s">
         <v>120</v>
       </c>
-      <c r="I3" s="108"/>
-      <c r="J3" s="108"/>
+      <c r="I3" s="111"/>
+      <c r="J3" s="111"/>
       <c r="K3" s="34"/>
       <c r="M3" s="2" t="s">
         <v>38</v>
@@ -2834,17 +2850,17 @@
     </row>
     <row r="3" spans="2:22" s="2" customFormat="1" ht="19.5" customHeight="1">
       <c r="G3" s="33"/>
-      <c r="H3" s="108" t="s">
+      <c r="H3" s="111" t="s">
         <v>120</v>
       </c>
-      <c r="I3" s="108"/>
-      <c r="J3" s="108"/>
+      <c r="I3" s="111"/>
+      <c r="J3" s="111"/>
       <c r="K3" s="34"/>
       <c r="Q3"/>
     </row>
     <row r="4" spans="2:22" ht="22.5" customHeight="1">
       <c r="B4" s="47" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C4" s="22"/>
       <c r="D4" s="1"/>
@@ -2905,7 +2921,7 @@
       </c>
       <c r="P5" s="3"/>
       <c r="Q5" s="29" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="6" spans="2:22" s="1" customFormat="1">
@@ -2920,13 +2936,13 @@
       </c>
       <c r="C7"/>
       <c r="D7" s="90">
-        <v>9791712</v>
+        <v>9791771.6999999993</v>
       </c>
       <c r="E7" s="16">
-        <v>0</v>
+        <v>10401385.1</v>
       </c>
       <c r="F7" s="16">
-        <v>0</v>
+        <v>10278045.199999999</v>
       </c>
       <c r="G7" s="16">
         <v>0</v>
@@ -2957,7 +2973,7 @@
       </c>
       <c r="P7" s="8"/>
       <c r="Q7" s="91">
-        <v>9791712</v>
+        <v>9791771.6999999993</v>
       </c>
       <c r="V7" s="16"/>
     </row>
@@ -3021,13 +3037,13 @@
         <v>25</v>
       </c>
       <c r="D11" s="90">
-        <v>1628795.8</v>
+        <v>1598504.2</v>
       </c>
       <c r="E11" s="16">
-        <v>0</v>
+        <v>1479108.8</v>
       </c>
       <c r="F11" s="16">
-        <v>0</v>
+        <v>1694815.5</v>
       </c>
       <c r="G11" s="16">
         <v>0</v>
@@ -3058,7 +3074,7 @@
       </c>
       <c r="P11" s="8"/>
       <c r="Q11" s="91">
-        <v>1628795.8</v>
+        <v>4772428.5</v>
       </c>
     </row>
     <row r="12" spans="2:22" s="1" customFormat="1">
@@ -3067,13 +3083,13 @@
       </c>
       <c r="C12"/>
       <c r="D12" s="90">
-        <v>339234</v>
+        <v>345410.8</v>
       </c>
       <c r="E12" s="16">
-        <v>0</v>
+        <v>316928.90000000002</v>
       </c>
       <c r="F12" s="16">
-        <v>0</v>
+        <v>345015.6</v>
       </c>
       <c r="G12" s="16">
         <v>0</v>
@@ -3104,7 +3120,7 @@
       </c>
       <c r="P12" s="8"/>
       <c r="Q12" s="91">
-        <v>339234</v>
+        <v>1007355.2999999999</v>
       </c>
     </row>
     <row r="13" spans="2:22">
@@ -3112,13 +3128,13 @@
         <v>27</v>
       </c>
       <c r="D13" s="90">
-        <v>167246.1</v>
+        <v>175112.7</v>
       </c>
       <c r="E13" s="16">
-        <v>0</v>
+        <v>155535.4</v>
       </c>
       <c r="F13" s="16">
-        <v>0</v>
+        <v>167755.6</v>
       </c>
       <c r="G13" s="16">
         <v>0</v>
@@ -3149,7 +3165,7 @@
       </c>
       <c r="P13" s="8"/>
       <c r="Q13" s="91">
-        <v>167246.1</v>
+        <v>498403.69999999995</v>
       </c>
     </row>
     <row r="14" spans="2:22">
@@ -3157,13 +3173,13 @@
         <v>122</v>
       </c>
       <c r="D14" s="96">
-        <v>639936.30000000005</v>
+        <v>655846.19999999995</v>
       </c>
       <c r="E14" s="76">
-        <v>0</v>
+        <v>595209.19999999995</v>
       </c>
       <c r="F14" s="76">
-        <v>0</v>
+        <v>669833.6</v>
       </c>
       <c r="G14" s="75">
         <v>0</v>
@@ -3194,7 +3210,7 @@
       </c>
       <c r="P14" s="76"/>
       <c r="Q14" s="96">
-        <v>639936.30000000005</v>
+        <v>1920889</v>
       </c>
     </row>
     <row r="15" spans="2:22" s="1" customFormat="1">
@@ -3202,13 +3218,13 @@
         <v>114</v>
       </c>
       <c r="D15" s="90">
-        <v>2775212.2</v>
+        <v>2774873.9000000004</v>
       </c>
       <c r="E15" s="16">
-        <v>0</v>
+        <v>2546782.2999999998</v>
       </c>
       <c r="F15" s="16">
-        <v>0</v>
+        <v>2877420.3000000003</v>
       </c>
       <c r="G15" s="16">
         <v>0</v>
@@ -3239,7 +3255,7 @@
       </c>
       <c r="P15" s="8"/>
       <c r="Q15" s="91">
-        <v>2775212.2</v>
+        <v>8199076.5</v>
       </c>
     </row>
     <row r="16" spans="2:22" s="1" customFormat="1">
@@ -3264,13 +3280,13 @@
         <v>30</v>
       </c>
       <c r="D17" s="90">
-        <v>465488.7</v>
+        <v>465994.7</v>
       </c>
       <c r="E17" s="16">
-        <v>0</v>
+        <v>402612.6</v>
       </c>
       <c r="F17" s="16">
-        <v>0</v>
+        <v>408668</v>
       </c>
       <c r="G17" s="16">
         <v>0</v>
@@ -3301,7 +3317,7 @@
       </c>
       <c r="P17" s="8"/>
       <c r="Q17" s="91">
-        <v>465488.7</v>
+        <v>1277275.3</v>
       </c>
     </row>
     <row r="18" spans="2:17">
@@ -3365,13 +3381,13 @@
       </c>
       <c r="C21" s="18"/>
       <c r="D21" s="90">
-        <v>9908622.6999999993</v>
+        <v>9908550</v>
       </c>
       <c r="E21" s="16">
-        <v>0</v>
+        <v>9007844</v>
       </c>
       <c r="F21" s="16">
-        <v>0</v>
+        <v>9954264</v>
       </c>
       <c r="G21" s="16">
         <v>0</v>
@@ -3402,7 +3418,7 @@
       </c>
       <c r="P21" s="8"/>
       <c r="Q21" s="91">
-        <v>9908622.6999999993</v>
+        <v>28870658</v>
       </c>
     </row>
     <row r="22" spans="2:17">
@@ -3414,10 +3430,10 @@
         <v>8723461.9000000004</v>
       </c>
       <c r="E22" s="16">
-        <v>0</v>
+        <v>7442103</v>
       </c>
       <c r="F22" s="16">
-        <v>0</v>
+        <v>8397483.3000000007</v>
       </c>
       <c r="G22" s="16">
         <v>0</v>
@@ -3448,7 +3464,7 @@
       </c>
       <c r="P22" s="8"/>
       <c r="Q22" s="91">
-        <v>8723461.9000000004</v>
+        <v>24563048.200000003</v>
       </c>
     </row>
     <row r="23" spans="2:17">
@@ -3460,10 +3476,10 @@
         <v>-7655105</v>
       </c>
       <c r="E23" s="16">
-        <v>0</v>
+        <v>-6700087.0999999996</v>
       </c>
       <c r="F23" s="16">
-        <v>0</v>
+        <v>-7407328.9000000004</v>
       </c>
       <c r="G23" s="16">
         <v>0</v>
@@ -3494,7 +3510,7 @@
       </c>
       <c r="P23" s="8"/>
       <c r="Q23" s="91">
-        <v>-7655105</v>
+        <v>-21762521</v>
       </c>
     </row>
     <row r="24" spans="2:17">
@@ -3503,13 +3519,13 @@
       </c>
       <c r="C24" s="17"/>
       <c r="D24" s="90">
-        <v>10976979.600000001</v>
+        <v>10976906.899999999</v>
       </c>
       <c r="E24" s="16">
-        <v>0</v>
+        <v>9749859.9000000004</v>
       </c>
       <c r="F24" s="16">
-        <v>0</v>
+        <v>10944418.4</v>
       </c>
       <c r="G24" s="16">
         <v>0</v>
@@ -3540,7 +3556,7 @@
       </c>
       <c r="P24" s="8"/>
       <c r="Q24" s="91">
-        <v>10976979.600000001</v>
+        <v>31671185.200000003</v>
       </c>
     </row>
     <row r="25" spans="2:17">
@@ -3548,13 +3564,13 @@
         <v>28</v>
       </c>
       <c r="D25" s="95">
-        <v>6541474</v>
+        <v>6541236</v>
       </c>
       <c r="E25" s="42">
-        <v>0</v>
+        <v>5775194.9000000004</v>
       </c>
       <c r="F25" s="42">
-        <v>0</v>
+        <v>6311042.0999999996</v>
       </c>
       <c r="G25" s="42">
         <v>0</v>
@@ -3585,7 +3601,7 @@
       </c>
       <c r="P25" s="8"/>
       <c r="Q25" s="98">
-        <v>6541474</v>
+        <v>18627473</v>
       </c>
     </row>
     <row r="26" spans="2:17">
@@ -3593,13 +3609,13 @@
         <v>46</v>
       </c>
       <c r="D26" s="90">
-        <v>17518453.600000001</v>
+        <v>17518142.899999999</v>
       </c>
       <c r="E26" s="16">
-        <v>0</v>
+        <v>15525054.800000001</v>
       </c>
       <c r="F26" s="16">
-        <v>0</v>
+        <v>17255460.5</v>
       </c>
       <c r="G26" s="16">
         <v>0</v>
@@ -3630,7 +3646,7 @@
       </c>
       <c r="P26" s="8"/>
       <c r="Q26" s="91">
-        <v>17518453.600000001</v>
+        <v>50298658.200000003</v>
       </c>
     </row>
     <row r="27" spans="2:17">
@@ -3656,13 +3672,13 @@
       </c>
       <c r="C28" s="17"/>
       <c r="D28" s="90">
-        <v>20759154.5</v>
+        <v>20759011.499999996</v>
       </c>
       <c r="E28" s="16">
-        <v>0</v>
+        <v>18474449.700000003</v>
       </c>
       <c r="F28" s="16">
-        <v>0</v>
+        <v>20541548.800000001</v>
       </c>
       <c r="G28" s="16">
         <v>0</v>
@@ -3693,7 +3709,7 @@
       </c>
       <c r="P28" s="8"/>
       <c r="Q28" s="90">
-        <v>20759154.5</v>
+        <v>59775010</v>
       </c>
     </row>
     <row r="29" spans="2:17">
@@ -3737,13 +3753,13 @@
         <v>49</v>
       </c>
       <c r="D31" s="90">
-        <v>1388226.7</v>
+        <v>1388226.8</v>
       </c>
       <c r="E31" s="16">
-        <v>0</v>
+        <v>1222883.7</v>
       </c>
       <c r="F31" s="16">
-        <v>0</v>
+        <v>1318091.8999999999</v>
       </c>
       <c r="G31" s="16">
         <v>0</v>
@@ -3774,7 +3790,7 @@
       </c>
       <c r="P31" s="8"/>
       <c r="Q31" s="91">
-        <v>1388226.7</v>
+        <v>3929202.4</v>
       </c>
     </row>
     <row r="32" spans="2:17">
@@ -3785,10 +3801,10 @@
         <v>404376.2</v>
       </c>
       <c r="E32" s="16">
-        <v>0</v>
+        <v>358067.1</v>
       </c>
       <c r="F32" s="16">
-        <v>0</v>
+        <v>388650.6</v>
       </c>
       <c r="G32" s="16">
         <v>0</v>
@@ -3819,7 +3835,7 @@
       </c>
       <c r="P32" s="8"/>
       <c r="Q32" s="90">
-        <v>404376.2</v>
+        <v>1151093.8999999999</v>
       </c>
     </row>
     <row r="33" spans="2:17">
@@ -3848,10 +3864,10 @@
         <v>10103.799999999999</v>
       </c>
       <c r="E34" s="16">
-        <v>0</v>
+        <v>10462.299999999999</v>
       </c>
       <c r="F34" s="16">
-        <v>0</v>
+        <v>22910.799999999999</v>
       </c>
       <c r="G34" s="16">
         <v>0</v>
@@ -3882,7 +3898,7 @@
       </c>
       <c r="P34" s="8"/>
       <c r="Q34" s="91">
-        <v>10103.799999999999</v>
+        <v>43476.899999999994</v>
       </c>
     </row>
     <row r="35" spans="2:17">
@@ -3894,10 +3910,10 @@
         <v>11035</v>
       </c>
       <c r="E35" s="16">
-        <v>0</v>
+        <v>9726.9</v>
       </c>
       <c r="F35" s="16">
-        <v>0</v>
+        <v>12144.8</v>
       </c>
       <c r="G35" s="16">
         <v>0</v>
@@ -3928,7 +3944,7 @@
       </c>
       <c r="P35" s="8"/>
       <c r="Q35" s="91">
-        <v>11035</v>
+        <v>32906.699999999997</v>
       </c>
     </row>
     <row r="36" spans="2:17">
@@ -3940,10 +3956,10 @@
         <v>487218.8</v>
       </c>
       <c r="E36" s="16">
-        <v>0</v>
+        <v>419193.2</v>
       </c>
       <c r="F36" s="16">
-        <v>0</v>
+        <v>424689.1</v>
       </c>
       <c r="G36" s="16">
         <v>0</v>
@@ -3974,7 +3990,7 @@
       </c>
       <c r="P36" s="8"/>
       <c r="Q36" s="91">
-        <v>487218.8</v>
+        <v>1331101.1000000001</v>
       </c>
     </row>
     <row r="37" spans="2:17">
@@ -4004,10 +4020,10 @@
         <v>289216.7</v>
       </c>
       <c r="E38" s="16">
-        <v>0</v>
+        <v>261443.1</v>
       </c>
       <c r="F38" s="16">
-        <v>0</v>
+        <v>295219.7</v>
       </c>
       <c r="G38" s="16">
         <v>0</v>
@@ -4038,7 +4054,7 @@
       </c>
       <c r="P38" s="8"/>
       <c r="Q38" s="91">
-        <v>289216.7</v>
+        <v>845879.5</v>
       </c>
     </row>
     <row r="39" spans="2:17">
@@ -4050,10 +4066,10 @@
         <v>325.7</v>
       </c>
       <c r="E39" s="16">
-        <v>0</v>
+        <v>21.3</v>
       </c>
       <c r="F39" s="16">
-        <v>0</v>
+        <v>19.3</v>
       </c>
       <c r="G39" s="16">
         <v>0</v>
@@ -4084,7 +4100,7 @@
       </c>
       <c r="P39" s="8"/>
       <c r="Q39" s="91">
-        <v>325.7</v>
+        <v>366.3</v>
       </c>
     </row>
     <row r="40" spans="2:17">
@@ -4134,10 +4150,10 @@
         <v>540930.4</v>
       </c>
       <c r="E42" s="78">
-        <v>0</v>
+        <v>497870.1</v>
       </c>
       <c r="F42" s="78">
-        <v>0</v>
+        <v>536174.69999999995</v>
       </c>
       <c r="G42" s="78">
         <v>0</v>
@@ -4168,8 +4184,7 @@
       </c>
       <c r="P42" s="79"/>
       <c r="Q42" s="79">
-        <f t="shared" ref="Q42:Q57" si="0">D42</f>
-        <v>540930.4</v>
+        <v>1574975.2</v>
       </c>
     </row>
     <row r="43" spans="2:17">
@@ -4178,14 +4193,13 @@
       </c>
       <c r="C43" s="18"/>
       <c r="D43" s="78">
-        <f>545525.1+761707.6</f>
         <v>1307232.7</v>
       </c>
       <c r="E43" s="78">
-        <v>0</v>
+        <v>1264304.8</v>
       </c>
       <c r="F43" s="78">
-        <v>0</v>
+        <v>1386274.4</v>
       </c>
       <c r="G43" s="78">
         <v>0</v>
@@ -4216,8 +4230,7 @@
       </c>
       <c r="P43" s="79"/>
       <c r="Q43" s="79">
-        <f t="shared" si="0"/>
-        <v>1307232.7</v>
+        <v>3957811.9</v>
       </c>
     </row>
     <row r="44" spans="2:17">
@@ -4229,10 +4242,10 @@
         <v>817025.9</v>
       </c>
       <c r="E44" s="78">
-        <v>0</v>
+        <v>742303.3</v>
       </c>
       <c r="F44" s="78">
-        <v>0</v>
+        <v>918096.4</v>
       </c>
       <c r="G44" s="78">
         <v>0</v>
@@ -4263,8 +4276,7 @@
       </c>
       <c r="P44" s="79"/>
       <c r="Q44" s="79">
-        <f t="shared" si="0"/>
-        <v>817025.9</v>
+        <v>2477425.6</v>
       </c>
     </row>
     <row r="45" spans="2:17">
@@ -4276,10 +4288,10 @@
         <v>304164.7</v>
       </c>
       <c r="E45" s="80">
-        <v>0</v>
+        <v>248678.1</v>
       </c>
       <c r="F45" s="80">
-        <v>0</v>
+        <v>305054.5</v>
       </c>
       <c r="G45" s="80">
         <v>0</v>
@@ -4310,8 +4322,7 @@
       </c>
       <c r="P45" s="80"/>
       <c r="Q45" s="80">
-        <f t="shared" si="0"/>
-        <v>304164.7</v>
+        <v>857897.3</v>
       </c>
     </row>
     <row r="46" spans="2:17">
@@ -4320,14 +4331,13 @@
       </c>
       <c r="C46" s="17"/>
       <c r="D46" s="89">
-        <f t="shared" ref="D46" si="1">SUM(D42:D45)</f>
         <v>2969353.7</v>
       </c>
       <c r="E46" s="89">
-        <v>0</v>
+        <v>2753156.3000000003</v>
       </c>
       <c r="F46" s="89">
-        <v>0</v>
+        <v>3145600</v>
       </c>
       <c r="G46" s="89">
         <v>0</v>
@@ -4358,8 +4368,7 @@
       </c>
       <c r="P46" s="79"/>
       <c r="Q46" s="79">
-        <f t="shared" si="0"/>
-        <v>2969353.7</v>
+        <v>8868110</v>
       </c>
     </row>
     <row r="47" spans="2:17">
@@ -4385,14 +4394,13 @@
         <v>58</v>
       </c>
       <c r="D48" s="89">
-        <f t="shared" ref="D48" si="2">D31+D32+D34+D35+D36+D38+D39+D46</f>
-        <v>5559856.6000000006</v>
+        <v>5559856.7000000011</v>
       </c>
       <c r="E48" s="89">
-        <v>0</v>
+        <v>5034953.9000000004</v>
       </c>
       <c r="F48" s="89">
-        <v>0</v>
+        <v>5607326.2000000002</v>
       </c>
       <c r="G48" s="89">
         <v>0</v>
@@ -4423,8 +4431,7 @@
       </c>
       <c r="P48" s="79"/>
       <c r="Q48" s="79">
-        <f t="shared" si="0"/>
-        <v>5559856.6000000006</v>
+        <v>16202136.800000001</v>
       </c>
     </row>
     <row r="49" spans="2:17">
@@ -4452,10 +4459,10 @@
         <v>209662.3</v>
       </c>
       <c r="E50" s="78">
-        <v>0</v>
+        <v>196874.4</v>
       </c>
       <c r="F50" s="78">
-        <v>0</v>
+        <v>198498.7</v>
       </c>
       <c r="G50" s="78">
         <v>0</v>
@@ -4486,8 +4493,7 @@
       </c>
       <c r="P50" s="79"/>
       <c r="Q50" s="79">
-        <f t="shared" si="0"/>
-        <v>209662.3</v>
+        <v>605035.39999999991</v>
       </c>
     </row>
     <row r="51" spans="2:17">
@@ -4495,13 +4501,13 @@
         <v>22</v>
       </c>
       <c r="D51" s="78">
-        <v>117473.8</v>
+        <v>117361.8</v>
       </c>
       <c r="E51" s="78">
-        <v>0</v>
+        <v>102367.4</v>
       </c>
       <c r="F51" s="78">
-        <v>0</v>
+        <v>118692.6</v>
       </c>
       <c r="G51" s="78">
         <v>0</v>
@@ -4532,8 +4538,7 @@
       </c>
       <c r="P51" s="79"/>
       <c r="Q51" s="79">
-        <f t="shared" si="0"/>
-        <v>117473.8</v>
+        <v>338421.80000000005</v>
       </c>
     </row>
     <row r="52" spans="2:17">
@@ -4541,13 +4546,13 @@
         <v>17</v>
       </c>
       <c r="D52" s="78">
-        <v>395846.40000000002</v>
+        <v>395848.1</v>
       </c>
       <c r="E52" s="78">
-        <v>0</v>
+        <v>351825.7</v>
       </c>
       <c r="F52" s="78">
-        <v>0</v>
+        <v>389791.3</v>
       </c>
       <c r="G52" s="78">
         <v>0</v>
@@ -4578,26 +4583,25 @@
       </c>
       <c r="P52" s="78"/>
       <c r="Q52" s="78">
-        <f t="shared" si="0"/>
-        <v>395846.40000000002</v>
+        <v>1137465.1000000001</v>
       </c>
     </row>
     <row r="53" spans="2:17" ht="14.25" customHeight="1">
       <c r="B53" s="104"/>
       <c r="C53" s="101"/>
-      <c r="D53" s="111"/>
-      <c r="E53" s="107"/>
-      <c r="F53" s="107"/>
-      <c r="G53" s="107"/>
-      <c r="H53" s="107"/>
-      <c r="I53" s="107"/>
-      <c r="J53" s="107"/>
-      <c r="K53" s="107"/>
-      <c r="L53" s="107"/>
-      <c r="M53" s="107"/>
-      <c r="N53" s="107"/>
-      <c r="O53" s="107"/>
-      <c r="P53" s="107"/>
+      <c r="D53" s="108"/>
+      <c r="E53" s="108"/>
+      <c r="F53" s="108"/>
+      <c r="G53" s="108"/>
+      <c r="H53" s="108"/>
+      <c r="I53" s="108"/>
+      <c r="J53" s="108"/>
+      <c r="K53" s="108"/>
+      <c r="L53" s="108"/>
+      <c r="M53" s="108"/>
+      <c r="N53" s="108"/>
+      <c r="O53" s="108"/>
+      <c r="P53" s="108"/>
       <c r="Q53" s="109"/>
     </row>
     <row r="54" spans="2:17" s="1" customFormat="1" ht="15" customHeight="1">
@@ -4606,13 +4610,13 @@
       </c>
       <c r="C54" s="4"/>
       <c r="D54" s="83">
-        <v>10073236.6</v>
+        <v>10401802.9</v>
       </c>
       <c r="E54" s="83">
-        <v>0</v>
+        <v>10278429.9</v>
       </c>
       <c r="F54" s="83">
-        <v>0</v>
+        <v>10007289</v>
       </c>
       <c r="G54" s="83">
         <v>0</v>
@@ -4643,8 +4647,7 @@
       </c>
       <c r="P54" s="83"/>
       <c r="Q54" s="84">
-        <f t="shared" si="0"/>
-        <v>10073236.6</v>
+        <v>10007289</v>
       </c>
     </row>
     <row r="55" spans="2:17">
@@ -4652,13 +4655,13 @@
         <v>50</v>
       </c>
       <c r="D55" s="78">
-        <v>-281448.59999999998</v>
+        <v>62971.3</v>
       </c>
       <c r="E55" s="78">
-        <v>0</v>
+        <v>-12008.8</v>
       </c>
       <c r="F55" s="78">
-        <v>0</v>
+        <v>-19187.599999999999</v>
       </c>
       <c r="G55" s="78">
         <v>0</v>
@@ -4689,8 +4692,7 @@
       </c>
       <c r="P55" s="79"/>
       <c r="Q55" s="79">
-        <f t="shared" si="0"/>
-        <v>-281448.59999999998</v>
+        <v>31774.9</v>
       </c>
     </row>
     <row r="56" spans="2:17" ht="15.75" thickBot="1">
@@ -4716,14 +4718,13 @@
         <v>31</v>
       </c>
       <c r="D57" s="89">
-        <f t="shared" ref="D57" si="3">D7-D54+(D28+D48)-(D50+D51+D52)+D55</f>
-        <v>25033055.399999999</v>
+        <v>25048936.099999994</v>
       </c>
       <c r="E57" s="89">
-        <v>0</v>
+        <v>22969282.5</v>
       </c>
       <c r="F57" s="89">
-        <v>0</v>
+        <v>25693460.999999996</v>
       </c>
       <c r="G57" s="89">
         <v>0</v>
@@ -4754,8 +4755,7 @@
       </c>
       <c r="P57" s="79"/>
       <c r="Q57" s="79">
-        <f t="shared" si="0"/>
-        <v>25033055.399999999</v>
+        <v>73711679.599999994</v>
       </c>
     </row>
     <row r="58" spans="2:17">
@@ -4777,7 +4777,7 @@
     </row>
     <row r="59" spans="2:17" s="1" customFormat="1" ht="18" customHeight="1">
       <c r="B59" s="47" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C59" s="4"/>
       <c r="D59" s="106"/>
@@ -4793,7 +4793,7 @@
       <c r="N59" s="106"/>
       <c r="O59" s="106"/>
       <c r="P59" s="106"/>
-      <c r="Q59" s="110" t="s">
+      <c r="Q59" s="107" t="s">
         <v>13</v>
       </c>
     </row>
@@ -4837,7 +4837,7 @@
       </c>
       <c r="P60" s="100"/>
       <c r="Q60" s="99" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="61" spans="2:17" s="1" customFormat="1">
@@ -4887,10 +4887,10 @@
         <v>98126.2</v>
       </c>
       <c r="E63" s="90">
-        <v>0</v>
+        <v>57853.799999999996</v>
       </c>
       <c r="F63" s="90">
-        <v>0</v>
+        <v>76643.399999999994</v>
       </c>
       <c r="G63" s="90">
         <v>0</v>
@@ -4921,8 +4921,7 @@
       </c>
       <c r="P63" s="91"/>
       <c r="Q63" s="91">
-        <f>D63</f>
-        <v>98126.2</v>
+        <v>232623.4</v>
       </c>
     </row>
     <row r="64" spans="2:17">
@@ -4933,10 +4932,10 @@
         <v>2486272.5</v>
       </c>
       <c r="E64" s="90">
-        <v>0</v>
+        <v>2318442.2000000002</v>
       </c>
       <c r="F64" s="90">
-        <v>0</v>
+        <v>2622767.9</v>
       </c>
       <c r="G64" s="90">
         <v>0</v>
@@ -4967,8 +4966,7 @@
       </c>
       <c r="P64" s="91"/>
       <c r="Q64" s="91">
-        <f t="shared" ref="Q64:Q70" si="4">D64</f>
-        <v>2486272.5</v>
+        <v>7427482.5999999996</v>
       </c>
     </row>
     <row r="65" spans="2:17">
@@ -4976,13 +4974,13 @@
         <v>53</v>
       </c>
       <c r="D65" s="90">
-        <v>11296.8</v>
+        <v>11308.9</v>
       </c>
       <c r="E65" s="90">
-        <v>0</v>
+        <v>9971</v>
       </c>
       <c r="F65" s="90">
-        <v>0</v>
+        <v>9949.4</v>
       </c>
       <c r="G65" s="90">
         <v>0</v>
@@ -5013,8 +5011,7 @@
       </c>
       <c r="P65" s="91"/>
       <c r="Q65" s="91">
-        <f t="shared" si="4"/>
-        <v>11296.8</v>
+        <v>31229.300000000003</v>
       </c>
     </row>
     <row r="66" spans="2:17">
@@ -5025,10 +5022,10 @@
         <v>23532.6</v>
       </c>
       <c r="E66" s="90">
-        <v>0</v>
+        <v>16462.3</v>
       </c>
       <c r="F66" s="90">
-        <v>0</v>
+        <v>14134.8</v>
       </c>
       <c r="G66" s="90">
         <v>0</v>
@@ -5059,8 +5056,7 @@
       </c>
       <c r="P66" s="91"/>
       <c r="Q66" s="91">
-        <f t="shared" si="4"/>
-        <v>23532.6</v>
+        <v>54129.7</v>
       </c>
     </row>
     <row r="67" spans="2:17" s="1" customFormat="1">
@@ -5072,10 +5068,10 @@
         <v>404.9</v>
       </c>
       <c r="E67" s="90">
-        <v>0</v>
+        <v>246.1</v>
       </c>
       <c r="F67" s="90">
-        <v>0</v>
+        <v>320</v>
       </c>
       <c r="G67" s="90">
         <v>0</v>
@@ -5106,8 +5102,7 @@
       </c>
       <c r="P67" s="91"/>
       <c r="Q67" s="93">
-        <f t="shared" si="4"/>
-        <v>404.9</v>
+        <v>971</v>
       </c>
     </row>
     <row r="68" spans="2:17" s="1" customFormat="1">
@@ -5116,13 +5111,13 @@
       </c>
       <c r="C68" s="24"/>
       <c r="D68" s="90">
-        <v>-22912.799999999999</v>
+        <v>-22759.200000000001</v>
       </c>
       <c r="E68" s="90">
-        <v>0</v>
+        <v>-7155.6</v>
       </c>
       <c r="F68" s="90">
-        <v>0</v>
+        <v>1851.2</v>
       </c>
       <c r="G68" s="90">
         <v>0</v>
@@ -5153,8 +5148,7 @@
       </c>
       <c r="P68" s="91"/>
       <c r="Q68" s="90">
-        <f t="shared" si="4"/>
-        <v>-22912.799999999999</v>
+        <v>-28063.600000000002</v>
       </c>
     </row>
     <row r="69" spans="2:17">
@@ -5163,13 +5157,13 @@
       </c>
       <c r="C69" s="19"/>
       <c r="D69" s="90">
-        <v>346210.7</v>
+        <v>345848.1</v>
       </c>
       <c r="E69" s="90">
-        <v>0</v>
+        <v>320501.40000000002</v>
       </c>
       <c r="F69" s="90">
-        <v>0</v>
+        <v>325675.09999999998</v>
       </c>
       <c r="G69" s="90">
         <v>0</v>
@@ -5200,8 +5194,7 @@
       </c>
       <c r="P69" s="91"/>
       <c r="Q69" s="91">
-        <f t="shared" si="4"/>
-        <v>346210.7</v>
+        <v>992024.6</v>
       </c>
     </row>
     <row r="70" spans="2:17">
@@ -5210,13 +5203,13 @@
       </c>
       <c r="C70" s="19"/>
       <c r="D70" s="90">
-        <v>2942930.9000000004</v>
+        <v>2942734</v>
       </c>
       <c r="E70" s="90">
-        <v>0</v>
+        <v>2716321.1999999997</v>
       </c>
       <c r="F70" s="90">
-        <v>0</v>
+        <v>3051341.8</v>
       </c>
       <c r="G70" s="90">
         <v>0</v>
@@ -5247,8 +5240,7 @@
       </c>
       <c r="P70" s="91"/>
       <c r="Q70" s="91">
-        <f t="shared" si="4"/>
-        <v>2942930.9000000004</v>
+        <v>8710397</v>
       </c>
     </row>
     <row r="71" spans="2:17">
@@ -5275,13 +5267,13 @@
       </c>
       <c r="C72" s="19"/>
       <c r="D72" s="78">
-        <v>21651871.5</v>
+        <v>21651866.699999999</v>
       </c>
       <c r="E72" s="78">
-        <v>0</v>
+        <v>19348412.199999999</v>
       </c>
       <c r="F72" s="78">
-        <v>0</v>
+        <v>21686953.300000001</v>
       </c>
       <c r="G72" s="78">
         <v>0</v>
@@ -5312,8 +5304,7 @@
       </c>
       <c r="P72" s="79"/>
       <c r="Q72" s="79">
-        <f>D72</f>
-        <v>21651871.5</v>
+        <v>62687232.200000003</v>
       </c>
     </row>
     <row r="73" spans="2:17">
@@ -5322,13 +5313,13 @@
       </c>
       <c r="C73" s="19"/>
       <c r="D73" s="78">
-        <v>698447.46774193551</v>
+        <v>698447.31290322577</v>
       </c>
       <c r="E73" s="78">
-        <v>0</v>
+        <v>691014.72142857139</v>
       </c>
       <c r="F73" s="78">
-        <v>0</v>
+        <v>699579.1387096775</v>
       </c>
       <c r="G73" s="78">
         <v>0</v>
@@ -5359,8 +5350,7 @@
       </c>
       <c r="P73" s="79"/>
       <c r="Q73" s="79">
-        <f>D73</f>
-        <v>698447.46774193551</v>
+        <v>696347.05768049147</v>
       </c>
     </row>
     <row r="74" spans="2:17">
@@ -5387,13 +5377,13 @@
       </c>
       <c r="C75" s="17"/>
       <c r="D75" s="89">
-        <v>-279126.89999999106</v>
+        <v>454335.39999999478</v>
       </c>
       <c r="E75" s="89">
-        <v>0</v>
+        <v>904549.10000000149</v>
       </c>
       <c r="F75" s="89">
-        <v>0</v>
+        <v>955165.89999999478</v>
       </c>
       <c r="G75" s="89">
         <v>0</v>
@@ -5424,8 +5414,7 @@
       </c>
       <c r="P75" s="79"/>
       <c r="Q75" s="79">
-        <f>D75</f>
-        <v>-279126.89999999106</v>
+        <v>2314050.3999999911</v>
       </c>
     </row>
     <row r="76" spans="2:17">
@@ -5434,45 +5423,44 @@
       </c>
       <c r="C76" s="18"/>
       <c r="D76" s="94">
-        <v>-1.1479298611300804E-2</v>
-      </c>
-      <c r="E76" s="94" t="s">
-        <v>129</v>
-      </c>
-      <c r="F76" s="94" t="s">
-        <v>129</v>
+        <v>1.813791205287936E-2</v>
+      </c>
+      <c r="E76" s="94">
+        <v>3.9380816531818158E-2</v>
+      </c>
+      <c r="F76" s="94">
+        <v>3.7175447091382312E-2</v>
       </c>
       <c r="G76" s="94" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H76" s="94" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="I76" s="94" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="J76" s="94" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="K76" s="94" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="L76" s="94" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="M76" s="94" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="N76" s="94" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="O76" s="94" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="P76" s="94"/>
       <c r="Q76" s="79">
-        <f>D76</f>
-        <v>-1.1479298611300804E-2</v>
+        <v>3.1564725225359941E-2</v>
       </c>
     </row>
     <row r="77" spans="2:17" ht="15.75" thickBot="1">
@@ -5497,46 +5485,45 @@
       <c r="B78" s="59" t="s">
         <v>36</v>
       </c>
-      <c r="D78" s="89">
-        <v>24315675.500000007</v>
-      </c>
-      <c r="E78" s="89">
-        <v>0</v>
-      </c>
-      <c r="F78" s="89">
-        <v>0</v>
-      </c>
-      <c r="G78" s="89">
-        <v>0</v>
-      </c>
-      <c r="H78" s="89">
-        <v>0</v>
-      </c>
-      <c r="I78" s="89">
-        <v>0</v>
-      </c>
-      <c r="J78" s="89">
-        <v>0</v>
-      </c>
-      <c r="K78" s="89">
-        <v>0</v>
-      </c>
-      <c r="L78" s="89">
-        <v>0</v>
-      </c>
-      <c r="M78" s="89">
-        <v>0</v>
-      </c>
-      <c r="N78" s="89">
-        <v>0</v>
-      </c>
-      <c r="O78" s="89">
-        <v>0</v>
-      </c>
-      <c r="P78" s="79"/>
+      <c r="D78" s="112">
+        <v>25048936.099999994</v>
+      </c>
+      <c r="E78" s="112">
+        <v>22969282.5</v>
+      </c>
+      <c r="F78" s="110">
+        <v>25693460.999999996</v>
+      </c>
+      <c r="G78" s="110">
+        <v>0</v>
+      </c>
+      <c r="H78" s="110">
+        <v>0</v>
+      </c>
+      <c r="I78" s="110">
+        <v>0</v>
+      </c>
+      <c r="J78" s="110">
+        <v>0</v>
+      </c>
+      <c r="K78" s="110">
+        <v>0</v>
+      </c>
+      <c r="L78" s="110">
+        <v>0</v>
+      </c>
+      <c r="M78" s="110">
+        <v>0</v>
+      </c>
+      <c r="N78" s="110">
+        <v>0</v>
+      </c>
+      <c r="O78" s="110">
+        <v>0</v>
+      </c>
+      <c r="P78" s="82"/>
       <c r="Q78" s="82">
-        <f>D78</f>
-        <v>24315675.500000007</v>
+        <v>73711679.599999994</v>
       </c>
     </row>
     <row r="79" spans="2:17">

--- a/Oil_current.xlsx
+++ b/Oil_current.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="V:\Information Management\Info Sharing and Tracking\Product Services\Operations\Product Creation\ST3\ST3s_Report_Prep\All_Pages_Content_Update\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\eub.gov.ab.ca\CalFsrv\Share0\Information Management\Info Sharing and Tracking\Product Services\Operations\Product Creation\ST3\ST3s_Report_Prep\All_Pages_Content_Update\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94398B9E-ECF1-45AE-B4B7-1DDEB0DC2416}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E2C96A8-0788-4057-B553-D5936CEB6DD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="130">
   <si>
     <t>Reporting Adjustment</t>
   </si>
@@ -479,7 +479,7 @@
     <t/>
   </si>
   <si>
-    <t xml:space="preserve"> Run Date:  27 April 2026</t>
+    <t xml:space="preserve"> Run Date:  27 May 2026</t>
   </si>
 </sst>
 </file>
@@ -712,7 +712,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -802,17 +802,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="double">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -846,7 +835,7 @@
     </xf>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="113">
+  <cellXfs count="112">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1089,9 +1078,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -2936,16 +2922,16 @@
       </c>
       <c r="C7"/>
       <c r="D7" s="90">
-        <v>9791771.6999999993</v>
+        <v>9791732.8000000007</v>
       </c>
       <c r="E7" s="16">
-        <v>10401385.1</v>
+        <v>10401309.800000001</v>
       </c>
       <c r="F7" s="16">
-        <v>10278045.199999999</v>
+        <v>10278497.800000001</v>
       </c>
       <c r="G7" s="16">
-        <v>0</v>
+        <v>10007626.6</v>
       </c>
       <c r="H7" s="16">
         <v>0</v>
@@ -2973,7 +2959,7 @@
       </c>
       <c r="P7" s="8"/>
       <c r="Q7" s="91">
-        <v>9791771.6999999993</v>
+        <v>9791732.8000000007</v>
       </c>
       <c r="V7" s="16"/>
     </row>
@@ -3037,16 +3023,16 @@
         <v>25</v>
       </c>
       <c r="D11" s="90">
-        <v>1598504.2</v>
+        <v>1586542.4</v>
       </c>
       <c r="E11" s="16">
-        <v>1479108.8</v>
+        <v>1466675.6</v>
       </c>
       <c r="F11" s="16">
-        <v>1694815.5</v>
+        <v>1679352.6</v>
       </c>
       <c r="G11" s="16">
-        <v>0</v>
+        <v>1670019.7</v>
       </c>
       <c r="H11" s="16">
         <v>0</v>
@@ -3074,7 +3060,7 @@
       </c>
       <c r="P11" s="8"/>
       <c r="Q11" s="91">
-        <v>4772428.5</v>
+        <v>6402590.2999999998</v>
       </c>
     </row>
     <row r="12" spans="2:22" s="1" customFormat="1">
@@ -3083,16 +3069,16 @@
       </c>
       <c r="C12"/>
       <c r="D12" s="90">
-        <v>345410.8</v>
+        <v>348407.9</v>
       </c>
       <c r="E12" s="16">
-        <v>316928.90000000002</v>
+        <v>319117.8</v>
       </c>
       <c r="F12" s="16">
-        <v>345015.6</v>
+        <v>350676.9</v>
       </c>
       <c r="G12" s="16">
-        <v>0</v>
+        <v>326759.59999999998</v>
       </c>
       <c r="H12" s="16">
         <v>0</v>
@@ -3120,7 +3106,7 @@
       </c>
       <c r="P12" s="8"/>
       <c r="Q12" s="91">
-        <v>1007355.2999999999</v>
+        <v>1344962.2</v>
       </c>
     </row>
     <row r="13" spans="2:22">
@@ -3128,16 +3114,16 @@
         <v>27</v>
       </c>
       <c r="D13" s="90">
-        <v>175112.7</v>
+        <v>175414.2</v>
       </c>
       <c r="E13" s="16">
-        <v>155535.4</v>
+        <v>155795.4</v>
       </c>
       <c r="F13" s="16">
-        <v>167755.6</v>
+        <v>169389.1</v>
       </c>
       <c r="G13" s="16">
-        <v>0</v>
+        <v>160156.5</v>
       </c>
       <c r="H13" s="16">
         <v>0</v>
@@ -3165,7 +3151,7 @@
       </c>
       <c r="P13" s="8"/>
       <c r="Q13" s="91">
-        <v>498403.69999999995</v>
+        <v>660755.19999999995</v>
       </c>
     </row>
     <row r="14" spans="2:22">
@@ -3173,16 +3159,16 @@
         <v>122</v>
       </c>
       <c r="D14" s="96">
-        <v>655846.19999999995</v>
+        <v>660733.5</v>
       </c>
       <c r="E14" s="76">
-        <v>595209.19999999995</v>
+        <v>602014.19999999995</v>
       </c>
       <c r="F14" s="76">
-        <v>669833.6</v>
+        <v>674488.3</v>
       </c>
       <c r="G14" s="75">
-        <v>0</v>
+        <v>647101</v>
       </c>
       <c r="H14" s="75">
         <v>0</v>
@@ -3210,7 +3196,7 @@
       </c>
       <c r="P14" s="76"/>
       <c r="Q14" s="96">
-        <v>1920889</v>
+        <v>2584337</v>
       </c>
     </row>
     <row r="15" spans="2:22" s="1" customFormat="1">
@@ -3218,16 +3204,16 @@
         <v>114</v>
       </c>
       <c r="D15" s="90">
-        <v>2774873.9000000004</v>
+        <v>2771098</v>
       </c>
       <c r="E15" s="16">
-        <v>2546782.2999999998</v>
+        <v>2543603</v>
       </c>
       <c r="F15" s="16">
-        <v>2877420.3000000003</v>
+        <v>2873906.9000000004</v>
       </c>
       <c r="G15" s="16">
-        <v>0</v>
+        <v>2804036.8</v>
       </c>
       <c r="H15" s="16">
         <v>0</v>
@@ -3255,7 +3241,7 @@
       </c>
       <c r="P15" s="8"/>
       <c r="Q15" s="91">
-        <v>8199076.5</v>
+        <v>10992644.699999999</v>
       </c>
     </row>
     <row r="16" spans="2:22" s="1" customFormat="1">
@@ -3280,16 +3266,16 @@
         <v>30</v>
       </c>
       <c r="D17" s="90">
-        <v>465994.7</v>
+        <v>469688.8</v>
       </c>
       <c r="E17" s="16">
-        <v>402612.6</v>
+        <v>405740</v>
       </c>
       <c r="F17" s="16">
-        <v>408668</v>
+        <v>411742.3</v>
       </c>
       <c r="G17" s="16">
-        <v>0</v>
+        <v>424283.9</v>
       </c>
       <c r="H17" s="16">
         <v>0</v>
@@ -3317,7 +3303,7 @@
       </c>
       <c r="P17" s="8"/>
       <c r="Q17" s="91">
-        <v>1277275.3</v>
+        <v>1711455</v>
       </c>
     </row>
     <row r="18" spans="2:17">
@@ -3387,10 +3373,10 @@
         <v>9007844</v>
       </c>
       <c r="F21" s="16">
-        <v>9954264</v>
+        <v>9954219.8000000007</v>
       </c>
       <c r="G21" s="16">
-        <v>0</v>
+        <v>9390531.5999999996</v>
       </c>
       <c r="H21" s="16">
         <v>0</v>
@@ -3418,7 +3404,7 @@
       </c>
       <c r="P21" s="8"/>
       <c r="Q21" s="91">
-        <v>28870658</v>
+        <v>38261145.399999999</v>
       </c>
     </row>
     <row r="22" spans="2:17">
@@ -3436,7 +3422,7 @@
         <v>8397483.3000000007</v>
       </c>
       <c r="G22" s="16">
-        <v>0</v>
+        <v>8228817.2000000002</v>
       </c>
       <c r="H22" s="16">
         <v>0</v>
@@ -3464,7 +3450,7 @@
       </c>
       <c r="P22" s="8"/>
       <c r="Q22" s="91">
-        <v>24563048.200000003</v>
+        <v>32791865.400000002</v>
       </c>
     </row>
     <row r="23" spans="2:17">
@@ -3482,7 +3468,7 @@
         <v>-7407328.9000000004</v>
       </c>
       <c r="G23" s="16">
-        <v>0</v>
+        <v>-7541174.2999999998</v>
       </c>
       <c r="H23" s="16">
         <v>0</v>
@@ -3510,7 +3496,7 @@
       </c>
       <c r="P23" s="8"/>
       <c r="Q23" s="91">
-        <v>-21762521</v>
+        <v>-29303695.300000001</v>
       </c>
     </row>
     <row r="24" spans="2:17">
@@ -3525,10 +3511,10 @@
         <v>9749859.9000000004</v>
       </c>
       <c r="F24" s="16">
-        <v>10944418.4</v>
+        <v>10944374.200000001</v>
       </c>
       <c r="G24" s="16">
-        <v>0</v>
+        <v>10078174.5</v>
       </c>
       <c r="H24" s="16">
         <v>0</v>
@@ -3556,7 +3542,7 @@
       </c>
       <c r="P24" s="8"/>
       <c r="Q24" s="91">
-        <v>31671185.200000003</v>
+        <v>41749315.5</v>
       </c>
     </row>
     <row r="25" spans="2:17">
@@ -3573,7 +3559,7 @@
         <v>6311042.0999999996</v>
       </c>
       <c r="G25" s="42">
-        <v>0</v>
+        <v>6485610.4000000004</v>
       </c>
       <c r="H25" s="42">
         <v>0</v>
@@ -3601,7 +3587,7 @@
       </c>
       <c r="P25" s="8"/>
       <c r="Q25" s="98">
-        <v>18627473</v>
+        <v>25113083.399999999</v>
       </c>
     </row>
     <row r="26" spans="2:17">
@@ -3615,10 +3601,10 @@
         <v>15525054.800000001</v>
       </c>
       <c r="F26" s="16">
-        <v>17255460.5</v>
+        <v>17255416.300000001</v>
       </c>
       <c r="G26" s="16">
-        <v>0</v>
+        <v>16563784.9</v>
       </c>
       <c r="H26" s="16">
         <v>0</v>
@@ -3646,7 +3632,7 @@
       </c>
       <c r="P26" s="8"/>
       <c r="Q26" s="91">
-        <v>50298658.200000003</v>
+        <v>66862398.899999999</v>
       </c>
     </row>
     <row r="27" spans="2:17">
@@ -3672,16 +3658,16 @@
       </c>
       <c r="C28" s="17"/>
       <c r="D28" s="90">
-        <v>20759011.499999996</v>
+        <v>20758929.699999999</v>
       </c>
       <c r="E28" s="16">
-        <v>18474449.700000003</v>
+        <v>18474397.800000001</v>
       </c>
       <c r="F28" s="16">
-        <v>20541548.800000001</v>
+        <v>20541065.500000004</v>
       </c>
       <c r="G28" s="16">
-        <v>0</v>
+        <v>19792105.599999998</v>
       </c>
       <c r="H28" s="16">
         <v>0</v>
@@ -3709,7 +3695,7 @@
       </c>
       <c r="P28" s="8"/>
       <c r="Q28" s="90">
-        <v>59775010</v>
+        <v>79566498.599999994</v>
       </c>
     </row>
     <row r="29" spans="2:17">
@@ -3753,16 +3739,16 @@
         <v>49</v>
       </c>
       <c r="D31" s="90">
-        <v>1388226.8</v>
+        <v>1388228.4</v>
       </c>
       <c r="E31" s="16">
-        <v>1222883.7</v>
+        <v>1222880.2</v>
       </c>
       <c r="F31" s="16">
-        <v>1318091.8999999999</v>
+        <v>1318314.6000000001</v>
       </c>
       <c r="G31" s="16">
-        <v>0</v>
+        <v>1263507.8999999999</v>
       </c>
       <c r="H31" s="16">
         <v>0</v>
@@ -3790,7 +3776,7 @@
       </c>
       <c r="P31" s="8"/>
       <c r="Q31" s="91">
-        <v>3929202.4</v>
+        <v>5192931.0999999996</v>
       </c>
     </row>
     <row r="32" spans="2:17">
@@ -3807,7 +3793,7 @@
         <v>388650.6</v>
       </c>
       <c r="G32" s="16">
-        <v>0</v>
+        <v>367833.7</v>
       </c>
       <c r="H32" s="16">
         <v>0</v>
@@ -3835,7 +3821,7 @@
       </c>
       <c r="P32" s="8"/>
       <c r="Q32" s="90">
-        <v>1151093.8999999999</v>
+        <v>1518927.5999999999</v>
       </c>
     </row>
     <row r="33" spans="2:17">
@@ -3867,10 +3853,10 @@
         <v>10462.299999999999</v>
       </c>
       <c r="F34" s="16">
-        <v>22910.799999999999</v>
+        <v>22941.3</v>
       </c>
       <c r="G34" s="16">
-        <v>0</v>
+        <v>11894.2</v>
       </c>
       <c r="H34" s="16">
         <v>0</v>
@@ -3898,7 +3884,7 @@
       </c>
       <c r="P34" s="8"/>
       <c r="Q34" s="91">
-        <v>43476.899999999994</v>
+        <v>55401.599999999991</v>
       </c>
     </row>
     <row r="35" spans="2:17">
@@ -3916,7 +3902,7 @@
         <v>12144.8</v>
       </c>
       <c r="G35" s="16">
-        <v>0</v>
+        <v>9616.5</v>
       </c>
       <c r="H35" s="16">
         <v>0</v>
@@ -3944,7 +3930,7 @@
       </c>
       <c r="P35" s="8"/>
       <c r="Q35" s="91">
-        <v>32906.699999999997</v>
+        <v>42523.199999999997</v>
       </c>
     </row>
     <row r="36" spans="2:17">
@@ -3953,16 +3939,16 @@
       </c>
       <c r="C36" s="17"/>
       <c r="D36" s="90">
-        <v>487218.8</v>
+        <v>487262.6</v>
       </c>
       <c r="E36" s="16">
-        <v>419193.2</v>
+        <v>420400.9</v>
       </c>
       <c r="F36" s="16">
-        <v>424689.1</v>
+        <v>424701.5</v>
       </c>
       <c r="G36" s="16">
-        <v>0</v>
+        <v>346376.9</v>
       </c>
       <c r="H36" s="16">
         <v>0</v>
@@ -3990,7 +3976,7 @@
       </c>
       <c r="P36" s="8"/>
       <c r="Q36" s="91">
-        <v>1331101.1000000001</v>
+        <v>1678741.9</v>
       </c>
     </row>
     <row r="37" spans="2:17">
@@ -4023,10 +4009,10 @@
         <v>261443.1</v>
       </c>
       <c r="F38" s="16">
-        <v>295219.7</v>
+        <v>295214.3</v>
       </c>
       <c r="G38" s="16">
-        <v>0</v>
+        <v>281163.09999999998</v>
       </c>
       <c r="H38" s="16">
         <v>0</v>
@@ -4054,7 +4040,7 @@
       </c>
       <c r="P38" s="8"/>
       <c r="Q38" s="91">
-        <v>845879.5</v>
+        <v>1127037.2000000002</v>
       </c>
     </row>
     <row r="39" spans="2:17">
@@ -4072,7 +4058,7 @@
         <v>19.3</v>
       </c>
       <c r="G39" s="16">
-        <v>0</v>
+        <v>25.6</v>
       </c>
       <c r="H39" s="16">
         <v>0</v>
@@ -4100,7 +4086,7 @@
       </c>
       <c r="P39" s="8"/>
       <c r="Q39" s="91">
-        <v>366.3</v>
+        <v>391.90000000000003</v>
       </c>
     </row>
     <row r="40" spans="2:17">
@@ -4156,7 +4142,7 @@
         <v>536174.69999999995</v>
       </c>
       <c r="G42" s="78">
-        <v>0</v>
+        <v>489978.2</v>
       </c>
       <c r="H42" s="78">
         <v>0</v>
@@ -4184,7 +4170,7 @@
       </c>
       <c r="P42" s="79"/>
       <c r="Q42" s="79">
-        <v>1574975.2</v>
+        <v>2064953.4</v>
       </c>
     </row>
     <row r="43" spans="2:17">
@@ -4202,7 +4188,7 @@
         <v>1386274.4</v>
       </c>
       <c r="G43" s="78">
-        <v>0</v>
+        <v>1245264.2</v>
       </c>
       <c r="H43" s="78">
         <v>0</v>
@@ -4230,7 +4216,7 @@
       </c>
       <c r="P43" s="79"/>
       <c r="Q43" s="79">
-        <v>3957811.9</v>
+        <v>5203076.0999999996</v>
       </c>
     </row>
     <row r="44" spans="2:17">
@@ -4248,7 +4234,7 @@
         <v>918096.4</v>
       </c>
       <c r="G44" s="78">
-        <v>0</v>
+        <v>821047</v>
       </c>
       <c r="H44" s="78">
         <v>0</v>
@@ -4276,7 +4262,7 @@
       </c>
       <c r="P44" s="79"/>
       <c r="Q44" s="79">
-        <v>2477425.6</v>
+        <v>3298472.6</v>
       </c>
     </row>
     <row r="45" spans="2:17">
@@ -4294,7 +4280,7 @@
         <v>305054.5</v>
       </c>
       <c r="G45" s="80">
-        <v>0</v>
+        <v>293280.90000000002</v>
       </c>
       <c r="H45" s="80">
         <v>0</v>
@@ -4322,7 +4308,7 @@
       </c>
       <c r="P45" s="80"/>
       <c r="Q45" s="80">
-        <v>857897.3</v>
+        <v>1151178.2000000002</v>
       </c>
     </row>
     <row r="46" spans="2:17">
@@ -4334,13 +4320,13 @@
         <v>2969353.7</v>
       </c>
       <c r="E46" s="89">
-        <v>2753156.3000000003</v>
+        <v>2753156.3</v>
       </c>
       <c r="F46" s="89">
         <v>3145600</v>
       </c>
       <c r="G46" s="89">
-        <v>0</v>
+        <v>2849570.3</v>
       </c>
       <c r="H46" s="89">
         <v>0</v>
@@ -4368,7 +4354,7 @@
       </c>
       <c r="P46" s="79"/>
       <c r="Q46" s="79">
-        <v>8868110</v>
+        <v>11717680.300000001</v>
       </c>
     </row>
     <row r="47" spans="2:17">
@@ -4394,16 +4380,16 @@
         <v>58</v>
       </c>
       <c r="D48" s="89">
-        <v>5559856.7000000011</v>
+        <v>5559902.0999999996</v>
       </c>
       <c r="E48" s="89">
-        <v>5034953.9000000004</v>
+        <v>5036158.0999999996</v>
       </c>
       <c r="F48" s="89">
-        <v>5607326.2000000002</v>
+        <v>5607586.4000000004</v>
       </c>
       <c r="G48" s="89">
-        <v>0</v>
+        <v>5129988.2</v>
       </c>
       <c r="H48" s="89">
         <v>0</v>
@@ -4431,7 +4417,7 @@
       </c>
       <c r="P48" s="79"/>
       <c r="Q48" s="79">
-        <v>16202136.800000001</v>
+        <v>21333634.800000001</v>
       </c>
     </row>
     <row r="49" spans="2:17">
@@ -4465,7 +4451,7 @@
         <v>198498.7</v>
       </c>
       <c r="G50" s="78">
-        <v>0</v>
+        <v>213335.4</v>
       </c>
       <c r="H50" s="78">
         <v>0</v>
@@ -4493,7 +4479,7 @@
       </c>
       <c r="P50" s="79"/>
       <c r="Q50" s="79">
-        <v>605035.39999999991</v>
+        <v>818370.79999999993</v>
       </c>
     </row>
     <row r="51" spans="2:17">
@@ -4510,7 +4496,7 @@
         <v>118692.6</v>
       </c>
       <c r="G51" s="78">
-        <v>0</v>
+        <v>104525.2</v>
       </c>
       <c r="H51" s="78">
         <v>0</v>
@@ -4538,7 +4524,7 @@
       </c>
       <c r="P51" s="79"/>
       <c r="Q51" s="79">
-        <v>338421.80000000005</v>
+        <v>442947.00000000006</v>
       </c>
     </row>
     <row r="52" spans="2:17">
@@ -4546,16 +4532,16 @@
         <v>17</v>
       </c>
       <c r="D52" s="78">
-        <v>395848.1</v>
+        <v>395848.4</v>
       </c>
       <c r="E52" s="78">
-        <v>351825.7</v>
+        <v>351825</v>
       </c>
       <c r="F52" s="78">
-        <v>389791.3</v>
+        <v>389916</v>
       </c>
       <c r="G52" s="78">
-        <v>0</v>
+        <v>369971.1</v>
       </c>
       <c r="H52" s="78">
         <v>0</v>
@@ -4583,7 +4569,7 @@
       </c>
       <c r="P52" s="78"/>
       <c r="Q52" s="78">
-        <v>1137465.1000000001</v>
+        <v>1507560.5</v>
       </c>
     </row>
     <row r="53" spans="2:17" ht="14.25" customHeight="1">
@@ -4610,16 +4596,16 @@
       </c>
       <c r="C54" s="4"/>
       <c r="D54" s="83">
-        <v>10401802.9</v>
+        <v>10401727.6</v>
       </c>
       <c r="E54" s="83">
-        <v>10278429.9</v>
+        <v>10278547.1</v>
       </c>
       <c r="F54" s="83">
-        <v>10007289</v>
+        <v>10007763.699999999</v>
       </c>
       <c r="G54" s="83">
-        <v>0</v>
+        <v>9978577</v>
       </c>
       <c r="H54" s="83">
         <v>0</v>
@@ -4647,7 +4633,7 @@
       </c>
       <c r="P54" s="83"/>
       <c r="Q54" s="84">
-        <v>10007289</v>
+        <v>9978577</v>
       </c>
     </row>
     <row r="55" spans="2:17">
@@ -4661,10 +4647,10 @@
         <v>-12008.8</v>
       </c>
       <c r="F55" s="78">
-        <v>-19187.599999999999</v>
+        <v>-18879.3</v>
       </c>
       <c r="G55" s="78">
-        <v>0</v>
+        <v>33351.4</v>
       </c>
       <c r="H55" s="78">
         <v>0</v>
@@ -4692,7 +4678,7 @@
       </c>
       <c r="P55" s="79"/>
       <c r="Q55" s="79">
-        <v>31774.9</v>
+        <v>65434.600000000006</v>
       </c>
     </row>
     <row r="56" spans="2:17" ht="15.75" thickBot="1">
@@ -4718,16 +4704,16 @@
         <v>31</v>
       </c>
       <c r="D57" s="89">
-        <v>25048936.099999994</v>
+        <v>25048935.800000001</v>
       </c>
       <c r="E57" s="89">
-        <v>22969282.5</v>
+        <v>22970243</v>
       </c>
       <c r="F57" s="89">
-        <v>25693460.999999996</v>
+        <v>25693399.399999999</v>
       </c>
       <c r="G57" s="89">
-        <v>0</v>
+        <v>24296663.100000001</v>
       </c>
       <c r="H57" s="89">
         <v>0</v>
@@ -4755,7 +4741,7 @@
       </c>
       <c r="P57" s="79"/>
       <c r="Q57" s="79">
-        <v>73711679.599999994</v>
+        <v>98009241.299999997</v>
       </c>
     </row>
     <row r="58" spans="2:17">
@@ -4893,7 +4879,7 @@
         <v>76643.399999999994</v>
       </c>
       <c r="G63" s="90">
-        <v>0</v>
+        <v>54364.800000000003</v>
       </c>
       <c r="H63" s="90">
         <v>0</v>
@@ -4921,7 +4907,7 @@
       </c>
       <c r="P63" s="91"/>
       <c r="Q63" s="91">
-        <v>232623.4</v>
+        <v>286988.2</v>
       </c>
     </row>
     <row r="64" spans="2:17">
@@ -4938,7 +4924,7 @@
         <v>2622767.9</v>
       </c>
       <c r="G64" s="90">
-        <v>0</v>
+        <v>1850153.3</v>
       </c>
       <c r="H64" s="90">
         <v>0</v>
@@ -4966,7 +4952,7 @@
       </c>
       <c r="P64" s="91"/>
       <c r="Q64" s="91">
-        <v>7427482.5999999996</v>
+        <v>9277635.9000000004</v>
       </c>
     </row>
     <row r="65" spans="2:17">
@@ -4983,7 +4969,7 @@
         <v>9949.4</v>
       </c>
       <c r="G65" s="90">
-        <v>0</v>
+        <v>8712.1</v>
       </c>
       <c r="H65" s="90">
         <v>0</v>
@@ -5011,7 +4997,7 @@
       </c>
       <c r="P65" s="91"/>
       <c r="Q65" s="91">
-        <v>31229.300000000003</v>
+        <v>39941.4</v>
       </c>
     </row>
     <row r="66" spans="2:17">
@@ -5028,7 +5014,7 @@
         <v>14134.8</v>
       </c>
       <c r="G66" s="90">
-        <v>0</v>
+        <v>-6767.8</v>
       </c>
       <c r="H66" s="90">
         <v>0</v>
@@ -5056,7 +5042,7 @@
       </c>
       <c r="P66" s="91"/>
       <c r="Q66" s="91">
-        <v>54129.7</v>
+        <v>47361.899999999994</v>
       </c>
     </row>
     <row r="67" spans="2:17" s="1" customFormat="1">
@@ -5114,13 +5100,13 @@
         <v>-22759.200000000001</v>
       </c>
       <c r="E68" s="90">
-        <v>-7155.6</v>
+        <v>-9075.2000000000007</v>
       </c>
       <c r="F68" s="90">
-        <v>1851.2</v>
+        <v>2379.5</v>
       </c>
       <c r="G68" s="90">
-        <v>0</v>
+        <v>5270.8</v>
       </c>
       <c r="H68" s="90">
         <v>0</v>
@@ -5148,7 +5134,7 @@
       </c>
       <c r="P68" s="91"/>
       <c r="Q68" s="90">
-        <v>-28063.600000000002</v>
+        <v>-24184.100000000002</v>
       </c>
     </row>
     <row r="69" spans="2:17">
@@ -5163,10 +5149,10 @@
         <v>320501.40000000002</v>
       </c>
       <c r="F69" s="90">
-        <v>325675.09999999998</v>
+        <v>325433</v>
       </c>
       <c r="G69" s="90">
-        <v>0</v>
+        <v>581423.19999999995</v>
       </c>
       <c r="H69" s="90">
         <v>0</v>
@@ -5194,7 +5180,7 @@
       </c>
       <c r="P69" s="91"/>
       <c r="Q69" s="91">
-        <v>992024.6</v>
+        <v>1573205.7</v>
       </c>
     </row>
     <row r="70" spans="2:17">
@@ -5206,13 +5192,13 @@
         <v>2942734</v>
       </c>
       <c r="E70" s="90">
-        <v>2716321.1999999997</v>
+        <v>2714401.5999999996</v>
       </c>
       <c r="F70" s="90">
-        <v>3051341.8</v>
+        <v>3051627.9999999995</v>
       </c>
       <c r="G70" s="90">
-        <v>0</v>
+        <v>2493156.4000000004</v>
       </c>
       <c r="H70" s="90">
         <v>0</v>
@@ -5240,7 +5226,7 @@
       </c>
       <c r="P70" s="91"/>
       <c r="Q70" s="91">
-        <v>8710397</v>
+        <v>11201920</v>
       </c>
     </row>
     <row r="71" spans="2:17">
@@ -5276,7 +5262,7 @@
         <v>21686953.300000001</v>
       </c>
       <c r="G72" s="78">
-        <v>0</v>
+        <v>21284253.800000001</v>
       </c>
       <c r="H72" s="78">
         <v>0</v>
@@ -5304,7 +5290,7 @@
       </c>
       <c r="P72" s="79"/>
       <c r="Q72" s="79">
-        <v>62687232.200000003</v>
+        <v>83971486</v>
       </c>
     </row>
     <row r="73" spans="2:17">
@@ -5322,7 +5308,7 @@
         <v>699579.1387096775</v>
       </c>
       <c r="G73" s="78">
-        <v>0</v>
+        <v>709475.12666666671</v>
       </c>
       <c r="H73" s="78">
         <v>0</v>
@@ -5350,7 +5336,7 @@
       </c>
       <c r="P73" s="79"/>
       <c r="Q73" s="79">
-        <v>696347.05768049147</v>
+        <v>699629.07492703525</v>
       </c>
     </row>
     <row r="74" spans="2:17">
@@ -5377,16 +5363,16 @@
       </c>
       <c r="C75" s="17"/>
       <c r="D75" s="89">
-        <v>454335.39999999478</v>
+        <v>454335.1</v>
       </c>
       <c r="E75" s="89">
-        <v>904549.10000000149</v>
+        <v>907429.2</v>
       </c>
       <c r="F75" s="89">
-        <v>955165.89999999478</v>
+        <v>954818.1</v>
       </c>
       <c r="G75" s="89">
-        <v>0</v>
+        <v>519252.9</v>
       </c>
       <c r="H75" s="89">
         <v>0</v>
@@ -5414,7 +5400,7 @@
       </c>
       <c r="P75" s="79"/>
       <c r="Q75" s="79">
-        <v>2314050.3999999911</v>
+        <v>2835835.3</v>
       </c>
     </row>
     <row r="76" spans="2:17">
@@ -5423,16 +5409,16 @@
       </c>
       <c r="C76" s="18"/>
       <c r="D76" s="94">
-        <v>1.813791205287936E-2</v>
+        <v>-1.0810849954728521E-2</v>
       </c>
       <c r="E76" s="94">
-        <v>3.9380816531818158E-2</v>
+        <v>7.8857805049079577E-3</v>
       </c>
       <c r="F76" s="94">
-        <v>3.7175447091382312E-2</v>
-      </c>
-      <c r="G76" s="94" t="s">
-        <v>128</v>
+        <v>4.3588161272999646E-3</v>
+      </c>
+      <c r="G76" s="94">
+        <v>-8.0259945396266644E-3</v>
       </c>
       <c r="H76" s="94" t="s">
         <v>128</v>
@@ -5460,7 +5446,7 @@
       </c>
       <c r="P76" s="94"/>
       <c r="Q76" s="79">
-        <v>3.1564725225359941E-2</v>
+        <v>-1.7756414074776179E-3</v>
       </c>
     </row>
     <row r="77" spans="2:17" ht="15.75" thickBot="1">
@@ -5485,17 +5471,17 @@
       <c r="B78" s="59" t="s">
         <v>36</v>
       </c>
-      <c r="D78" s="112">
-        <v>25048936.099999994</v>
-      </c>
-      <c r="E78" s="112">
-        <v>22969282.5</v>
+      <c r="D78" s="89">
+        <v>25048935.800000001</v>
+      </c>
+      <c r="E78" s="89">
+        <v>22970243</v>
       </c>
       <c r="F78" s="110">
-        <v>25693460.999999996</v>
+        <v>25693399.399999999</v>
       </c>
       <c r="G78" s="110">
-        <v>0</v>
+        <v>24296663.100000001</v>
       </c>
       <c r="H78" s="110">
         <v>0</v>
@@ -5523,7 +5509,7 @@
       </c>
       <c r="P78" s="82"/>
       <c r="Q78" s="82">
-        <v>73711679.599999994</v>
+        <v>98009241.299999997</v>
       </c>
     </row>
     <row r="79" spans="2:17">

--- a/Oil_current.xlsx
+++ b/Oil_current.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\eub.gov.ab.ca\CalFsrv\Share0\Information Management\Info Sharing and Tracking\Product Services\Operations\Product Creation\ST3\ST3s_Report_Prep\All_Pages_Content_Update\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="V:\Information Management\Info Sharing and Tracking\Product Services\Operations\Product Creation\ST3\ST3s_Report_Prep\All_Pages_Content_Update\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E2C96A8-0788-4057-B553-D5936CEB6DD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75D6F203-9DA5-4D39-A2D1-D0F020BFC85B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="16440" windowHeight="28320" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Documentation" sheetId="21" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="130">
   <si>
     <t>Reporting Adjustment</t>
   </si>
@@ -479,7 +479,7 @@
     <t/>
   </si>
   <si>
-    <t xml:space="preserve"> Run Date:  27 May 2026</t>
+    <t xml:space="preserve"> Run Date:  29 June 2026</t>
   </si>
 </sst>
 </file>
@@ -487,12 +487,12 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="6">
-    <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="165" formatCode="#,##0.0"/>
-    <numFmt numFmtId="166" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="167" formatCode="0.00_)"/>
-    <numFmt numFmtId="168" formatCode="0____"/>
-    <numFmt numFmtId="169" formatCode="0.0"/>
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="#,##0.0"/>
+    <numFmt numFmtId="165" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="166" formatCode="0.00_)"/>
+    <numFmt numFmtId="167" formatCode="0____"/>
+    <numFmt numFmtId="168" formatCode="0.0"/>
   </numFmts>
   <fonts count="31">
     <font>
@@ -805,14 +805,14 @@
   </borders>
   <cellStyleXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
     <xf numFmtId="4" fontId="11" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="167" fontId="12" fillId="0" borderId="0">
+    <xf numFmtId="166" fontId="12" fillId="0" borderId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="40" fontId="13" fillId="0" borderId="0">
@@ -823,7 +823,7 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0">
       <alignment textRotation="90"/>
     </xf>
-    <xf numFmtId="168" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="167" fontId="16" fillId="0" borderId="0"/>
     <xf numFmtId="39" fontId="17" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
@@ -848,23 +848,23 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -876,13 +876,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" indent="6"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -892,7 +892,7 @@
       <alignment horizontal="left" indent="3"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" indent="3"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -912,15 +912,15 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -929,13 +929,13 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="25" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="25" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="27" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="27" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -966,13 +966,13 @@
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="165" fontId="29" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="29" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="29" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="29" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="3"/>
     </xf>
-    <xf numFmtId="165" fontId="29" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="29" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" indent="6"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -981,8 +981,8 @@
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="24" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="24" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="24" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="24" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="24" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -995,63 +995,63 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="6"/>
     </xf>
-    <xf numFmtId="166" fontId="29" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="29" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="29" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="29" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="29" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="29" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="29" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="29" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="29" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="29" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="29" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="29" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="29" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="29" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="29" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="29" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="29" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="29" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="29" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="29" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="29" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="29" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="169" fontId="2" fillId="0" borderId="0" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="2" fillId="0" borderId="0" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="2" fillId="0" borderId="0" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1074,7 +1074,7 @@
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1513,17 +1513,17 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:BK84"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
     <col min="2" max="2" width="43" customWidth="1"/>
-    <col min="3" max="3" width="3.85546875" customWidth="1"/>
-    <col min="4" max="15" width="14.5703125" customWidth="1"/>
-    <col min="16" max="16" width="1.5703125" customWidth="1"/>
+    <col min="3" max="3" width="3.88671875" customWidth="1"/>
+    <col min="4" max="15" width="14.5546875" customWidth="1"/>
+    <col min="16" max="16" width="1.5546875" customWidth="1"/>
     <col min="17" max="17" width="17" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" customWidth="1"/>
-    <col min="21" max="21" width="20.28515625" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.5546875" customWidth="1"/>
+    <col min="21" max="21" width="20.33203125" customWidth="1"/>
+    <col min="22" max="22" width="14.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:63" s="2" customFormat="1" ht="20.25" customHeight="1">
@@ -2499,7 +2499,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="56" spans="1:19" ht="15.75" thickBot="1">
+    <row r="56" spans="1:19" ht="15" thickBot="1">
       <c r="B56" s="50"/>
       <c r="C56" s="17"/>
       <c r="D56" s="69"/>
@@ -2516,7 +2516,7 @@
       <c r="O56" s="25"/>
       <c r="Q56" s="25"/>
     </row>
-    <row r="57" spans="1:19" ht="15.75" thickTop="1">
+    <row r="57" spans="1:19" ht="15" thickTop="1">
       <c r="B57" s="59" t="s">
         <v>31</v>
       </c>
@@ -2738,7 +2738,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="77" spans="2:17" ht="15.75" thickBot="1">
+    <row r="77" spans="2:17" ht="15" thickBot="1">
       <c r="B77" s="50"/>
       <c r="C77" s="19"/>
       <c r="D77" s="69"/>
@@ -2755,7 +2755,7 @@
       <c r="O77" s="25"/>
       <c r="Q77" s="25"/>
     </row>
-    <row r="78" spans="2:17" ht="15.75" thickTop="1">
+    <row r="78" spans="2:17" ht="15" thickTop="1">
       <c r="B78" s="59" t="s">
         <v>36</v>
       </c>
@@ -2809,16 +2809,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:V89"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
-    <col min="2" max="2" width="44.7109375" customWidth="1"/>
+    <col min="2" max="2" width="44.6640625" customWidth="1"/>
     <col min="3" max="3" width="4" customWidth="1"/>
-    <col min="4" max="13" width="15.7109375" customWidth="1"/>
-    <col min="14" max="14" width="15.85546875" customWidth="1"/>
-    <col min="15" max="15" width="15.7109375" customWidth="1"/>
-    <col min="16" max="16" width="1.5703125" customWidth="1"/>
-    <col min="17" max="17" width="19.42578125" customWidth="1"/>
+    <col min="4" max="13" width="15.6640625" customWidth="1"/>
+    <col min="14" max="14" width="15.88671875" customWidth="1"/>
+    <col min="15" max="15" width="15.6640625" customWidth="1"/>
+    <col min="16" max="16" width="1.5546875" customWidth="1"/>
+    <col min="17" max="17" width="19.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:22" s="2" customFormat="1" ht="20.25" customHeight="1">
@@ -2922,19 +2922,19 @@
       </c>
       <c r="C7"/>
       <c r="D7" s="90">
-        <v>9791732.8000000007</v>
+        <v>9791726.6999999993</v>
       </c>
       <c r="E7" s="16">
-        <v>10401309.800000001</v>
+        <v>10401301.199999999</v>
       </c>
       <c r="F7" s="16">
-        <v>10278497.800000001</v>
+        <v>10278308.9</v>
       </c>
       <c r="G7" s="16">
-        <v>10007626.6</v>
+        <v>10007751.800000001</v>
       </c>
       <c r="H7" s="16">
-        <v>0</v>
+        <v>9977907.4000000004</v>
       </c>
       <c r="I7" s="16">
         <v>0</v>
@@ -2959,7 +2959,7 @@
       </c>
       <c r="P7" s="8"/>
       <c r="Q7" s="91">
-        <v>9791732.8000000007</v>
+        <v>9791726.6999999993</v>
       </c>
       <c r="V7" s="16"/>
     </row>
@@ -3023,19 +3023,19 @@
         <v>25</v>
       </c>
       <c r="D11" s="90">
-        <v>1586542.4</v>
+        <v>1579182.9</v>
       </c>
       <c r="E11" s="16">
-        <v>1466675.6</v>
+        <v>1459726.6</v>
       </c>
       <c r="F11" s="16">
-        <v>1679352.6</v>
+        <v>1670794.9</v>
       </c>
       <c r="G11" s="16">
-        <v>1670019.7</v>
+        <v>1644302.4</v>
       </c>
       <c r="H11" s="16">
-        <v>0</v>
+        <v>1660272.4</v>
       </c>
       <c r="I11" s="16">
         <v>0</v>
@@ -3060,7 +3060,7 @@
       </c>
       <c r="P11" s="8"/>
       <c r="Q11" s="91">
-        <v>6402590.2999999998</v>
+        <v>8014279.2000000011</v>
       </c>
     </row>
     <row r="12" spans="2:22" s="1" customFormat="1">
@@ -3069,19 +3069,19 @@
       </c>
       <c r="C12"/>
       <c r="D12" s="90">
-        <v>348407.9</v>
+        <v>351193.3</v>
       </c>
       <c r="E12" s="16">
-        <v>319117.8</v>
+        <v>321641.2</v>
       </c>
       <c r="F12" s="16">
-        <v>350676.9</v>
+        <v>353823.9</v>
       </c>
       <c r="G12" s="16">
-        <v>326759.59999999998</v>
+        <v>329849.90000000002</v>
       </c>
       <c r="H12" s="16">
-        <v>0</v>
+        <v>337241.4</v>
       </c>
       <c r="I12" s="16">
         <v>0</v>
@@ -3106,7 +3106,7 @@
       </c>
       <c r="P12" s="8"/>
       <c r="Q12" s="91">
-        <v>1344962.2</v>
+        <v>1693749.7000000002</v>
       </c>
     </row>
     <row r="13" spans="2:22">
@@ -3114,19 +3114,19 @@
         <v>27</v>
       </c>
       <c r="D13" s="90">
-        <v>175414.2</v>
+        <v>175925.6</v>
       </c>
       <c r="E13" s="16">
-        <v>155795.4</v>
+        <v>156255.29999999999</v>
       </c>
       <c r="F13" s="16">
-        <v>169389.1</v>
+        <v>169881.60000000001</v>
       </c>
       <c r="G13" s="16">
-        <v>160156.5</v>
+        <v>161000.70000000001</v>
       </c>
       <c r="H13" s="16">
-        <v>0</v>
+        <v>158689.29999999999</v>
       </c>
       <c r="I13" s="16">
         <v>0</v>
@@ -3151,7 +3151,7 @@
       </c>
       <c r="P13" s="8"/>
       <c r="Q13" s="91">
-        <v>660755.19999999995</v>
+        <v>821752.5</v>
       </c>
     </row>
     <row r="14" spans="2:22">
@@ -3159,19 +3159,19 @@
         <v>122</v>
       </c>
       <c r="D14" s="96">
-        <v>660733.5</v>
+        <v>662102.4</v>
       </c>
       <c r="E14" s="76">
-        <v>602014.19999999995</v>
+        <v>603743.19999999995</v>
       </c>
       <c r="F14" s="76">
-        <v>674488.3</v>
+        <v>677253.2</v>
       </c>
       <c r="G14" s="75">
-        <v>647101</v>
+        <v>648387.9</v>
       </c>
       <c r="H14" s="75">
-        <v>0</v>
+        <v>659544.69999999995</v>
       </c>
       <c r="I14" s="75">
         <v>0</v>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="P14" s="76"/>
       <c r="Q14" s="96">
-        <v>2584337</v>
+        <v>3251031.4000000004</v>
       </c>
     </row>
     <row r="15" spans="2:22" s="1" customFormat="1">
@@ -3204,19 +3204,19 @@
         <v>114</v>
       </c>
       <c r="D15" s="90">
-        <v>2771098</v>
+        <v>2768404.1999999997</v>
       </c>
       <c r="E15" s="16">
-        <v>2543603</v>
+        <v>2541366.2999999998</v>
       </c>
       <c r="F15" s="16">
-        <v>2873906.9000000004</v>
+        <v>2871753.5999999996</v>
       </c>
       <c r="G15" s="16">
-        <v>2804036.8</v>
+        <v>2783540.9</v>
       </c>
       <c r="H15" s="16">
-        <v>0</v>
+        <v>2815747.8</v>
       </c>
       <c r="I15" s="16">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="P15" s="8"/>
       <c r="Q15" s="91">
-        <v>10992644.699999999</v>
+        <v>13780812.800000001</v>
       </c>
     </row>
     <row r="16" spans="2:22" s="1" customFormat="1">
@@ -3266,19 +3266,19 @@
         <v>30</v>
       </c>
       <c r="D17" s="90">
-        <v>469688.8</v>
+        <v>472483.3</v>
       </c>
       <c r="E17" s="16">
-        <v>405740</v>
+        <v>408049.9</v>
       </c>
       <c r="F17" s="16">
-        <v>411742.3</v>
+        <v>413927.6</v>
       </c>
       <c r="G17" s="16">
-        <v>424283.9</v>
+        <v>444724</v>
       </c>
       <c r="H17" s="16">
-        <v>0</v>
+        <v>443733.5</v>
       </c>
       <c r="I17" s="16">
         <v>0</v>
@@ -3303,7 +3303,7 @@
       </c>
       <c r="P17" s="8"/>
       <c r="Q17" s="91">
-        <v>1711455</v>
+        <v>2182918.2999999998</v>
       </c>
     </row>
     <row r="18" spans="2:17">
@@ -3376,10 +3376,10 @@
         <v>9954219.8000000007</v>
       </c>
       <c r="G21" s="16">
-        <v>9390531.5999999996</v>
+        <v>9390531</v>
       </c>
       <c r="H21" s="16">
-        <v>0</v>
+        <v>9148799</v>
       </c>
       <c r="I21" s="16">
         <v>0</v>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="P21" s="8"/>
       <c r="Q21" s="91">
-        <v>38261145.399999999</v>
+        <v>47409943.799999997</v>
       </c>
     </row>
     <row r="22" spans="2:17">
@@ -3425,7 +3425,7 @@
         <v>8228817.2000000002</v>
       </c>
       <c r="H22" s="16">
-        <v>0</v>
+        <v>8248260.5999999996</v>
       </c>
       <c r="I22" s="16">
         <v>0</v>
@@ -3450,7 +3450,7 @@
       </c>
       <c r="P22" s="8"/>
       <c r="Q22" s="91">
-        <v>32791865.400000002</v>
+        <v>41040126</v>
       </c>
     </row>
     <row r="23" spans="2:17">
@@ -3471,7 +3471,7 @@
         <v>-7541174.2999999998</v>
       </c>
       <c r="H23" s="16">
-        <v>0</v>
+        <v>-7070611.9000000004</v>
       </c>
       <c r="I23" s="16">
         <v>0</v>
@@ -3496,7 +3496,7 @@
       </c>
       <c r="P23" s="8"/>
       <c r="Q23" s="91">
-        <v>-29303695.300000001</v>
+        <v>-36374307.200000003</v>
       </c>
     </row>
     <row r="24" spans="2:17">
@@ -3514,10 +3514,10 @@
         <v>10944374.200000001</v>
       </c>
       <c r="G24" s="16">
-        <v>10078174.5</v>
+        <v>10078173.899999999</v>
       </c>
       <c r="H24" s="16">
-        <v>0</v>
+        <v>10326447.700000001</v>
       </c>
       <c r="I24" s="16">
         <v>0</v>
@@ -3542,7 +3542,7 @@
       </c>
       <c r="P24" s="8"/>
       <c r="Q24" s="91">
-        <v>41749315.5</v>
+        <v>52075762.600000001</v>
       </c>
     </row>
     <row r="25" spans="2:17">
@@ -3562,7 +3562,7 @@
         <v>6485610.4000000004</v>
       </c>
       <c r="H25" s="42">
-        <v>0</v>
+        <v>6061292.5999999996</v>
       </c>
       <c r="I25" s="42">
         <v>0</v>
@@ -3587,7 +3587,7 @@
       </c>
       <c r="P25" s="8"/>
       <c r="Q25" s="98">
-        <v>25113083.399999999</v>
+        <v>31174376</v>
       </c>
     </row>
     <row r="26" spans="2:17">
@@ -3604,10 +3604,10 @@
         <v>17255416.300000001</v>
       </c>
       <c r="G26" s="16">
-        <v>16563784.9</v>
+        <v>16563784.299999999</v>
       </c>
       <c r="H26" s="16">
-        <v>0</v>
+        <v>16387740.300000001</v>
       </c>
       <c r="I26" s="16">
         <v>0</v>
@@ -3632,7 +3632,7 @@
       </c>
       <c r="P26" s="8"/>
       <c r="Q26" s="91">
-        <v>66862398.899999999</v>
+        <v>83250138.599999994</v>
       </c>
     </row>
     <row r="27" spans="2:17">
@@ -3658,19 +3658,19 @@
       </c>
       <c r="C28" s="17"/>
       <c r="D28" s="90">
-        <v>20758929.699999999</v>
+        <v>20759030.399999999</v>
       </c>
       <c r="E28" s="16">
-        <v>18474397.800000001</v>
+        <v>18474471</v>
       </c>
       <c r="F28" s="16">
-        <v>20541065.500000004</v>
+        <v>20541097.5</v>
       </c>
       <c r="G28" s="16">
-        <v>19792105.599999998</v>
+        <v>19792049.199999999</v>
       </c>
       <c r="H28" s="16">
-        <v>0</v>
+        <v>19647221.600000001</v>
       </c>
       <c r="I28" s="16">
         <v>0</v>
@@ -3695,7 +3695,7 @@
       </c>
       <c r="P28" s="8"/>
       <c r="Q28" s="90">
-        <v>79566498.599999994</v>
+        <v>99213869.699999988</v>
       </c>
     </row>
     <row r="29" spans="2:17">
@@ -3739,19 +3739,19 @@
         <v>49</v>
       </c>
       <c r="D31" s="90">
-        <v>1388228.4</v>
+        <v>1388554.4</v>
       </c>
       <c r="E31" s="16">
-        <v>1222880.2</v>
+        <v>1223193</v>
       </c>
       <c r="F31" s="16">
-        <v>1318314.6000000001</v>
+        <v>1318684.1000000001</v>
       </c>
       <c r="G31" s="16">
-        <v>1263507.8999999999</v>
+        <v>1263897.1000000001</v>
       </c>
       <c r="H31" s="16">
-        <v>0</v>
+        <v>1251807.8999999999</v>
       </c>
       <c r="I31" s="16">
         <v>0</v>
@@ -3776,7 +3776,7 @@
       </c>
       <c r="P31" s="8"/>
       <c r="Q31" s="91">
-        <v>5192931.0999999996</v>
+        <v>6446136.5</v>
       </c>
     </row>
     <row r="32" spans="2:17">
@@ -3796,7 +3796,7 @@
         <v>367833.7</v>
       </c>
       <c r="H32" s="16">
-        <v>0</v>
+        <v>349925.2</v>
       </c>
       <c r="I32" s="16">
         <v>0</v>
@@ -3821,7 +3821,7 @@
       </c>
       <c r="P32" s="8"/>
       <c r="Q32" s="90">
-        <v>1518927.5999999999</v>
+        <v>1868852.7999999998</v>
       </c>
     </row>
     <row r="33" spans="2:17">
@@ -3856,10 +3856,10 @@
         <v>22941.3</v>
       </c>
       <c r="G34" s="16">
-        <v>11894.2</v>
+        <v>11894.1</v>
       </c>
       <c r="H34" s="16">
-        <v>0</v>
+        <v>10581.2</v>
       </c>
       <c r="I34" s="16">
         <v>0</v>
@@ -3884,7 +3884,7 @@
       </c>
       <c r="P34" s="8"/>
       <c r="Q34" s="91">
-        <v>55401.599999999991</v>
+        <v>65982.7</v>
       </c>
     </row>
     <row r="35" spans="2:17">
@@ -3905,7 +3905,7 @@
         <v>9616.5</v>
       </c>
       <c r="H35" s="16">
-        <v>0</v>
+        <v>13626.8</v>
       </c>
       <c r="I35" s="16">
         <v>0</v>
@@ -3930,7 +3930,7 @@
       </c>
       <c r="P35" s="8"/>
       <c r="Q35" s="91">
-        <v>42523.199999999997</v>
+        <v>56150</v>
       </c>
     </row>
     <row r="36" spans="2:17">
@@ -3939,19 +3939,19 @@
       </c>
       <c r="C36" s="17"/>
       <c r="D36" s="90">
-        <v>487262.6</v>
+        <v>485333.8</v>
       </c>
       <c r="E36" s="16">
-        <v>420400.9</v>
+        <v>416742.8</v>
       </c>
       <c r="F36" s="16">
-        <v>424701.5</v>
+        <v>422497.7</v>
       </c>
       <c r="G36" s="16">
-        <v>346376.9</v>
+        <v>339609.1</v>
       </c>
       <c r="H36" s="16">
-        <v>0</v>
+        <v>379369.4</v>
       </c>
       <c r="I36" s="16">
         <v>0</v>
@@ -3976,7 +3976,7 @@
       </c>
       <c r="P36" s="8"/>
       <c r="Q36" s="91">
-        <v>1678741.9</v>
+        <v>2043552.7999999998</v>
       </c>
     </row>
     <row r="37" spans="2:17">
@@ -4012,10 +4012,10 @@
         <v>295214.3</v>
       </c>
       <c r="G38" s="16">
-        <v>281163.09999999998</v>
+        <v>285283.20000000001</v>
       </c>
       <c r="H38" s="16">
-        <v>0</v>
+        <v>217668.4</v>
       </c>
       <c r="I38" s="16">
         <v>0</v>
@@ -4040,7 +4040,7 @@
       </c>
       <c r="P38" s="8"/>
       <c r="Q38" s="91">
-        <v>1127037.2000000002</v>
+        <v>1348825.7</v>
       </c>
     </row>
     <row r="39" spans="2:17">
@@ -4061,7 +4061,7 @@
         <v>25.6</v>
       </c>
       <c r="H39" s="16">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="I39" s="16">
         <v>0</v>
@@ -4086,7 +4086,7 @@
       </c>
       <c r="P39" s="8"/>
       <c r="Q39" s="91">
-        <v>391.90000000000003</v>
+        <v>417.90000000000003</v>
       </c>
     </row>
     <row r="40" spans="2:17">
@@ -4145,7 +4145,7 @@
         <v>489978.2</v>
       </c>
       <c r="H42" s="78">
-        <v>0</v>
+        <v>518354</v>
       </c>
       <c r="I42" s="78">
         <v>0</v>
@@ -4170,7 +4170,7 @@
       </c>
       <c r="P42" s="79"/>
       <c r="Q42" s="79">
-        <v>2064953.4</v>
+        <v>2583307.4</v>
       </c>
     </row>
     <row r="43" spans="2:17">
@@ -4188,10 +4188,10 @@
         <v>1386274.4</v>
       </c>
       <c r="G43" s="78">
-        <v>1245264.2</v>
+        <v>1245264.2000000002</v>
       </c>
       <c r="H43" s="78">
-        <v>0</v>
+        <v>1154506.2000000002</v>
       </c>
       <c r="I43" s="78">
         <v>0</v>
@@ -4216,7 +4216,7 @@
       </c>
       <c r="P43" s="79"/>
       <c r="Q43" s="79">
-        <v>5203076.0999999996</v>
+        <v>6357582.2999999998</v>
       </c>
     </row>
     <row r="44" spans="2:17">
@@ -4225,19 +4225,19 @@
       </c>
       <c r="C44" s="18"/>
       <c r="D44" s="78">
-        <v>817025.9</v>
+        <v>818954.7</v>
       </c>
       <c r="E44" s="78">
-        <v>742303.3</v>
+        <v>745961.4</v>
       </c>
       <c r="F44" s="78">
-        <v>918096.4</v>
+        <v>920300.2</v>
       </c>
       <c r="G44" s="78">
-        <v>821047</v>
+        <v>827814.9</v>
       </c>
       <c r="H44" s="78">
-        <v>0</v>
+        <v>954654.6</v>
       </c>
       <c r="I44" s="78">
         <v>0</v>
@@ -4262,7 +4262,7 @@
       </c>
       <c r="P44" s="79"/>
       <c r="Q44" s="79">
-        <v>3298472.6</v>
+        <v>4267685.8</v>
       </c>
     </row>
     <row r="45" spans="2:17">
@@ -4283,7 +4283,7 @@
         <v>293280.90000000002</v>
       </c>
       <c r="H45" s="80">
-        <v>0</v>
+        <v>267619.09999999998</v>
       </c>
       <c r="I45" s="80">
         <v>0</v>
@@ -4308,7 +4308,7 @@
       </c>
       <c r="P45" s="80"/>
       <c r="Q45" s="80">
-        <v>1151178.2000000002</v>
+        <v>1418797.3000000003</v>
       </c>
     </row>
     <row r="46" spans="2:17">
@@ -4317,19 +4317,19 @@
       </c>
       <c r="C46" s="17"/>
       <c r="D46" s="89">
-        <v>2969353.7</v>
+        <v>2971282.5</v>
       </c>
       <c r="E46" s="89">
-        <v>2753156.3</v>
+        <v>2756814.4</v>
       </c>
       <c r="F46" s="89">
-        <v>3145600</v>
+        <v>3147803.8</v>
       </c>
       <c r="G46" s="89">
-        <v>2849570.3</v>
+        <v>2856338.2</v>
       </c>
       <c r="H46" s="89">
-        <v>0</v>
+        <v>2895133.9000000004</v>
       </c>
       <c r="I46" s="89">
         <v>0</v>
@@ -4354,7 +4354,7 @@
       </c>
       <c r="P46" s="79"/>
       <c r="Q46" s="79">
-        <v>11717680.300000001</v>
+        <v>14627372.799999999</v>
       </c>
     </row>
     <row r="47" spans="2:17">
@@ -4380,19 +4380,19 @@
         <v>58</v>
       </c>
       <c r="D48" s="89">
-        <v>5559902.0999999996</v>
+        <v>5560228.0999999996</v>
       </c>
       <c r="E48" s="89">
-        <v>5036158.0999999996</v>
+        <v>5036470.9000000004</v>
       </c>
       <c r="F48" s="89">
-        <v>5607586.4000000004</v>
+        <v>5607955.9000000004</v>
       </c>
       <c r="G48" s="89">
-        <v>5129988.2</v>
+        <v>5134497.5</v>
       </c>
       <c r="H48" s="89">
-        <v>0</v>
+        <v>5118138.8000000007</v>
       </c>
       <c r="I48" s="89">
         <v>0</v>
@@ -4417,7 +4417,7 @@
       </c>
       <c r="P48" s="79"/>
       <c r="Q48" s="79">
-        <v>21333634.800000001</v>
+        <v>26457291.199999999</v>
       </c>
     </row>
     <row r="49" spans="2:17">
@@ -4454,7 +4454,7 @@
         <v>213335.4</v>
       </c>
       <c r="H50" s="78">
-        <v>0</v>
+        <v>204114.6</v>
       </c>
       <c r="I50" s="78">
         <v>0</v>
@@ -4479,7 +4479,7 @@
       </c>
       <c r="P50" s="79"/>
       <c r="Q50" s="79">
-        <v>818370.79999999993</v>
+        <v>1022485.3999999999</v>
       </c>
     </row>
     <row r="51" spans="2:17">
@@ -4499,7 +4499,7 @@
         <v>104525.2</v>
       </c>
       <c r="H51" s="78">
-        <v>0</v>
+        <v>118550.1</v>
       </c>
       <c r="I51" s="78">
         <v>0</v>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="P51" s="79"/>
       <c r="Q51" s="79">
-        <v>442947.00000000006</v>
+        <v>561497.10000000009</v>
       </c>
     </row>
     <row r="52" spans="2:17">
@@ -4532,19 +4532,19 @@
         <v>17</v>
       </c>
       <c r="D52" s="78">
-        <v>395848.4</v>
+        <v>395915.8</v>
       </c>
       <c r="E52" s="78">
-        <v>351825</v>
+        <v>351889.7</v>
       </c>
       <c r="F52" s="78">
-        <v>389916</v>
+        <v>389992.4</v>
       </c>
       <c r="G52" s="78">
-        <v>369971.1</v>
+        <v>370051.7</v>
       </c>
       <c r="H52" s="78">
-        <v>0</v>
+        <v>371063.7</v>
       </c>
       <c r="I52" s="78">
         <v>0</v>
@@ -4569,7 +4569,7 @@
       </c>
       <c r="P52" s="78"/>
       <c r="Q52" s="78">
-        <v>1507560.5</v>
+        <v>1878913.2999999998</v>
       </c>
     </row>
     <row r="53" spans="2:17" ht="14.25" customHeight="1">
@@ -4596,19 +4596,19 @@
       </c>
       <c r="C54" s="4"/>
       <c r="D54" s="83">
-        <v>10401727.6</v>
+        <v>10401719</v>
       </c>
       <c r="E54" s="83">
-        <v>10278547.1</v>
+        <v>10278358.199999999</v>
       </c>
       <c r="F54" s="83">
-        <v>10007763.699999999</v>
+        <v>10007751.800000001</v>
       </c>
       <c r="G54" s="83">
-        <v>9978577</v>
+        <v>9978078.0999999996</v>
       </c>
       <c r="H54" s="83">
-        <v>0</v>
+        <v>9207711.5</v>
       </c>
       <c r="I54" s="83">
         <v>0</v>
@@ -4633,7 +4633,7 @@
       </c>
       <c r="P54" s="83"/>
       <c r="Q54" s="84">
-        <v>9978577</v>
+        <v>9207711.5</v>
       </c>
     </row>
     <row r="55" spans="2:17">
@@ -4650,10 +4650,10 @@
         <v>-18879.3</v>
       </c>
       <c r="G55" s="78">
-        <v>33351.4</v>
+        <v>33394.6</v>
       </c>
       <c r="H55" s="78">
-        <v>0</v>
+        <v>-6179.5</v>
       </c>
       <c r="I55" s="78">
         <v>0</v>
@@ -4678,10 +4678,10 @@
       </c>
       <c r="P55" s="79"/>
       <c r="Q55" s="79">
-        <v>65434.600000000006</v>
-      </c>
-    </row>
-    <row r="56" spans="2:17" ht="15.75" thickBot="1">
+        <v>59298.3</v>
+      </c>
+    </row>
+    <row r="56" spans="2:17" ht="15" thickBot="1">
       <c r="B56" s="104"/>
       <c r="C56" s="18"/>
       <c r="D56" s="85"/>
@@ -4699,24 +4699,24 @@
       <c r="P56" s="86"/>
       <c r="Q56" s="86"/>
     </row>
-    <row r="57" spans="2:17" ht="15.75" thickTop="1">
+    <row r="57" spans="2:17" ht="15" thickTop="1">
       <c r="B57" s="59" t="s">
         <v>31</v>
       </c>
       <c r="D57" s="89">
-        <v>25048935.800000001</v>
+        <v>25049297.600000001</v>
       </c>
       <c r="E57" s="89">
-        <v>22970243</v>
+        <v>22970744.599999998</v>
       </c>
       <c r="F57" s="89">
-        <v>25693399.399999999</v>
+        <v>25693547.5</v>
       </c>
       <c r="G57" s="89">
-        <v>24296663.100000001</v>
+        <v>24301702.699999999</v>
       </c>
       <c r="H57" s="89">
-        <v>0</v>
+        <v>24835648.400000006</v>
       </c>
       <c r="I57" s="89">
         <v>0</v>
@@ -4741,7 +4741,7 @@
       </c>
       <c r="P57" s="79"/>
       <c r="Q57" s="79">
-        <v>98009241.299999997</v>
+        <v>122850940.80000001</v>
       </c>
     </row>
     <row r="58" spans="2:17">
@@ -4783,7 +4783,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="60" spans="2:17" ht="15.75">
+    <row r="60" spans="2:17" ht="15.6">
       <c r="B60" s="48"/>
       <c r="D60" s="92" t="s">
         <v>1</v>
@@ -4882,7 +4882,7 @@
         <v>54364.800000000003</v>
       </c>
       <c r="H63" s="90">
-        <v>0</v>
+        <v>44470.2</v>
       </c>
       <c r="I63" s="90">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="P63" s="91"/>
       <c r="Q63" s="91">
-        <v>286988.2</v>
+        <v>331458.40000000002</v>
       </c>
     </row>
     <row r="64" spans="2:17">
@@ -4927,7 +4927,7 @@
         <v>1850153.3</v>
       </c>
       <c r="H64" s="90">
-        <v>0</v>
+        <v>2197029</v>
       </c>
       <c r="I64" s="90">
         <v>0</v>
@@ -4952,7 +4952,7 @@
       </c>
       <c r="P64" s="91"/>
       <c r="Q64" s="91">
-        <v>9277635.9000000004</v>
+        <v>11474664.9</v>
       </c>
     </row>
     <row r="65" spans="2:17">
@@ -4969,10 +4969,10 @@
         <v>9949.4</v>
       </c>
       <c r="G65" s="90">
-        <v>8712.1</v>
+        <v>8707.2000000000007</v>
       </c>
       <c r="H65" s="90">
-        <v>0</v>
+        <v>14622.2</v>
       </c>
       <c r="I65" s="90">
         <v>0</v>
@@ -4997,7 +4997,7 @@
       </c>
       <c r="P65" s="91"/>
       <c r="Q65" s="91">
-        <v>39941.4</v>
+        <v>54558.7</v>
       </c>
     </row>
     <row r="66" spans="2:17">
@@ -5017,7 +5017,7 @@
         <v>-6767.8</v>
       </c>
       <c r="H66" s="90">
-        <v>0</v>
+        <v>4486.6000000000004</v>
       </c>
       <c r="I66" s="90">
         <v>0</v>
@@ -5042,7 +5042,7 @@
       </c>
       <c r="P66" s="91"/>
       <c r="Q66" s="91">
-        <v>47361.899999999994</v>
+        <v>51848.499999999993</v>
       </c>
     </row>
     <row r="67" spans="2:17" s="1" customFormat="1">
@@ -5100,16 +5100,16 @@
         <v>-22759.200000000001</v>
       </c>
       <c r="E68" s="90">
-        <v>-9075.2000000000007</v>
+        <v>-9468.2000000000007</v>
       </c>
       <c r="F68" s="90">
-        <v>2379.5</v>
+        <v>2772.5</v>
       </c>
       <c r="G68" s="90">
-        <v>5270.8</v>
+        <v>5272</v>
       </c>
       <c r="H68" s="90">
-        <v>0</v>
+        <v>11673.8</v>
       </c>
       <c r="I68" s="90">
         <v>0</v>
@@ -5134,7 +5134,7 @@
       </c>
       <c r="P68" s="91"/>
       <c r="Q68" s="90">
-        <v>-24184.100000000002</v>
+        <v>-12509.100000000002</v>
       </c>
     </row>
     <row r="69" spans="2:17">
@@ -5152,10 +5152,10 @@
         <v>325433</v>
       </c>
       <c r="G69" s="90">
-        <v>581423.19999999995</v>
+        <v>585929.1</v>
       </c>
       <c r="H69" s="90">
-        <v>0</v>
+        <v>395169.3</v>
       </c>
       <c r="I69" s="90">
         <v>0</v>
@@ -5180,7 +5180,7 @@
       </c>
       <c r="P69" s="91"/>
       <c r="Q69" s="91">
-        <v>1573205.7</v>
+        <v>1972880.9000000001</v>
       </c>
     </row>
     <row r="70" spans="2:17">
@@ -5192,16 +5192,16 @@
         <v>2942734</v>
       </c>
       <c r="E70" s="90">
-        <v>2714401.5999999996</v>
+        <v>2714008.5999999996</v>
       </c>
       <c r="F70" s="90">
-        <v>3051627.9999999995</v>
+        <v>3052020.9999999995</v>
       </c>
       <c r="G70" s="90">
-        <v>2493156.4000000004</v>
+        <v>2497658.6</v>
       </c>
       <c r="H70" s="90">
-        <v>0</v>
+        <v>2667451.1</v>
       </c>
       <c r="I70" s="90">
         <v>0</v>
@@ -5226,7 +5226,7 @@
       </c>
       <c r="P70" s="91"/>
       <c r="Q70" s="91">
-        <v>11201920</v>
+        <v>13873873.299999999</v>
       </c>
     </row>
     <row r="71" spans="2:17">
@@ -5265,7 +5265,7 @@
         <v>21284253.800000001</v>
       </c>
       <c r="H72" s="78">
-        <v>0</v>
+        <v>21429472.399999999</v>
       </c>
       <c r="I72" s="78">
         <v>0</v>
@@ -5290,7 +5290,7 @@
       </c>
       <c r="P72" s="79"/>
       <c r="Q72" s="79">
-        <v>83971486</v>
+        <v>105400958.40000001</v>
       </c>
     </row>
     <row r="73" spans="2:17">
@@ -5311,7 +5311,7 @@
         <v>709475.12666666671</v>
       </c>
       <c r="H73" s="78">
-        <v>0</v>
+        <v>691273.30322580645</v>
       </c>
       <c r="I73" s="78">
         <v>0</v>
@@ -5336,7 +5336,7 @@
       </c>
       <c r="P73" s="79"/>
       <c r="Q73" s="79">
-        <v>699629.07492703525</v>
+        <v>697957.92058678949</v>
       </c>
     </row>
     <row r="74" spans="2:17">
@@ -5363,19 +5363,19 @@
       </c>
       <c r="C75" s="17"/>
       <c r="D75" s="89">
-        <v>454335.1</v>
+        <v>454696.90000000224</v>
       </c>
       <c r="E75" s="89">
-        <v>907429.2</v>
+        <v>908323.80000000075</v>
       </c>
       <c r="F75" s="89">
-        <v>954818.1</v>
+        <v>954573.19999999925</v>
       </c>
       <c r="G75" s="89">
-        <v>519252.9</v>
+        <v>519790.29999999702</v>
       </c>
       <c r="H75" s="89">
-        <v>0</v>
+        <v>738724.90000000596</v>
       </c>
       <c r="I75" s="89">
         <v>0</v>
@@ -5400,7 +5400,7 @@
       </c>
       <c r="P75" s="79"/>
       <c r="Q75" s="79">
-        <v>2835835.3</v>
+        <v>3576109.1000000052</v>
       </c>
     </row>
     <row r="76" spans="2:17">
@@ -5409,19 +5409,19 @@
       </c>
       <c r="C76" s="18"/>
       <c r="D76" s="94">
-        <v>-1.0810849954728521E-2</v>
+        <v>1.8152081837216952E-2</v>
       </c>
       <c r="E76" s="94">
-        <v>7.8857805049079577E-3</v>
+        <v>3.9542636332302476E-2</v>
       </c>
       <c r="F76" s="94">
-        <v>4.3588161272999646E-3</v>
+        <v>3.7152253887868122E-2</v>
       </c>
       <c r="G76" s="94">
-        <v>-8.0259945396266644E-3</v>
-      </c>
-      <c r="H76" s="94" t="s">
-        <v>128</v>
+        <v>2.138904859534789E-2</v>
+      </c>
+      <c r="H76" s="94">
+        <v>2.9744538499748039E-2</v>
       </c>
       <c r="I76" s="94" t="s">
         <v>128</v>
@@ -5446,10 +5446,10 @@
       </c>
       <c r="P76" s="94"/>
       <c r="Q76" s="79">
-        <v>-1.7756414074776179E-3</v>
-      </c>
-    </row>
-    <row r="77" spans="2:17" ht="15.75" thickBot="1">
+        <v>2.9196111830496696E-2</v>
+      </c>
+    </row>
+    <row r="77" spans="2:17" ht="15" thickBot="1">
       <c r="B77" s="104"/>
       <c r="C77" s="26"/>
       <c r="D77" s="87"/>
@@ -5467,24 +5467,24 @@
       <c r="P77" s="79"/>
       <c r="Q77" s="88"/>
     </row>
-    <row r="78" spans="2:17" ht="15.75" thickTop="1">
+    <row r="78" spans="2:17" ht="15" thickTop="1">
       <c r="B78" s="59" t="s">
         <v>36</v>
       </c>
       <c r="D78" s="89">
-        <v>25048935.800000001</v>
+        <v>25049297.600000001</v>
       </c>
       <c r="E78" s="89">
-        <v>22970243</v>
+        <v>22970744.599999998</v>
       </c>
       <c r="F78" s="110">
-        <v>25693399.399999999</v>
+        <v>25693547.5</v>
       </c>
       <c r="G78" s="110">
-        <v>24296663.100000001</v>
+        <v>24301702.699999999</v>
       </c>
       <c r="H78" s="110">
-        <v>0</v>
+        <v>24835648.400000006</v>
       </c>
       <c r="I78" s="110">
         <v>0</v>
@@ -5509,7 +5509,7 @@
       </c>
       <c r="P78" s="82"/>
       <c r="Q78" s="82">
-        <v>98009241.299999997</v>
+        <v>122850940.80000001</v>
       </c>
     </row>
     <row r="79" spans="2:17">
@@ -5614,15 +5614,15 @@
       <c r="D86" s="12"/>
       <c r="Q86" s="91"/>
     </row>
-    <row r="87" spans="2:17" ht="15.75">
+    <row r="87" spans="2:17" ht="15.6">
       <c r="B87" s="35"/>
       <c r="D87" s="12"/>
       <c r="Q87" s="91"/>
     </row>
-    <row r="88" spans="2:17" ht="15.75">
+    <row r="88" spans="2:17" ht="15.6">
       <c r="B88" s="35"/>
     </row>
-    <row r="89" spans="2:17" ht="15.75">
+    <row r="89" spans="2:17" ht="15.6">
       <c r="B89" s="35"/>
     </row>
   </sheetData>

--- a/Oil_current.xlsx
+++ b/Oil_current.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="V:\Information Management\Info Sharing and Tracking\Product Services\Operations\Product Creation\ST3\ST3s_Report_Prep\All_Pages_Content_Update\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75D6F203-9DA5-4D39-A2D1-D0F020BFC85B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE799592-970B-48E1-B1E1-BB52EDEDD1C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="16440" windowHeight="28320" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Documentation" sheetId="21" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="130">
   <si>
     <t>Reporting Adjustment</t>
   </si>
@@ -479,7 +479,7 @@
     <t/>
   </si>
   <si>
-    <t xml:space="preserve"> Run Date:  29 June 2026</t>
+    <t xml:space="preserve"> Run Date:  31 July 2026</t>
   </si>
 </sst>
 </file>
@@ -712,7 +712,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -802,6 +802,17 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="double">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -835,7 +846,7 @@
     </xf>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="112">
+  <cellXfs count="113">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1064,20 +1075,23 @@
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1178,9 +1192,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>1697990</xdr:colOff>
+      <xdr:colOff>1694180</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>21861</xdr:rowOff>
+      <xdr:rowOff>18051</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1636,11 +1650,11 @@
     </row>
     <row r="3" spans="1:63" s="2" customFormat="1" ht="19.5" customHeight="1">
       <c r="G3" s="33"/>
-      <c r="H3" s="111" t="s">
+      <c r="H3" s="107" t="s">
         <v>120</v>
       </c>
-      <c r="I3" s="111"/>
-      <c r="J3" s="111"/>
+      <c r="I3" s="107"/>
+      <c r="J3" s="107"/>
       <c r="K3" s="34"/>
       <c r="M3" s="2" t="s">
         <v>38</v>
@@ -2836,11 +2850,11 @@
     </row>
     <row r="3" spans="2:22" s="2" customFormat="1" ht="19.5" customHeight="1">
       <c r="G3" s="33"/>
-      <c r="H3" s="111" t="s">
+      <c r="H3" s="107" t="s">
         <v>120</v>
       </c>
-      <c r="I3" s="111"/>
-      <c r="J3" s="111"/>
+      <c r="I3" s="107"/>
+      <c r="J3" s="107"/>
       <c r="K3" s="34"/>
       <c r="Q3"/>
     </row>
@@ -2922,22 +2936,22 @@
       </c>
       <c r="C7"/>
       <c r="D7" s="90">
-        <v>9791726.6999999993</v>
+        <v>9797215.1999999993</v>
       </c>
       <c r="E7" s="16">
-        <v>10401301.199999999</v>
+        <v>10406583.199999999</v>
       </c>
       <c r="F7" s="16">
-        <v>10278308.9</v>
+        <v>10283338.199999999</v>
       </c>
       <c r="G7" s="16">
-        <v>10007751.800000001</v>
+        <v>10012585.300000001</v>
       </c>
       <c r="H7" s="16">
-        <v>9977907.4000000004</v>
+        <v>9984207.3000000007</v>
       </c>
       <c r="I7" s="16">
-        <v>0</v>
+        <v>9211646.5</v>
       </c>
       <c r="J7" s="16">
         <v>0</v>
@@ -2959,7 +2973,7 @@
       </c>
       <c r="P7" s="8"/>
       <c r="Q7" s="91">
-        <v>9791726.6999999993</v>
+        <v>9797215.1999999993</v>
       </c>
       <c r="V7" s="16"/>
     </row>
@@ -3023,22 +3037,22 @@
         <v>25</v>
       </c>
       <c r="D11" s="90">
-        <v>1579182.9</v>
+        <v>1567050.9</v>
       </c>
       <c r="E11" s="16">
-        <v>1459726.6</v>
+        <v>1445368.3</v>
       </c>
       <c r="F11" s="16">
-        <v>1670794.9</v>
+        <v>1653353.6</v>
       </c>
       <c r="G11" s="16">
-        <v>1644302.4</v>
+        <v>1630395.2</v>
       </c>
       <c r="H11" s="16">
-        <v>1660272.4</v>
+        <v>1647737.4</v>
       </c>
       <c r="I11" s="16">
-        <v>0</v>
+        <v>1569685.2</v>
       </c>
       <c r="J11" s="16">
         <v>0</v>
@@ -3060,7 +3074,7 @@
       </c>
       <c r="P11" s="8"/>
       <c r="Q11" s="91">
-        <v>8014279.2000000011</v>
+        <v>9513590.5999999996</v>
       </c>
     </row>
     <row r="12" spans="2:22" s="1" customFormat="1">
@@ -3069,22 +3083,22 @@
       </c>
       <c r="C12"/>
       <c r="D12" s="90">
-        <v>351193.3</v>
+        <v>352073.8</v>
       </c>
       <c r="E12" s="16">
-        <v>321641.2</v>
+        <v>323801.90000000002</v>
       </c>
       <c r="F12" s="16">
-        <v>353823.9</v>
+        <v>357972.1</v>
       </c>
       <c r="G12" s="16">
-        <v>329849.90000000002</v>
+        <v>332830</v>
       </c>
       <c r="H12" s="16">
-        <v>337241.4</v>
+        <v>340149.4</v>
       </c>
       <c r="I12" s="16">
-        <v>0</v>
+        <v>324604.3</v>
       </c>
       <c r="J12" s="16">
         <v>0</v>
@@ -3106,7 +3120,7 @@
       </c>
       <c r="P12" s="8"/>
       <c r="Q12" s="91">
-        <v>1693749.7000000002</v>
+        <v>2031431.4999999998</v>
       </c>
     </row>
     <row r="13" spans="2:22">
@@ -3114,22 +3128,22 @@
         <v>27</v>
       </c>
       <c r="D13" s="90">
-        <v>175925.6</v>
+        <v>175939.4</v>
       </c>
       <c r="E13" s="16">
-        <v>156255.29999999999</v>
+        <v>156266.29999999999</v>
       </c>
       <c r="F13" s="16">
         <v>169881.60000000001</v>
       </c>
       <c r="G13" s="16">
-        <v>161000.70000000001</v>
+        <v>161030.9</v>
       </c>
       <c r="H13" s="16">
-        <v>158689.29999999999</v>
+        <v>158725.4</v>
       </c>
       <c r="I13" s="16">
-        <v>0</v>
+        <v>151327</v>
       </c>
       <c r="J13" s="16">
         <v>0</v>
@@ -3151,7 +3165,7 @@
       </c>
       <c r="P13" s="8"/>
       <c r="Q13" s="91">
-        <v>821752.5</v>
+        <v>973170.6</v>
       </c>
     </row>
     <row r="14" spans="2:22">
@@ -3159,22 +3173,22 @@
         <v>122</v>
       </c>
       <c r="D14" s="96">
-        <v>662102.4</v>
+        <v>673331.1</v>
       </c>
       <c r="E14" s="76">
-        <v>603743.19999999995</v>
+        <v>615927.9</v>
       </c>
       <c r="F14" s="76">
-        <v>677253.2</v>
+        <v>690537.1</v>
       </c>
       <c r="G14" s="75">
-        <v>648387.9</v>
+        <v>659179.6</v>
       </c>
       <c r="H14" s="75">
-        <v>659544.69999999995</v>
+        <v>668666.6</v>
       </c>
       <c r="I14" s="75">
-        <v>0</v>
+        <v>650895.4</v>
       </c>
       <c r="J14" s="75">
         <v>0</v>
@@ -3196,7 +3210,7 @@
       </c>
       <c r="P14" s="76"/>
       <c r="Q14" s="96">
-        <v>3251031.4000000004</v>
+        <v>3958537.7</v>
       </c>
     </row>
     <row r="15" spans="2:22" s="1" customFormat="1">
@@ -3204,22 +3218,22 @@
         <v>114</v>
       </c>
       <c r="D15" s="90">
-        <v>2768404.1999999997</v>
+        <v>2768395.1999999997</v>
       </c>
       <c r="E15" s="16">
-        <v>2541366.2999999998</v>
+        <v>2541364.4000000004</v>
       </c>
       <c r="F15" s="16">
-        <v>2871753.5999999996</v>
+        <v>2871744.4000000004</v>
       </c>
       <c r="G15" s="16">
-        <v>2783540.9</v>
+        <v>2783435.7</v>
       </c>
       <c r="H15" s="16">
-        <v>2815747.8</v>
+        <v>2815278.8</v>
       </c>
       <c r="I15" s="16">
-        <v>0</v>
+        <v>2696511.9</v>
       </c>
       <c r="J15" s="16">
         <v>0</v>
@@ -3241,7 +3255,7 @@
       </c>
       <c r="P15" s="8"/>
       <c r="Q15" s="91">
-        <v>13780812.800000001</v>
+        <v>16476730.399999999</v>
       </c>
     </row>
     <row r="16" spans="2:22" s="1" customFormat="1">
@@ -3269,19 +3283,19 @@
         <v>472483.3</v>
       </c>
       <c r="E17" s="16">
-        <v>408049.9</v>
+        <v>408060.3</v>
       </c>
       <c r="F17" s="16">
-        <v>413927.6</v>
+        <v>413927</v>
       </c>
       <c r="G17" s="16">
-        <v>444724</v>
+        <v>444723.8</v>
       </c>
       <c r="H17" s="16">
-        <v>443733.5</v>
+        <v>443731.7</v>
       </c>
       <c r="I17" s="16">
-        <v>0</v>
+        <v>464019.8</v>
       </c>
       <c r="J17" s="16">
         <v>0</v>
@@ -3303,7 +3317,7 @@
       </c>
       <c r="P17" s="8"/>
       <c r="Q17" s="91">
-        <v>2182918.2999999998</v>
+        <v>2646945.9</v>
       </c>
     </row>
     <row r="18" spans="2:17">
@@ -3376,13 +3390,13 @@
         <v>9954219.8000000007</v>
       </c>
       <c r="G21" s="16">
-        <v>9390531</v>
+        <v>9390632.4000000004</v>
       </c>
       <c r="H21" s="16">
-        <v>9148799</v>
+        <v>9149218.3000000007</v>
       </c>
       <c r="I21" s="16">
-        <v>0</v>
+        <v>9444530.5</v>
       </c>
       <c r="J21" s="16">
         <v>0</v>
@@ -3404,7 +3418,7 @@
       </c>
       <c r="P21" s="8"/>
       <c r="Q21" s="91">
-        <v>47409943.799999997</v>
+        <v>56854995</v>
       </c>
     </row>
     <row r="22" spans="2:17">
@@ -3428,7 +3442,7 @@
         <v>8248260.5999999996</v>
       </c>
       <c r="I22" s="16">
-        <v>0</v>
+        <v>8026658.5</v>
       </c>
       <c r="J22" s="16">
         <v>0</v>
@@ -3450,7 +3464,7 @@
       </c>
       <c r="P22" s="8"/>
       <c r="Q22" s="91">
-        <v>41040126</v>
+        <v>49066784.5</v>
       </c>
     </row>
     <row r="23" spans="2:17">
@@ -3474,7 +3488,7 @@
         <v>-7070611.9000000004</v>
       </c>
       <c r="I23" s="16">
-        <v>0</v>
+        <v>-7233292</v>
       </c>
       <c r="J23" s="16">
         <v>0</v>
@@ -3496,7 +3510,7 @@
       </c>
       <c r="P23" s="8"/>
       <c r="Q23" s="91">
-        <v>-36374307.200000003</v>
+        <v>-43607599.200000003</v>
       </c>
     </row>
     <row r="24" spans="2:17">
@@ -3514,13 +3528,13 @@
         <v>10944374.200000001</v>
       </c>
       <c r="G24" s="16">
-        <v>10078173.899999999</v>
+        <v>10078275.300000001</v>
       </c>
       <c r="H24" s="16">
-        <v>10326447.700000001</v>
+        <v>10326866.999999998</v>
       </c>
       <c r="I24" s="16">
-        <v>0</v>
+        <v>10237897</v>
       </c>
       <c r="J24" s="16">
         <v>0</v>
@@ -3542,7 +3556,7 @@
       </c>
       <c r="P24" s="8"/>
       <c r="Q24" s="91">
-        <v>52075762.600000001</v>
+        <v>62314180.299999997</v>
       </c>
     </row>
     <row r="25" spans="2:17">
@@ -3562,10 +3576,10 @@
         <v>6485610.4000000004</v>
       </c>
       <c r="H25" s="42">
-        <v>6061292.5999999996</v>
+        <v>6093745.5999999996</v>
       </c>
       <c r="I25" s="42">
-        <v>0</v>
+        <v>6275595.4000000004</v>
       </c>
       <c r="J25" s="42">
         <v>0</v>
@@ -3587,7 +3601,7 @@
       </c>
       <c r="P25" s="8"/>
       <c r="Q25" s="98">
-        <v>31174376</v>
+        <v>37482424.399999999</v>
       </c>
     </row>
     <row r="26" spans="2:17">
@@ -3604,13 +3618,13 @@
         <v>17255416.300000001</v>
       </c>
       <c r="G26" s="16">
-        <v>16563784.299999999</v>
+        <v>16563885.700000001</v>
       </c>
       <c r="H26" s="16">
-        <v>16387740.300000001</v>
+        <v>16420612.599999998</v>
       </c>
       <c r="I26" s="16">
-        <v>0</v>
+        <v>16513492.4</v>
       </c>
       <c r="J26" s="16">
         <v>0</v>
@@ -3632,7 +3646,7 @@
       </c>
       <c r="P26" s="8"/>
       <c r="Q26" s="91">
-        <v>83250138.599999994</v>
+        <v>99796604.699999988</v>
       </c>
     </row>
     <row r="27" spans="2:17">
@@ -3658,22 +3672,22 @@
       </c>
       <c r="C28" s="17"/>
       <c r="D28" s="90">
-        <v>20759030.399999999</v>
+        <v>20759021.399999999</v>
       </c>
       <c r="E28" s="16">
-        <v>18474471</v>
+        <v>18474479.500000004</v>
       </c>
       <c r="F28" s="16">
-        <v>20541097.5</v>
+        <v>20541087.700000003</v>
       </c>
       <c r="G28" s="16">
-        <v>19792049.199999999</v>
+        <v>19792045.200000003</v>
       </c>
       <c r="H28" s="16">
-        <v>19647221.600000001</v>
+        <v>19679623.099999998</v>
       </c>
       <c r="I28" s="16">
-        <v>0</v>
+        <v>19674024.100000001</v>
       </c>
       <c r="J28" s="16">
         <v>0</v>
@@ -3695,7 +3709,7 @@
       </c>
       <c r="P28" s="8"/>
       <c r="Q28" s="90">
-        <v>99213869.699999988</v>
+        <v>118920281</v>
       </c>
     </row>
     <row r="29" spans="2:17">
@@ -3739,22 +3753,22 @@
         <v>49</v>
       </c>
       <c r="D31" s="90">
-        <v>1388554.4</v>
+        <v>1388572.5</v>
       </c>
       <c r="E31" s="16">
-        <v>1223193</v>
+        <v>1223176.8999999999</v>
       </c>
       <c r="F31" s="16">
-        <v>1318684.1000000001</v>
+        <v>1318490.7</v>
       </c>
       <c r="G31" s="16">
-        <v>1263897.1000000001</v>
+        <v>1263815.1000000001</v>
       </c>
       <c r="H31" s="16">
-        <v>1251807.8999999999</v>
+        <v>1251521.7</v>
       </c>
       <c r="I31" s="16">
-        <v>0</v>
+        <v>1333664.8999999999</v>
       </c>
       <c r="J31" s="16">
         <v>0</v>
@@ -3776,7 +3790,7 @@
       </c>
       <c r="P31" s="8"/>
       <c r="Q31" s="91">
-        <v>6446136.5</v>
+        <v>7779241.7999999989</v>
       </c>
     </row>
     <row r="32" spans="2:17">
@@ -3793,13 +3807,13 @@
         <v>388650.6</v>
       </c>
       <c r="G32" s="16">
-        <v>367833.7</v>
+        <v>367901.5</v>
       </c>
       <c r="H32" s="16">
         <v>349925.2</v>
       </c>
       <c r="I32" s="16">
-        <v>0</v>
+        <v>413013.7</v>
       </c>
       <c r="J32" s="16">
         <v>0</v>
@@ -3821,7 +3835,7 @@
       </c>
       <c r="P32" s="8"/>
       <c r="Q32" s="90">
-        <v>1868852.7999999998</v>
+        <v>2281934.2999999998</v>
       </c>
     </row>
     <row r="33" spans="2:17">
@@ -3853,7 +3867,7 @@
         <v>10462.299999999999</v>
       </c>
       <c r="F34" s="16">
-        <v>22941.3</v>
+        <v>12276.3</v>
       </c>
       <c r="G34" s="16">
         <v>11894.1</v>
@@ -3862,7 +3876,7 @@
         <v>10581.2</v>
       </c>
       <c r="I34" s="16">
-        <v>0</v>
+        <v>11209</v>
       </c>
       <c r="J34" s="16">
         <v>0</v>
@@ -3884,7 +3898,7 @@
       </c>
       <c r="P34" s="8"/>
       <c r="Q34" s="91">
-        <v>65982.7</v>
+        <v>66526.7</v>
       </c>
     </row>
     <row r="35" spans="2:17">
@@ -3908,7 +3922,7 @@
         <v>13626.8</v>
       </c>
       <c r="I35" s="16">
-        <v>0</v>
+        <v>14528.6</v>
       </c>
       <c r="J35" s="16">
         <v>0</v>
@@ -3930,7 +3944,7 @@
       </c>
       <c r="P35" s="8"/>
       <c r="Q35" s="91">
-        <v>56150</v>
+        <v>70678.600000000006</v>
       </c>
     </row>
     <row r="36" spans="2:17">
@@ -3939,22 +3953,22 @@
       </c>
       <c r="C36" s="17"/>
       <c r="D36" s="90">
-        <v>485333.8</v>
+        <v>485656.1</v>
       </c>
       <c r="E36" s="16">
-        <v>416742.8</v>
+        <v>417024.8</v>
       </c>
       <c r="F36" s="16">
-        <v>422497.7</v>
+        <v>422699.8</v>
       </c>
       <c r="G36" s="16">
-        <v>339609.1</v>
+        <v>339859.5</v>
       </c>
       <c r="H36" s="16">
-        <v>379369.4</v>
+        <v>380634.4</v>
       </c>
       <c r="I36" s="16">
-        <v>0</v>
+        <v>373853.1</v>
       </c>
       <c r="J36" s="16">
         <v>0</v>
@@ -3976,7 +3990,7 @@
       </c>
       <c r="P36" s="8"/>
       <c r="Q36" s="91">
-        <v>2043552.7999999998</v>
+        <v>2419727.7000000002</v>
       </c>
     </row>
     <row r="37" spans="2:17">
@@ -4009,16 +4023,16 @@
         <v>261443.1</v>
       </c>
       <c r="F38" s="16">
-        <v>295214.3</v>
+        <v>295447.3</v>
       </c>
       <c r="G38" s="16">
         <v>285283.20000000001</v>
       </c>
       <c r="H38" s="16">
-        <v>217668.4</v>
+        <v>217903.3</v>
       </c>
       <c r="I38" s="16">
-        <v>0</v>
+        <v>221429.4</v>
       </c>
       <c r="J38" s="16">
         <v>0</v>
@@ -4040,7 +4054,7 @@
       </c>
       <c r="P38" s="8"/>
       <c r="Q38" s="91">
-        <v>1348825.7</v>
+        <v>1570723</v>
       </c>
     </row>
     <row r="39" spans="2:17">
@@ -4064,7 +4078,7 @@
         <v>26</v>
       </c>
       <c r="I39" s="16">
-        <v>0</v>
+        <v>32.6</v>
       </c>
       <c r="J39" s="16">
         <v>0</v>
@@ -4086,7 +4100,7 @@
       </c>
       <c r="P39" s="8"/>
       <c r="Q39" s="91">
-        <v>417.90000000000003</v>
+        <v>450.50000000000006</v>
       </c>
     </row>
     <row r="40" spans="2:17">
@@ -4148,7 +4162,7 @@
         <v>518354</v>
       </c>
       <c r="I42" s="78">
-        <v>0</v>
+        <v>481208</v>
       </c>
       <c r="J42" s="78">
         <v>0</v>
@@ -4170,7 +4184,8 @@
       </c>
       <c r="P42" s="79"/>
       <c r="Q42" s="79">
-        <v>2583307.4</v>
+        <f t="shared" ref="Q42:Q46" si="0">SUM(D42:O42)</f>
+        <v>3064515.4</v>
       </c>
     </row>
     <row r="43" spans="2:17">
@@ -4179,22 +4194,28 @@
       </c>
       <c r="C43" s="18"/>
       <c r="D43" s="78">
-        <v>1307232.7</v>
+        <f>589852.8+761707.6</f>
+        <v>1351560.4</v>
       </c>
       <c r="E43" s="78">
+        <f>532241+732063.8</f>
         <v>1264304.8</v>
       </c>
       <c r="F43" s="78">
+        <f>539759.3+846515.1</f>
         <v>1386274.4</v>
       </c>
       <c r="G43" s="78">
-        <v>1245264.2000000002</v>
+        <f>536581.6+708570.8</f>
+        <v>1245152.3999999999</v>
       </c>
       <c r="H43" s="78">
+        <f>501093.4+653412.8</f>
         <v>1154506.2000000002</v>
       </c>
       <c r="I43" s="78">
-        <v>0</v>
+        <f>460702.9+522490.8</f>
+        <v>983193.7</v>
       </c>
       <c r="J43" s="78">
         <v>0</v>
@@ -4216,7 +4237,8 @@
       </c>
       <c r="P43" s="79"/>
       <c r="Q43" s="79">
-        <v>6357582.2999999998</v>
+        <f t="shared" si="0"/>
+        <v>7384991.9000000004</v>
       </c>
     </row>
     <row r="44" spans="2:17">
@@ -4237,10 +4259,10 @@
         <v>827814.9</v>
       </c>
       <c r="H44" s="78">
-        <v>954654.6</v>
+        <v>954781.5</v>
       </c>
       <c r="I44" s="78">
-        <v>0</v>
+        <v>804022.8</v>
       </c>
       <c r="J44" s="78">
         <v>0</v>
@@ -4262,7 +4284,8 @@
       </c>
       <c r="P44" s="79"/>
       <c r="Q44" s="79">
-        <v>4267685.8</v>
+        <f t="shared" si="0"/>
+        <v>5071835.4999999991</v>
       </c>
     </row>
     <row r="45" spans="2:17">
@@ -4286,7 +4309,7 @@
         <v>267619.09999999998</v>
       </c>
       <c r="I45" s="80">
-        <v>0</v>
+        <v>293530.8</v>
       </c>
       <c r="J45" s="80">
         <v>0</v>
@@ -4308,7 +4331,8 @@
       </c>
       <c r="P45" s="80"/>
       <c r="Q45" s="80">
-        <v>1418797.3000000003</v>
+        <f t="shared" si="0"/>
+        <v>1712328.1000000003</v>
       </c>
     </row>
     <row r="46" spans="2:17">
@@ -4317,22 +4341,28 @@
       </c>
       <c r="C46" s="17"/>
       <c r="D46" s="89">
-        <v>2971282.5</v>
+        <f t="shared" ref="D46:I46" si="1">SUM(D42:D45)</f>
+        <v>3015610.2</v>
       </c>
       <c r="E46" s="89">
+        <f t="shared" si="1"/>
         <v>2756814.4</v>
       </c>
       <c r="F46" s="89">
+        <f t="shared" si="1"/>
         <v>3147803.8</v>
       </c>
       <c r="G46" s="89">
-        <v>2856338.2</v>
+        <f t="shared" si="1"/>
+        <v>2856226.4</v>
       </c>
       <c r="H46" s="89">
-        <v>2895133.9000000004</v>
+        <f t="shared" si="1"/>
+        <v>2895260.8000000003</v>
       </c>
       <c r="I46" s="89">
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>2561955.2999999998</v>
       </c>
       <c r="J46" s="89">
         <v>0</v>
@@ -4354,7 +4384,8 @@
       </c>
       <c r="P46" s="79"/>
       <c r="Q46" s="79">
-        <v>14627372.799999999</v>
+        <f t="shared" si="0"/>
+        <v>17233670.899999999</v>
       </c>
     </row>
     <row r="47" spans="2:17">
@@ -4380,22 +4411,28 @@
         <v>58</v>
       </c>
       <c r="D48" s="89">
-        <v>5560228.0999999996</v>
+        <f t="shared" ref="D48:I48" si="2">D31+D32+D34+D35+D36+D38+D39+D46</f>
+        <v>5604896.2000000011</v>
       </c>
       <c r="E48" s="89">
-        <v>5036470.9000000004</v>
+        <f t="shared" si="2"/>
+        <v>5036736.8</v>
       </c>
       <c r="F48" s="89">
-        <v>5607955.9000000004</v>
+        <f t="shared" si="2"/>
+        <v>5597532.5999999996</v>
       </c>
       <c r="G48" s="89">
-        <v>5134497.5</v>
+        <f t="shared" si="2"/>
+        <v>5134621.9000000004</v>
       </c>
       <c r="H48" s="89">
-        <v>5118138.8000000007</v>
+        <f t="shared" si="2"/>
+        <v>5119479.4000000004</v>
       </c>
       <c r="I48" s="89">
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>4929686.5999999996</v>
       </c>
       <c r="J48" s="89">
         <v>0</v>
@@ -4417,7 +4454,8 @@
       </c>
       <c r="P48" s="79"/>
       <c r="Q48" s="79">
-        <v>26457291.199999999</v>
+        <f>SUM(D48:O48)</f>
+        <v>31422953.5</v>
       </c>
     </row>
     <row r="49" spans="2:17">
@@ -4457,7 +4495,7 @@
         <v>204114.6</v>
       </c>
       <c r="I50" s="78">
-        <v>0</v>
+        <v>229881.1</v>
       </c>
       <c r="J50" s="78">
         <v>0</v>
@@ -4479,7 +4517,8 @@
       </c>
       <c r="P50" s="79"/>
       <c r="Q50" s="79">
-        <v>1022485.3999999999</v>
+        <f t="shared" ref="Q50:Q52" si="3">SUM(D50:O50)</f>
+        <v>1252366.5</v>
       </c>
     </row>
     <row r="51" spans="2:17">
@@ -4502,7 +4541,7 @@
         <v>118550.1</v>
       </c>
       <c r="I51" s="78">
-        <v>0</v>
+        <v>109090</v>
       </c>
       <c r="J51" s="78">
         <v>0</v>
@@ -4524,7 +4563,8 @@
       </c>
       <c r="P51" s="79"/>
       <c r="Q51" s="79">
-        <v>561497.10000000009</v>
+        <f t="shared" si="3"/>
+        <v>670587.10000000009</v>
       </c>
     </row>
     <row r="52" spans="2:17">
@@ -4532,22 +4572,22 @@
         <v>17</v>
       </c>
       <c r="D52" s="78">
-        <v>395915.8</v>
+        <v>395919.5</v>
       </c>
       <c r="E52" s="78">
-        <v>351889.7</v>
+        <v>351886.4</v>
       </c>
       <c r="F52" s="78">
-        <v>389992.4</v>
+        <v>389952.5</v>
       </c>
       <c r="G52" s="78">
-        <v>370051.7</v>
+        <v>370034.8</v>
       </c>
       <c r="H52" s="78">
-        <v>371063.7</v>
+        <v>370999.9</v>
       </c>
       <c r="I52" s="78">
-        <v>0</v>
+        <v>382034</v>
       </c>
       <c r="J52" s="78">
         <v>0</v>
@@ -4569,7 +4609,8 @@
       </c>
       <c r="P52" s="78"/>
       <c r="Q52" s="78">
-        <v>1878913.2999999998</v>
+        <f t="shared" si="3"/>
+        <v>2260827.1</v>
       </c>
     </row>
     <row r="53" spans="2:17" ht="14.25" customHeight="1">
@@ -4596,22 +4637,22 @@
       </c>
       <c r="C54" s="4"/>
       <c r="D54" s="83">
-        <v>10401719</v>
+        <v>10407001</v>
       </c>
       <c r="E54" s="83">
-        <v>10278358.199999999</v>
+        <v>10283387.5</v>
       </c>
       <c r="F54" s="83">
-        <v>10007751.800000001</v>
+        <v>10012585.300000001</v>
       </c>
       <c r="G54" s="83">
-        <v>9978078.0999999996</v>
+        <v>9984207.3000000007</v>
       </c>
       <c r="H54" s="83">
-        <v>9207711.5</v>
+        <v>9211960.1999999993</v>
       </c>
       <c r="I54" s="83">
-        <v>0</v>
+        <v>9414910.3000000007</v>
       </c>
       <c r="J54" s="83">
         <v>0</v>
@@ -4633,7 +4674,7 @@
       </c>
       <c r="P54" s="83"/>
       <c r="Q54" s="84">
-        <v>9207711.5</v>
+        <v>9414910.3000000007</v>
       </c>
     </row>
     <row r="55" spans="2:17">
@@ -4644,19 +4685,19 @@
         <v>62971.3</v>
       </c>
       <c r="E55" s="78">
-        <v>-12008.8</v>
+        <v>-12014.7</v>
       </c>
       <c r="F55" s="78">
-        <v>-18879.3</v>
+        <v>-18879.5</v>
       </c>
       <c r="G55" s="78">
-        <v>33394.6</v>
+        <v>33390.400000000001</v>
       </c>
       <c r="H55" s="78">
-        <v>-6179.5</v>
+        <v>-39542.699999999997</v>
       </c>
       <c r="I55" s="78">
-        <v>0</v>
+        <v>17742.3</v>
       </c>
       <c r="J55" s="78">
         <v>0</v>
@@ -4678,7 +4719,8 @@
       </c>
       <c r="P55" s="79"/>
       <c r="Q55" s="79">
-        <v>59298.3</v>
+        <f>SUM(D55:O55)</f>
+        <v>43667.100000000006</v>
       </c>
     </row>
     <row r="56" spans="2:17" ht="15" thickBot="1">
@@ -4704,22 +4746,28 @@
         <v>31</v>
       </c>
       <c r="D57" s="89">
-        <v>25049297.600000001</v>
+        <f t="shared" ref="D57:I57" si="4">D7-D54+(D28+D48)-(D50+D51+D52)+D55</f>
+        <v>25094159.5</v>
       </c>
       <c r="E57" s="89">
-        <v>22970744.599999998</v>
+        <f t="shared" si="4"/>
+        <v>22971269.100000005</v>
       </c>
       <c r="F57" s="89">
-        <v>25693547.5</v>
+        <f t="shared" si="4"/>
+        <v>25683349.900000002</v>
       </c>
       <c r="G57" s="89">
-        <v>24301702.699999999</v>
+        <f t="shared" si="4"/>
+        <v>24300540.100000001</v>
       </c>
       <c r="H57" s="89">
-        <v>24835648.400000006</v>
+        <f t="shared" si="4"/>
+        <v>24838142.300000001</v>
       </c>
       <c r="I57" s="89">
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>23697184.100000001</v>
       </c>
       <c r="J57" s="89">
         <v>0</v>
@@ -4741,7 +4789,8 @@
       </c>
       <c r="P57" s="79"/>
       <c r="Q57" s="79">
-        <v>122850940.80000001</v>
+        <f>SUM(D57:O57)</f>
+        <v>146584645.00000003</v>
       </c>
     </row>
     <row r="58" spans="2:17">
@@ -4766,20 +4815,20 @@
         <v>129</v>
       </c>
       <c r="C59" s="4"/>
-      <c r="D59" s="106"/>
-      <c r="E59" s="106"/>
-      <c r="F59" s="106"/>
-      <c r="G59" s="106"/>
-      <c r="H59" s="106"/>
-      <c r="I59" s="106"/>
-      <c r="J59" s="106"/>
-      <c r="K59" s="106"/>
-      <c r="L59" s="106"/>
-      <c r="M59" s="106"/>
-      <c r="N59" s="106"/>
-      <c r="O59" s="106"/>
-      <c r="P59" s="106"/>
-      <c r="Q59" s="107" t="s">
+      <c r="D59" s="110"/>
+      <c r="E59" s="110"/>
+      <c r="F59" s="110"/>
+      <c r="G59" s="110"/>
+      <c r="H59" s="110"/>
+      <c r="I59" s="110"/>
+      <c r="J59" s="110"/>
+      <c r="K59" s="110"/>
+      <c r="L59" s="110"/>
+      <c r="M59" s="110"/>
+      <c r="N59" s="110"/>
+      <c r="O59" s="110"/>
+      <c r="P59" s="110"/>
+      <c r="Q59" s="111" t="s">
         <v>13</v>
       </c>
     </row>
@@ -4876,16 +4925,16 @@
         <v>57853.799999999996</v>
       </c>
       <c r="F63" s="90">
-        <v>76643.399999999994</v>
+        <v>65978.399999999994</v>
       </c>
       <c r="G63" s="90">
         <v>54364.800000000003</v>
       </c>
       <c r="H63" s="90">
-        <v>44470.2</v>
+        <v>44473.7</v>
       </c>
       <c r="I63" s="90">
-        <v>0</v>
+        <v>45842.6</v>
       </c>
       <c r="J63" s="90">
         <v>0</v>
@@ -4907,7 +4956,8 @@
       </c>
       <c r="P63" s="91"/>
       <c r="Q63" s="91">
-        <v>331458.40000000002</v>
+        <f>SUM(D63:O63)</f>
+        <v>366639.5</v>
       </c>
     </row>
     <row r="64" spans="2:17">
@@ -4915,22 +4965,22 @@
         <v>32</v>
       </c>
       <c r="D64" s="90">
-        <v>2486272.5</v>
+        <v>2484777.6</v>
       </c>
       <c r="E64" s="90">
-        <v>2318442.2000000002</v>
+        <v>2316686.2000000002</v>
       </c>
       <c r="F64" s="90">
-        <v>2622767.9</v>
+        <v>2620028.9</v>
       </c>
       <c r="G64" s="90">
-        <v>1850153.3</v>
+        <v>1846953.8</v>
       </c>
       <c r="H64" s="90">
-        <v>2197029</v>
+        <v>2193732.4</v>
       </c>
       <c r="I64" s="90">
-        <v>0</v>
+        <v>2529183.4</v>
       </c>
       <c r="J64" s="90">
         <v>0</v>
@@ -4952,7 +5002,8 @@
       </c>
       <c r="P64" s="91"/>
       <c r="Q64" s="91">
-        <v>11474664.9</v>
+        <f t="shared" ref="Q64:Q70" si="5">SUM(D64:O64)</f>
+        <v>13991362.300000003</v>
       </c>
     </row>
     <row r="65" spans="2:17">
@@ -4972,10 +5023,10 @@
         <v>8707.2000000000007</v>
       </c>
       <c r="H65" s="90">
-        <v>14622.2</v>
+        <v>14625</v>
       </c>
       <c r="I65" s="90">
-        <v>0</v>
+        <v>11975.3</v>
       </c>
       <c r="J65" s="90">
         <v>0</v>
@@ -4997,7 +5048,8 @@
       </c>
       <c r="P65" s="91"/>
       <c r="Q65" s="91">
-        <v>54558.7</v>
+        <f t="shared" si="5"/>
+        <v>66536.800000000003</v>
       </c>
     </row>
     <row r="66" spans="2:17">
@@ -5020,7 +5072,7 @@
         <v>4486.6000000000004</v>
       </c>
       <c r="I66" s="90">
-        <v>0</v>
+        <v>20121</v>
       </c>
       <c r="J66" s="90">
         <v>0</v>
@@ -5042,7 +5094,8 @@
       </c>
       <c r="P66" s="91"/>
       <c r="Q66" s="91">
-        <v>51848.499999999993</v>
+        <f t="shared" si="5"/>
+        <v>71969.5</v>
       </c>
     </row>
     <row r="67" spans="2:17" s="1" customFormat="1">
@@ -5066,7 +5119,7 @@
         <v>0</v>
       </c>
       <c r="I67" s="90">
-        <v>0</v>
+        <v>8689.9</v>
       </c>
       <c r="J67" s="90">
         <v>0</v>
@@ -5088,7 +5141,8 @@
       </c>
       <c r="P67" s="91"/>
       <c r="Q67" s="93">
-        <v>971</v>
+        <f t="shared" si="5"/>
+        <v>9660.9</v>
       </c>
     </row>
     <row r="68" spans="2:17" s="1" customFormat="1">
@@ -5109,10 +5163,10 @@
         <v>5272</v>
       </c>
       <c r="H68" s="90">
-        <v>11673.8</v>
+        <v>11839.6</v>
       </c>
       <c r="I68" s="90">
-        <v>0</v>
+        <v>-1177.4000000000001</v>
       </c>
       <c r="J68" s="90">
         <v>0</v>
@@ -5134,7 +5188,8 @@
       </c>
       <c r="P68" s="91"/>
       <c r="Q68" s="90">
-        <v>-12509.100000000002</v>
+        <f t="shared" si="5"/>
+        <v>-13520.7</v>
       </c>
     </row>
     <row r="69" spans="2:17">
@@ -5143,22 +5198,22 @@
       </c>
       <c r="C69" s="19"/>
       <c r="D69" s="90">
-        <v>345848.1</v>
+        <v>347880.9</v>
       </c>
       <c r="E69" s="90">
-        <v>320501.40000000002</v>
+        <v>322778.59999999998</v>
       </c>
       <c r="F69" s="90">
-        <v>325433</v>
+        <v>328599.5</v>
       </c>
       <c r="G69" s="90">
-        <v>585929.1</v>
+        <v>588060.9</v>
       </c>
       <c r="H69" s="90">
-        <v>395169.3</v>
+        <v>399833.4</v>
       </c>
       <c r="I69" s="90">
-        <v>0</v>
+        <v>362394.3</v>
       </c>
       <c r="J69" s="90">
         <v>0</v>
@@ -5180,7 +5235,8 @@
       </c>
       <c r="P69" s="91"/>
       <c r="Q69" s="91">
-        <v>1972880.9000000001</v>
+        <f t="shared" si="5"/>
+        <v>2349547.5999999996</v>
       </c>
     </row>
     <row r="70" spans="2:17">
@@ -5189,22 +5245,22 @@
       </c>
       <c r="C70" s="19"/>
       <c r="D70" s="90">
-        <v>2942734</v>
+        <v>2943271.9</v>
       </c>
       <c r="E70" s="90">
-        <v>2714008.5999999996</v>
+        <v>2714529.8</v>
       </c>
       <c r="F70" s="90">
-        <v>3052020.9999999995</v>
+        <v>3041783.4999999995</v>
       </c>
       <c r="G70" s="90">
-        <v>2497658.6</v>
+        <v>2496590.9</v>
       </c>
       <c r="H70" s="90">
-        <v>2667451.1</v>
+        <v>2668990.7000000002</v>
       </c>
       <c r="I70" s="90">
-        <v>0</v>
+        <v>2977029.0999999996</v>
       </c>
       <c r="J70" s="90">
         <v>0</v>
@@ -5226,7 +5282,8 @@
       </c>
       <c r="P70" s="91"/>
       <c r="Q70" s="91">
-        <v>13873873.299999999</v>
+        <f t="shared" si="5"/>
+        <v>16842195.899999999</v>
       </c>
     </row>
     <row r="71" spans="2:17">
@@ -5265,10 +5322,10 @@
         <v>21284253.800000001</v>
       </c>
       <c r="H72" s="78">
-        <v>21429472.399999999</v>
+        <v>21429599.300000001</v>
       </c>
       <c r="I72" s="78">
-        <v>0</v>
+        <v>20123902.899999999</v>
       </c>
       <c r="J72" s="78">
         <v>0</v>
@@ -5290,7 +5347,8 @@
       </c>
       <c r="P72" s="79"/>
       <c r="Q72" s="79">
-        <v>105400958.40000001</v>
+        <f>SUM(D72:O72)</f>
+        <v>125524988.19999999</v>
       </c>
     </row>
     <row r="73" spans="2:17">
@@ -5311,10 +5369,10 @@
         <v>709475.12666666671</v>
       </c>
       <c r="H73" s="78">
-        <v>691273.30322580645</v>
+        <v>691277.39677419362</v>
       </c>
       <c r="I73" s="78">
-        <v>0</v>
+        <v>670796.76333333331</v>
       </c>
       <c r="J73" s="78">
         <v>0</v>
@@ -5336,7 +5394,8 @@
       </c>
       <c r="P73" s="79"/>
       <c r="Q73" s="79">
-        <v>697957.92058678949</v>
+        <f>AVERAGE(D73:I73)</f>
+        <v>693431.74330261128</v>
       </c>
     </row>
     <row r="74" spans="2:17">
@@ -5363,22 +5422,28 @@
       </c>
       <c r="C75" s="17"/>
       <c r="D75" s="89">
-        <v>454696.90000000224</v>
+        <f t="shared" ref="D75:I75" si="6">D57-(D70+D72)</f>
+        <v>499020.90000000224</v>
       </c>
       <c r="E75" s="89">
-        <v>908323.80000000075</v>
+        <f t="shared" si="6"/>
+        <v>908327.10000000522</v>
       </c>
       <c r="F75" s="89">
-        <v>954573.19999999925</v>
+        <f t="shared" si="6"/>
+        <v>954613.10000000149</v>
       </c>
       <c r="G75" s="89">
-        <v>519790.29999999702</v>
+        <f t="shared" si="6"/>
+        <v>519695.40000000224</v>
       </c>
       <c r="H75" s="89">
-        <v>738724.90000000596</v>
+        <f t="shared" si="6"/>
+        <v>739552.30000000075</v>
       </c>
       <c r="I75" s="89">
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>596252.10000000149</v>
       </c>
       <c r="J75" s="89">
         <v>0</v>
@@ -5400,7 +5465,8 @@
       </c>
       <c r="P75" s="79"/>
       <c r="Q75" s="79">
-        <v>3576109.1000000052</v>
+        <f>SUM(D75:O75)</f>
+        <v>4217460.9000000134</v>
       </c>
     </row>
     <row r="76" spans="2:17">
@@ -5409,22 +5475,28 @@
       </c>
       <c r="C76" s="18"/>
       <c r="D76" s="94">
-        <v>1.8152081837216952E-2</v>
+        <f t="shared" ref="D76:I76" si="7">IF(D57&gt;0,D75/D57,"")</f>
+        <v>1.9885938000832513E-2</v>
       </c>
       <c r="E76" s="94">
-        <v>3.9542636332302476E-2</v>
+        <f t="shared" si="7"/>
+        <v>3.9541877118143422E-2</v>
       </c>
       <c r="F76" s="94">
-        <v>3.7152253887868122E-2</v>
+        <f t="shared" si="7"/>
+        <v>3.716855876343457E-2</v>
       </c>
       <c r="G76" s="94">
-        <v>2.138904859534789E-2</v>
+        <f t="shared" si="7"/>
+        <v>2.1386166639152281E-2</v>
       </c>
       <c r="H76" s="94">
-        <v>2.9744538499748039E-2</v>
-      </c>
-      <c r="I76" s="94" t="s">
-        <v>128</v>
+        <f t="shared" si="7"/>
+        <v>2.9774863637849466E-2</v>
+      </c>
+      <c r="I76" s="94">
+        <f t="shared" si="7"/>
+        <v>2.5161305979810547E-2</v>
       </c>
       <c r="J76" s="94" t="s">
         <v>128</v>
@@ -5446,7 +5518,8 @@
       </c>
       <c r="P76" s="94"/>
       <c r="Q76" s="79">
-        <v>2.9196111830496696E-2</v>
+        <f>AVERAGE(D76:I76)</f>
+        <v>2.8819785023203797E-2</v>
       </c>
     </row>
     <row r="77" spans="2:17" ht="15" thickBot="1">
@@ -5471,45 +5544,52 @@
       <c r="B78" s="59" t="s">
         <v>36</v>
       </c>
-      <c r="D78" s="89">
-        <v>25049297.600000001</v>
-      </c>
-      <c r="E78" s="89">
-        <v>22970744.599999998</v>
-      </c>
-      <c r="F78" s="110">
-        <v>25693547.5</v>
-      </c>
-      <c r="G78" s="110">
-        <v>24301702.699999999</v>
-      </c>
-      <c r="H78" s="110">
-        <v>24835648.400000006</v>
-      </c>
-      <c r="I78" s="110">
-        <v>0</v>
-      </c>
-      <c r="J78" s="110">
-        <v>0</v>
-      </c>
-      <c r="K78" s="110">
-        <v>0</v>
-      </c>
-      <c r="L78" s="110">
-        <v>0</v>
-      </c>
-      <c r="M78" s="110">
-        <v>0</v>
-      </c>
-      <c r="N78" s="110">
-        <v>0</v>
-      </c>
-      <c r="O78" s="110">
+      <c r="D78" s="112">
+        <f t="shared" ref="D78:I78" si="8">(D70+D72)+D75</f>
+        <v>25094159.5</v>
+      </c>
+      <c r="E78" s="112">
+        <f t="shared" si="8"/>
+        <v>22971269.100000005</v>
+      </c>
+      <c r="F78" s="112">
+        <f t="shared" si="8"/>
+        <v>25683349.900000002</v>
+      </c>
+      <c r="G78" s="112">
+        <f t="shared" si="8"/>
+        <v>24300540.100000001</v>
+      </c>
+      <c r="H78" s="112">
+        <f t="shared" si="8"/>
+        <v>24838142.300000001</v>
+      </c>
+      <c r="I78" s="112">
+        <f t="shared" si="8"/>
+        <v>23697184.100000001</v>
+      </c>
+      <c r="J78" s="106">
+        <v>0</v>
+      </c>
+      <c r="K78" s="106">
+        <v>0</v>
+      </c>
+      <c r="L78" s="106">
+        <v>0</v>
+      </c>
+      <c r="M78" s="106">
+        <v>0</v>
+      </c>
+      <c r="N78" s="106">
+        <v>0</v>
+      </c>
+      <c r="O78" s="106">
         <v>0</v>
       </c>
       <c r="P78" s="82"/>
       <c r="Q78" s="82">
-        <v>122850940.80000001</v>
+        <f>SUM(D78:O78)</f>
+        <v>146584645.00000003</v>
       </c>
     </row>
     <row r="79" spans="2:17">
